--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">恭喜你获得了专长点数！</t>
   </si>
   <si>
-    <t xml:space="preserve">…哎？你不知道什么是专长？</t>
+    <t xml:space="preserve">…嗯？你不知道什么是专长？</t>
   </si>
   <si>
     <t xml:space="preserve">让速度更快，让力量更强

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="799">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -1159,6 +1159,12 @@
   <si>
     <t xml:space="preserve">Oh, you didn’t die even once, huh?
 Good, good. Come here, let me give you some head pats!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAchievement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NERUN2</t>
   </si>
   <si>
     <t xml:space="preserve">nerun_nadenade2</t>
@@ -3665,7 +3671,7 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" ht="12.8">
@@ -3688,7 +3694,7 @@
         <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -3718,7 +3724,7 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="12.8">
@@ -3741,7 +3747,7 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="12.8">
@@ -3764,7 +3770,7 @@
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" ht="12.8">
@@ -3810,7 +3816,7 @@
         <v>29</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="12.8">
@@ -3833,7 +3839,7 @@
         <v>32</v>
       </c>
       <c r="H12" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" ht="12.8">
@@ -3856,7 +3862,7 @@
         <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -3886,7 +3892,7 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" ht="12.8">
@@ -3909,7 +3915,7 @@
         <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" ht="12.8">
@@ -3955,7 +3961,7 @@
         <v>47</v>
       </c>
       <c r="H17" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" ht="12.8">
@@ -4001,7 +4007,7 @@
         <v>53</v>
       </c>
       <c r="H19" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="20" ht="12.8">
@@ -4024,7 +4030,7 @@
         <v>56</v>
       </c>
       <c r="H20" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" ht="12.8">
@@ -4047,7 +4053,7 @@
         <v>59</v>
       </c>
       <c r="H21" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="22" ht="12.8">
@@ -4070,7 +4076,7 @@
         <v>62</v>
       </c>
       <c r="H22" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="23" ht="13.8">
@@ -4093,7 +4099,7 @@
         <v>65</v>
       </c>
       <c r="H23" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="24" ht="13.8">
@@ -4116,7 +4122,7 @@
         <v>68</v>
       </c>
       <c r="H24" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" ht="13.8">
@@ -4139,7 +4145,7 @@
         <v>71</v>
       </c>
       <c r="H25" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="26" ht="13.8">
@@ -4162,7 +4168,7 @@
         <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" ht="12.8">
@@ -4185,7 +4191,7 @@
         <v>77</v>
       </c>
       <c r="H27" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" ht="12.8">
@@ -4208,7 +4214,7 @@
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29" ht="12.8">
@@ -4232,7 +4238,7 @@
         <v>83</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -4263,7 +4269,7 @@
         <v>86</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -4294,7 +4300,7 @@
         <v>89</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="32" ht="12.8">
@@ -4318,7 +4324,7 @@
         <v>92</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -4349,7 +4355,7 @@
         <v>95</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="34" ht="12.8">
@@ -4373,7 +4379,7 @@
         <v>98</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="35" ht="12.8">
@@ -4397,7 +4403,7 @@
         <v>101</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -4428,7 +4434,7 @@
         <v>104</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -4481,7 +4487,7 @@
         <v>109</v>
       </c>
       <c r="H38" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="39" ht="12.8">
@@ -4504,7 +4510,7 @@
         <v>112</v>
       </c>
       <c r="H39" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -4523,7 +4529,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K374"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
     <col min="1" max="3" width="8.83" style="1" customWidth="1"/>
@@ -4619,7 +4625,7 @@
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" ht="35.05">
+    <row r="13" ht="12.8">
       <c r="I13" s="4" t="s">
         <v>126</v>
       </c>
@@ -4639,7 +4645,7 @@
         <v>129</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" ht="23.85">
@@ -4653,7 +4659,7 @@
         <v>131</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" ht="35.05">
@@ -4667,7 +4673,7 @@
         <v>133</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17" ht="23.85">
@@ -4681,10 +4687,10 @@
         <v>135</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="18" ht="22.35">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="H18" s="1">
         <v>327</v>
       </c>
@@ -4695,7 +4701,7 @@
         <v>137</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="19" ht="12.8">
@@ -4733,7 +4739,7 @@
         <v>140</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="24" ht="12.8">
@@ -4761,7 +4767,7 @@
         <v>142</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="26" ht="35.05">
@@ -4775,7 +4781,7 @@
         <v>144</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="27" ht="35.05">
@@ -4789,7 +4795,7 @@
         <v>146</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="28" ht="46.25">
@@ -4803,7 +4809,7 @@
         <v>148</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" ht="22.35">
@@ -4817,7 +4823,7 @@
         <v>150</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" ht="12.8">
@@ -4845,7 +4851,7 @@
         <v>152</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" ht="23.85">
@@ -4859,7 +4865,7 @@
         <v>154</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="33" ht="12.8">
@@ -4887,7 +4893,7 @@
         <v>156</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="36" ht="35.05">
@@ -4901,7 +4907,7 @@
         <v>158</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="37" ht="35.05">
@@ -4915,7 +4921,7 @@
         <v>160</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38" ht="23.85">
@@ -4929,7 +4935,7 @@
         <v>162</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="39" ht="35.05">
@@ -4943,7 +4949,7 @@
         <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="40" ht="34.3">
@@ -4957,7 +4963,7 @@
         <v>166</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="41" ht="35.05">
@@ -4971,7 +4977,7 @@
         <v>168</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="42" ht="12.8">
@@ -4985,7 +4991,7 @@
         <v>170</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="43" ht="12.8">
@@ -5033,7 +5039,7 @@
         <v>172</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="48" ht="12.8">
@@ -5047,7 +5053,7 @@
         <v>174</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="49" ht="12.8">
@@ -5090,7 +5096,7 @@
         <v>176</v>
       </c>
       <c r="K54" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="35.05">
@@ -5104,7 +5110,7 @@
         <v>178</v>
       </c>
       <c r="K55" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="23.85">
@@ -5118,7 +5124,7 @@
         <v>180</v>
       </c>
       <c r="K56" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="32.8">
@@ -5132,7 +5138,7 @@
         <v>182</v>
       </c>
       <c r="K57" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="35.05">
@@ -5146,7 +5152,7 @@
         <v>184</v>
       </c>
       <c r="K58" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="46.25">
@@ -5160,7 +5166,7 @@
         <v>186</v>
       </c>
       <c r="K59" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="23.85">
@@ -5174,7 +5180,7 @@
         <v>188</v>
       </c>
       <c r="K60" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="12.8">
@@ -5214,7 +5220,7 @@
         <v>190</v>
       </c>
       <c r="K66" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" ht="35.05">
@@ -5228,7 +5234,7 @@
         <v>192</v>
       </c>
       <c r="K67" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" ht="12.8">
@@ -5242,7 +5248,7 @@
         <v>194</v>
       </c>
       <c r="K68" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" ht="23.85">
@@ -5256,7 +5262,7 @@
         <v>196</v>
       </c>
       <c r="K69" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" ht="12.8">
@@ -5284,7 +5290,7 @@
         <v>198</v>
       </c>
       <c r="K71" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" ht="12.8">
@@ -5312,7 +5318,7 @@
         <v>200</v>
       </c>
       <c r="K73" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" ht="12.8">
@@ -5326,7 +5332,7 @@
         <v>202</v>
       </c>
       <c r="K74" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" ht="12.8">
@@ -5365,7 +5371,7 @@
         <v>204</v>
       </c>
       <c r="K80" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" ht="22.35">
@@ -5379,7 +5385,7 @@
         <v>206</v>
       </c>
       <c r="K81" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" ht="32.8">
@@ -5393,7 +5399,7 @@
         <v>208</v>
       </c>
       <c r="K82" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" ht="12.8">
@@ -5407,7 +5413,7 @@
         <v>210</v>
       </c>
       <c r="K83" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" ht="32.8">
@@ -5421,7 +5427,7 @@
         <v>212</v>
       </c>
       <c r="K84" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="22.35">
@@ -5435,7 +5441,7 @@
         <v>214</v>
       </c>
       <c r="K85" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="86" ht="12.8">
@@ -5464,7 +5470,7 @@
         <v>216</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="91" ht="35.05">
@@ -5478,7 +5484,7 @@
         <v>218</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="92" ht="23.85">
@@ -5492,7 +5498,7 @@
         <v>220</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="93" ht="35.05">
@@ -5506,7 +5512,7 @@
         <v>222</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="94" ht="12.8">
@@ -5532,7 +5538,7 @@
         <v>224</v>
       </c>
       <c r="K99" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" ht="32.8">
@@ -5546,7 +5552,7 @@
         <v>226</v>
       </c>
       <c r="K100" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" ht="32.8">
@@ -5560,7 +5566,7 @@
         <v>228</v>
       </c>
       <c r="K101" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="12.8">
@@ -5574,7 +5580,7 @@
         <v>230</v>
       </c>
       <c r="K102" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" ht="12.8">
@@ -5617,7 +5623,7 @@
         <v>232</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="107" ht="13.8">
@@ -5638,7 +5644,7 @@
         <v>234</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="108" ht="23.85">
@@ -5659,7 +5665,7 @@
         <v>236</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="109" ht="46.25">
@@ -5680,7 +5686,7 @@
         <v>238</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="110" ht="35.05">
@@ -5701,7 +5707,7 @@
         <v>240</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="111" ht="13.8">
@@ -5762,7 +5768,7 @@
         <v>242</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" ht="23.85">
@@ -5783,7 +5789,7 @@
         <v>244</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" ht="35.05">
@@ -5804,7 +5810,7 @@
         <v>246</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" ht="23.85">
@@ -5825,7 +5831,7 @@
         <v>248</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" ht="35.05">
@@ -5846,7 +5852,7 @@
         <v>250</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" ht="35.05">
@@ -5867,7 +5873,7 @@
         <v>252</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" ht="12.8">
@@ -5916,7 +5922,7 @@
         <v>254</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" ht="23.85">
@@ -5937,7 +5943,7 @@
         <v>256</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" ht="35.05">
@@ -5958,7 +5964,7 @@
         <v>258</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" ht="23.85">
@@ -5979,7 +5985,7 @@
         <v>260</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" ht="12.8">
@@ -6028,7 +6034,7 @@
         <v>262</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" ht="13.8">
@@ -6070,7 +6076,7 @@
         <v>264</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" ht="23.85">
@@ -6091,7 +6097,7 @@
         <v>266</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" ht="12.8">
@@ -6140,7 +6146,7 @@
         <v>268</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" ht="35.05">
@@ -6161,7 +6167,7 @@
         <v>270</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" ht="46.25">
@@ -6182,7 +6188,7 @@
         <v>272</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" ht="35.05">
@@ -6203,7 +6209,7 @@
         <v>274</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" ht="23.85">
@@ -6224,7 +6230,7 @@
         <v>276</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" ht="12.8">
@@ -6285,7 +6291,7 @@
         <v>278</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" ht="35.05">
@@ -6306,7 +6312,7 @@
         <v>280</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" ht="35.05">
@@ -6327,7 +6333,7 @@
         <v>282</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" ht="23.85">
@@ -6348,7 +6354,7 @@
         <v>284</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" ht="23.85">
@@ -6369,7 +6375,7 @@
         <v>286</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" ht="22.35">
@@ -6390,7 +6396,7 @@
         <v>288</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" ht="12.8">
@@ -6463,7 +6469,7 @@
         <v>290</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" ht="23.85">
@@ -6486,44 +6492,39 @@
         <v>293</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="154" s="1" customFormat="1" ht="23.85">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="154" s="1" customFormat="1" ht="22.35">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
+      <c r="E154" s="4" t="s">
+        <v>295</v>
+      </c>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
-      <c r="H154" s="1">
-        <v>231</v>
-      </c>
-      <c r="I154" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="J154" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="K154" s="4" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="155" s="1" customFormat="1" ht="22.35">
+      <c r="I154" s="12"/>
+      <c r="J154" s="10"/>
+      <c r="K154" s="4"/>
+    </row>
+    <row r="155" s="1" customFormat="1" ht="23.85">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
       <c r="H155" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I155" s="12" t="s">
         <v>297</v>
@@ -6532,31 +6533,33 @@
         <v>298</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="156" s="1" customFormat="1" ht="23.85">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="156" s="1" customFormat="1" ht="22.35">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
+      <c r="C156" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
       <c r="H156" s="1">
-        <v>128</v>
-      </c>
-      <c r="I156" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I156" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="J156" s="4" t="s">
+      <c r="J156" s="10" t="s">
         <v>300</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="157" s="1" customFormat="1" ht="12.8">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="157" s="1" customFormat="1" ht="23.85">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -6564,15 +6567,22 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="4"/>
+      <c r="H157" s="1">
+        <v>128</v>
+      </c>
+      <c r="I157" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="J157" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="158" s="1" customFormat="1" ht="12.8">
       <c r="A158" s="4"/>
-      <c r="B158" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B158" s="4"/>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -6584,7 +6594,9 @@
     </row>
     <row r="159" s="1" customFormat="1" ht="12.8">
       <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
+      <c r="B159" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -6595,9 +6607,7 @@
       <c r="K159" s="4"/>
     </row>
     <row r="160" s="1" customFormat="1" ht="12.8">
-      <c r="A160" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -6608,28 +6618,21 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="1" ht="13.8">
-      <c r="A161" s="4"/>
+    <row r="161" s="1" customFormat="1" ht="12.8">
+      <c r="A161" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
-      <c r="H161" s="1">
-        <v>129</v>
-      </c>
-      <c r="I161" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="J161" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="K161" s="4" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="162" s="1" customFormat="1" ht="23.85">
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+    </row>
+    <row r="162" s="1" customFormat="1" ht="13.8">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6638,16 +6641,16 @@
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I162" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="J162" s="4" t="s">
+      <c r="J162" s="10" t="s">
         <v>304</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" ht="23.85">
@@ -6659,7 +6662,7 @@
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
       <c r="H163" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I163" s="12" t="s">
         <v>305</v>
@@ -6668,7 +6671,7 @@
         <v>306</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" ht="23.85">
@@ -6680,7 +6683,7 @@
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
       <c r="H164" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I164" s="12" t="s">
         <v>307</v>
@@ -6689,10 +6692,10 @@
         <v>308</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="1" ht="35.05">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" ht="23.85">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -6701,7 +6704,7 @@
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
       <c r="H165" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I165" s="12" t="s">
         <v>309</v>
@@ -6710,7 +6713,7 @@
         <v>310</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" ht="35.05">
@@ -6722,7 +6725,7 @@
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
       <c r="H166" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I166" s="12" t="s">
         <v>311</v>
@@ -6731,10 +6734,10 @@
         <v>312</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="167" s="1" customFormat="1" ht="23.85">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="167" s="1" customFormat="1" ht="35.05">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -6743,16 +6746,16 @@
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="1">
-        <v>135</v>
-      </c>
-      <c r="I167" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I167" s="12" t="s">
         <v>313</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>314</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="168" s="1" customFormat="1" ht="23.85">
@@ -6764,7 +6767,7 @@
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
       <c r="H168" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I168" s="14" t="s">
         <v>315</v>
@@ -6773,26 +6776,35 @@
         <v>316</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="169" s="1" customFormat="1" ht="12.8">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="169" s="1" customFormat="1" ht="23.85">
       <c r="A169" s="4"/>
-      <c r="B169" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B169" s="4"/>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
-      <c r="K169" s="4"/>
+      <c r="H169" s="1">
+        <v>136</v>
+      </c>
+      <c r="I169" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="J169" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="170" s="1" customFormat="1" ht="12.8">
       <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
+      <c r="B170" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -6803,9 +6815,7 @@
       <c r="K170" s="4"/>
     </row>
     <row r="171" s="1" customFormat="1" ht="12.8">
-      <c r="A171" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
@@ -6816,28 +6826,21 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="1" ht="23.85">
-      <c r="A172" s="4"/>
+    <row r="172" s="1" customFormat="1" ht="12.8">
+      <c r="A172" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
-      <c r="H172" s="1">
-        <v>137</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="J172" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="K172" s="4" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="173" s="1" customFormat="1" ht="13.8">
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
+    </row>
+    <row r="173" s="1" customFormat="1" ht="23.85">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6846,7 +6849,7 @@
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I173" s="12" t="s">
         <v>319</v>
@@ -6855,7 +6858,7 @@
         <v>320</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="174" s="1" customFormat="1" ht="13.8">
@@ -6867,7 +6870,7 @@
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I174" s="12" t="s">
         <v>321</v>
@@ -6876,10 +6879,10 @@
         <v>322</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="175" s="1" customFormat="1" ht="35.05">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="175" s="1" customFormat="1" ht="13.8">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6888,7 +6891,7 @@
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
       <c r="H175" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I175" s="12" t="s">
         <v>323</v>
@@ -6897,10 +6900,10 @@
         <v>324</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="176" s="1" customFormat="1" ht="23.85">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="1" ht="35.05">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6909,7 +6912,7 @@
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I176" s="12" t="s">
         <v>325</v>
@@ -6918,10 +6921,10 @@
         <v>326</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="177" s="1" customFormat="1" ht="35.05">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="1" ht="23.85">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -6930,7 +6933,7 @@
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I177" s="12" t="s">
         <v>327</v>
@@ -6939,28 +6942,35 @@
         <v>328</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="178" s="1" customFormat="1" ht="12.8">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="178" s="1" customFormat="1" ht="35.05">
       <c r="A178" s="4"/>
-      <c r="B178" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B178" s="4"/>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
-      <c r="K178" s="4"/>
+      <c r="H178" s="1">
+        <v>142</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="J178" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="K178" s="4" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="179" s="1" customFormat="1" ht="12.8">
-      <c r="A179" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B179" s="4"/>
+      <c r="A179" s="4"/>
+      <c r="B179" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -6970,28 +6980,21 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="1" ht="13.8">
-      <c r="A180" s="4"/>
+    <row r="180" s="1" customFormat="1" ht="12.8">
+      <c r="A180" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
-      <c r="H180" s="1">
-        <v>143</v>
-      </c>
-      <c r="I180" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="J180" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="K180" s="4" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="181" s="1" customFormat="1" ht="35.05">
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
+    </row>
+    <row r="181" s="1" customFormat="1" ht="13.8">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7000,16 +7003,16 @@
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I181" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="J181" s="4" t="s">
+      <c r="J181" s="10" t="s">
         <v>332</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="182" s="1" customFormat="1" ht="35.05">
@@ -7021,7 +7024,7 @@
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I182" s="12" t="s">
         <v>333</v>
@@ -7030,7 +7033,7 @@
         <v>334</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="183" s="1" customFormat="1" ht="35.05">
@@ -7042,7 +7045,7 @@
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="1">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I183" s="12" t="s">
         <v>335</v>
@@ -7051,10 +7054,10 @@
         <v>336</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="184" s="1" customFormat="1" ht="46.25">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="184" s="1" customFormat="1" ht="35.05">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7063,7 +7066,7 @@
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="1">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I184" s="12" t="s">
         <v>337</v>
@@ -7072,10 +7075,10 @@
         <v>338</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="185" s="1" customFormat="1" ht="12.8">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="185" s="1" customFormat="1" ht="46.25">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -7083,9 +7086,18 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
-      <c r="K185" s="4"/>
+      <c r="H185" s="1">
+        <v>147</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="J185" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="K185" s="4" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="186" s="1" customFormat="1" ht="12.8">
       <c r="A186" s="4"/>
@@ -7101,9 +7113,7 @@
     </row>
     <row r="187" s="1" customFormat="1" ht="12.8">
       <c r="A187" s="4"/>
-      <c r="B187" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B187" s="4"/>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -7114,10 +7124,10 @@
       <c r="K187" s="4"/>
     </row>
     <row r="188" s="1" customFormat="1" ht="12.8">
-      <c r="A188" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B188" s="4"/>
+      <c r="A188" s="4"/>
+      <c r="B188" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -7128,25 +7138,18 @@
       <c r="K188" s="4"/>
     </row>
     <row r="189" s="1" customFormat="1" ht="12.8">
-      <c r="A189" s="4"/>
+      <c r="A189" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="1">
-        <v>148</v>
-      </c>
-      <c r="I189" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="J189" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="K189" s="4" t="s">
-        <v>693</v>
-      </c>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
     </row>
     <row r="190" s="1" customFormat="1" ht="12.8">
       <c r="A190" s="4"/>
@@ -7157,19 +7160,19 @@
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
       <c r="H190" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I190" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="J190" s="4" t="s">
+      <c r="J190" s="10" t="s">
         <v>342</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="191" s="1" customFormat="1" ht="32.8">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" ht="12.8">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7178,7 +7181,7 @@
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I191" s="4" t="s">
         <v>343</v>
@@ -7187,7 +7190,7 @@
         <v>344</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" ht="32.8">
@@ -7199,7 +7202,7 @@
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I192" s="4" t="s">
         <v>345</v>
@@ -7208,10 +7211,10 @@
         <v>346</v>
       </c>
       <c r="K192" s="4" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="193" s="1" customFormat="1" ht="43.25">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" ht="32.8">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7220,7 +7223,7 @@
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="1">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I193" s="4" t="s">
         <v>347</v>
@@ -7229,10 +7232,10 @@
         <v>348</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="194" s="1" customFormat="1" ht="32.8">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" ht="43.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7241,7 +7244,7 @@
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
       <c r="H194" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I194" s="4" t="s">
         <v>349</v>
@@ -7250,10 +7253,10 @@
         <v>350</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="195" ht="32.8">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" ht="32.8">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7262,7 +7265,7 @@
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
       <c r="H195" s="1">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I195" s="4" t="s">
         <v>351</v>
@@ -7271,63 +7274,70 @@
         <v>352</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="196" s="1" customFormat="1" ht="12.8">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="196" ht="32.8">
       <c r="A196" s="4"/>
-      <c r="B196" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="B196" s="4"/>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
+      <c r="H196" s="1">
+        <v>154</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J196" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="197" s="1" customFormat="1" ht="12.8">
-      <c r="B197" s="4"/>
+      <c r="A197" s="4"/>
+      <c r="B197" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
     </row>
     <row r="198" s="1" customFormat="1" ht="12.8">
-      <c r="A198" s="4" t="s">
+      <c r="B198" s="4"/>
+    </row>
+    <row r="199" s="1" customFormat="1" ht="12.8">
+      <c r="A199" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="199" s="1" customFormat="1" ht="12.8"/>
-    <row r="200" s="1" customFormat="1" ht="12.8">
-      <c r="H200" s="1">
+    <row r="200" s="1" customFormat="1" ht="12.8"/>
+    <row r="201" s="1" customFormat="1" ht="12.8">
+      <c r="H201" s="1">
         <v>105</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="J200" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="K200" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="201" s="1" customFormat="1" ht="22.35">
-      <c r="H201" s="1">
-        <v>106</v>
       </c>
       <c r="I201" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="J201" s="4" t="s">
+      <c r="J201" s="10" t="s">
         <v>356</v>
       </c>
       <c r="K201" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="202" s="1" customFormat="1" ht="32.8">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="202" s="1" customFormat="1" ht="22.35">
       <c r="H202" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I202" s="4" t="s">
         <v>357</v>
@@ -7336,12 +7346,12 @@
         <v>358</v>
       </c>
       <c r="K202" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="203" s="1" customFormat="1" ht="32.8">
       <c r="H203" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I203" s="4" t="s">
         <v>359</v>
@@ -7350,12 +7360,12 @@
         <v>360</v>
       </c>
       <c r="K203" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="204" s="1" customFormat="1" ht="22.35">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="204" s="1" customFormat="1" ht="32.8">
       <c r="H204" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I204" s="4" t="s">
         <v>361</v>
@@ -7364,37 +7374,37 @@
         <v>362</v>
       </c>
       <c r="K204" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="205" s="1" customFormat="1" ht="12.8">
-      <c r="B205" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="205" s="1" customFormat="1" ht="22.35">
+      <c r="H205" s="1">
+        <v>109</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="J205" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="K205" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="1" ht="12.8">
+      <c r="B206" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="206" s="1" customFormat="1" ht="12.8">
-      <c r="A206" s="4" t="s">
+    <row r="207" s="1" customFormat="1" ht="12.8">
+      <c r="A207" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="207" s="1" customFormat="1" ht="12.8"/>
-    <row r="208" s="1" customFormat="1" ht="12.8">
-      <c r="H208" s="1">
+    <row r="208" s="1" customFormat="1" ht="12.8"/>
+    <row r="209" s="1" customFormat="1" ht="12.8">
+      <c r="H209" s="1">
         <v>110</v>
-      </c>
-      <c r="I208" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="J208" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="K208" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="209" s="1" customFormat="1" ht="23.85">
-      <c r="H209" s="1">
-        <v>111</v>
       </c>
       <c r="I209" s="4" t="s">
         <v>365</v>
@@ -7403,12 +7413,12 @@
         <v>366</v>
       </c>
       <c r="K209" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="210" s="1" customFormat="1" ht="23.85">
       <c r="H210" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>367</v>
@@ -7417,12 +7427,12 @@
         <v>368</v>
       </c>
       <c r="K210" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="211" s="1" customFormat="1" ht="46.25">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" ht="23.85">
       <c r="H211" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I211" s="4" t="s">
         <v>369</v>
@@ -7431,12 +7441,12 @@
         <v>370</v>
       </c>
       <c r="K211" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="212" s="1" customFormat="1" ht="23.85">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" ht="46.25">
       <c r="H212" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>371</v>
@@ -7445,12 +7455,12 @@
         <v>372</v>
       </c>
       <c r="K212" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="213" ht="23.85">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" ht="23.85">
       <c r="H213" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I213" s="4" t="s">
         <v>373</v>
@@ -7458,55 +7468,55 @@
       <c r="J213" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="K213" s="1" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="214" s="1" customFormat="1" ht="12.8">
-      <c r="B214" s="4" t="s">
+      <c r="K213" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="214" ht="23.85">
+      <c r="H214" s="1">
+        <v>115</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="J214" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" ht="12.8">
+      <c r="B215" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="1" ht="12.8">
-      <c r="B215" s="4"/>
-    </row>
-    <row r="216" s="1" customFormat="1" ht="22.35">
-      <c r="A216" s="4" t="s">
+    <row r="216" s="1" customFormat="1" ht="12.8">
+      <c r="B216" s="4"/>
+    </row>
+    <row r="217" s="1" customFormat="1" ht="22.35">
+      <c r="A217" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="217" s="1" customFormat="1" ht="12.8"/>
-    <row r="218" s="1" customFormat="1" ht="12.8">
-      <c r="H218" s="1">
+    <row r="218" s="1" customFormat="1" ht="12.8"/>
+    <row r="219" s="1" customFormat="1" ht="12.8">
+      <c r="H219" s="1">
         <v>26</v>
-      </c>
-      <c r="I218" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="J218" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="K218" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="219" s="1" customFormat="1" ht="32.8">
-      <c r="H219" s="1">
-        <v>27</v>
       </c>
       <c r="I219" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="J219" s="4" t="s">
+      <c r="J219" s="10" t="s">
         <v>378</v>
       </c>
       <c r="K219" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="220" s="1" customFormat="1" ht="22.35">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="1" ht="32.8">
       <c r="H220" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I220" s="4" t="s">
         <v>379</v>
@@ -7515,12 +7525,12 @@
         <v>380</v>
       </c>
       <c r="K220" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="221" s="1" customFormat="1" ht="64.15">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="1" ht="22.35">
       <c r="H221" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I221" s="4" t="s">
         <v>381</v>
@@ -7529,12 +7539,12 @@
         <v>382</v>
       </c>
       <c r="K221" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="222" s="1" customFormat="1" ht="32.8">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="1" ht="64.15">
       <c r="H222" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I222" s="4" t="s">
         <v>383</v>
@@ -7543,12 +7553,12 @@
         <v>384</v>
       </c>
       <c r="K222" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="223" s="1" customFormat="1" ht="12.8">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="1" ht="32.8">
       <c r="H223" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I223" s="4" t="s">
         <v>385</v>
@@ -7557,40 +7567,40 @@
         <v>386</v>
       </c>
       <c r="K223" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" ht="12.8">
       <c r="H224" s="1">
+        <v>31</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="J224" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="K224" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="225" s="1" customFormat="1" ht="12.8">
+      <c r="H225" s="1">
         <v>32</v>
       </c>
-      <c r="I224" s="4" t="s">
+      <c r="I225" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J224" s="4" t="s">
+      <c r="J225" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K224" t="s">
+      <c r="K225" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="1" ht="22.35">
-      <c r="H225" s="1">
+    <row r="226" s="1" customFormat="1" ht="22.35">
+      <c r="H226" s="1">
         <v>33</v>
-      </c>
-      <c r="I225" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="J225" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="K225" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="226" ht="12.8">
-      <c r="H226" s="1">
-        <v>34</v>
       </c>
       <c r="I226" s="4" t="s">
         <v>389</v>
@@ -7598,106 +7608,106 @@
       <c r="J226" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="K226" s="1" t="s">
-        <v>718</v>
+      <c r="K226" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="227" ht="12.8">
-      <c r="B227" s="4" t="s">
+      <c r="H227" s="1">
+        <v>34</v>
+      </c>
+      <c r="I227" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="J227" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="228" ht="12.8">
+      <c r="B228" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K227" s="1"/>
-    </row>
-    <row r="228" ht="15.65" customHeight="1"/>
+      <c r="K228" s="1"/>
+    </row>
     <row r="229" ht="15.65" customHeight="1"/>
     <row r="230" ht="15.65" customHeight="1"/>
-    <row r="231" ht="12.8">
-      <c r="A231" s="1" t="s">
+    <row r="231" ht="15.65" customHeight="1"/>
+    <row r="232" ht="12.8">
+      <c r="A232" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="233" ht="12.8">
-      <c r="H233" s="1">
+    <row r="234" ht="12.8">
+      <c r="H234" s="1">
         <v>35</v>
       </c>
-      <c r="I233" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="J233" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="K233" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="234" ht="12.8">
-      <c r="B234" s="1" t="s">
+      <c r="I234" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="J234" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="H234" s="1">
-        <v>36</v>
-      </c>
-      <c r="I234" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="J234" s="10" t="s">
-        <v>396</v>
-      </c>
       <c r="K234" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="235" ht="12.8">
       <c r="B235" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H235" s="1">
+        <v>36</v>
+      </c>
+      <c r="I235" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H235" s="1">
+      <c r="J235" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="K235" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="236" ht="12.8">
+      <c r="B236" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H236" s="1">
         <v>37</v>
       </c>
-      <c r="I235" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="J235" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="K235" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="236" ht="12.8">
-      <c r="I236" s="4"/>
-      <c r="J236" s="10"/>
+      <c r="I236" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="J236" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="K236" t="s">
+        <v>723</v>
+      </c>
     </row>
     <row r="237" ht="12.8">
-      <c r="A237" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" ht="22.35">
-      <c r="H238" s="1">
+    <row r="238" ht="12.8">
+      <c r="A238" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I238" s="4"/>
+      <c r="J238" s="10"/>
+    </row>
+    <row r="239" ht="22.35">
+      <c r="H239" s="1">
         <v>38</v>
-      </c>
-      <c r="I238" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="J238" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="K238" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="239" s="1" customFormat="1" ht="22.35">
-      <c r="H239" s="1">
-        <v>39</v>
       </c>
       <c r="I239" s="4" t="s">
         <v>402</v>
@@ -7706,12 +7716,12 @@
         <v>403</v>
       </c>
       <c r="K239" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="240" ht="22.35">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="240" s="1" customFormat="1" ht="22.35">
       <c r="H240" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I240" s="4" t="s">
         <v>404</v>
@@ -7720,12 +7730,12 @@
         <v>405</v>
       </c>
       <c r="K240" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="241" ht="22.35">
       <c r="H241" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I241" s="4" t="s">
         <v>406</v>
@@ -7733,13 +7743,13 @@
       <c r="J241" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="K241" s="1" t="s">
-        <v>725</v>
+      <c r="K241" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="242" ht="22.35">
       <c r="H242" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I242" s="4" t="s">
         <v>408</v>
@@ -7747,13 +7757,13 @@
       <c r="J242" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K242" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="243" ht="32.8">
+      <c r="K242" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="243" ht="22.35">
       <c r="H243" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I243" s="4" t="s">
         <v>410</v>
@@ -7762,77 +7772,77 @@
         <v>411</v>
       </c>
       <c r="K243" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="244" ht="12.8">
-      <c r="B244" s="1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="244" ht="32.8">
+      <c r="H244" s="1">
+        <v>43</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="J244" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="K244" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="245" ht="12.8">
+      <c r="B245" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J244" s="4"/>
-    </row>
-    <row r="245" ht="12.8">
-      <c r="A245" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="J245" s="4"/>
     </row>
     <row r="246" ht="12.8">
-      <c r="H246" s="1">
+      <c r="A246" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J246" s="4"/>
+    </row>
+    <row r="247" ht="12.8">
+      <c r="H247" s="1">
         <v>44</v>
       </c>
-      <c r="I246" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="J246" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="K246" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="247" s="1" customFormat="1" ht="12.8">
-      <c r="B247" s="1" t="s">
+      <c r="I247" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="J247" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="K247" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="248" s="1" customFormat="1" ht="12.8">
+      <c r="B248" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="248" s="1" customFormat="1" ht="12.8"/>
-    <row r="249" s="1" customFormat="1" ht="12.8">
-      <c r="A249" s="4" t="s">
+    <row r="249" s="1" customFormat="1" ht="12.8"/>
+    <row r="250" s="1" customFormat="1" ht="12.8">
+      <c r="A250" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="250" s="1" customFormat="1" ht="23.85">
-      <c r="H250" s="1">
+    <row r="251" s="1" customFormat="1" ht="23.85">
+      <c r="H251" s="1">
         <v>93</v>
-      </c>
-      <c r="I250" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="J250" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="K250" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="251" s="1" customFormat="1" ht="32.8">
-      <c r="H251" s="1">
-        <v>94</v>
       </c>
       <c r="I251" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="J251" s="4" t="s">
+      <c r="J251" s="10" t="s">
         <v>417</v>
       </c>
       <c r="K251" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="1" ht="32.8">
       <c r="H252" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I252" s="4" t="s">
         <v>418</v>
@@ -7841,12 +7851,12 @@
         <v>419</v>
       </c>
       <c r="K252" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="1" ht="32.8">
       <c r="H253" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I253" s="4" t="s">
         <v>420</v>
@@ -7855,40 +7865,40 @@
         <v>421</v>
       </c>
       <c r="K253" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="254" s="1" customFormat="1" ht="12.8">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="254" s="1" customFormat="1" ht="32.8">
       <c r="H254" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I254" s="4" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>127</v>
+        <v>423</v>
       </c>
       <c r="K254" t="s">
-        <v>126</v>
+        <v>734</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="1" ht="12.8">
       <c r="H255" s="1">
+        <v>97</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J255" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K255" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="256" s="1" customFormat="1" ht="12.8">
+      <c r="H256" s="1">
         <v>98</v>
-      </c>
-      <c r="I255" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="J255" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="K255" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="256" s="1" customFormat="1" ht="32.8">
-      <c r="H256" s="1">
-        <v>99</v>
       </c>
       <c r="I256" s="4" t="s">
         <v>424</v>
@@ -7897,54 +7907,54 @@
         <v>425</v>
       </c>
       <c r="K256" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="257" s="1" customFormat="1" ht="12.8">
-      <c r="I257" s="4"/>
-      <c r="J257" s="4"/>
+        <v>735</v>
+      </c>
+    </row>
+    <row r="257" s="1" customFormat="1" ht="32.8">
+      <c r="H257" s="1">
+        <v>99</v>
+      </c>
+      <c r="I257" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="J257" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="K257" t="s">
+        <v>736</v>
+      </c>
     </row>
     <row r="258" s="1" customFormat="1" ht="12.8">
-      <c r="B258" s="4" t="s">
+      <c r="I258" s="4"/>
+      <c r="J258" s="4"/>
+    </row>
+    <row r="259" s="1" customFormat="1" ht="12.8">
+      <c r="B259" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="259" s="1" customFormat="1" ht="12.8">
-      <c r="A259" s="4" t="s">
+    <row r="260" s="1" customFormat="1" ht="12.8">
+      <c r="A260" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="260" s="1" customFormat="1" ht="23.85">
-      <c r="H260" s="1">
+    <row r="261" s="1" customFormat="1" ht="23.85">
+      <c r="H261" s="1">
         <v>100</v>
-      </c>
-      <c r="I260" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="J260" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="K260" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="261" s="1" customFormat="1" ht="43.25">
-      <c r="H261" s="1">
-        <v>101</v>
       </c>
       <c r="I261" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="J261" s="4" t="s">
+      <c r="J261" s="10" t="s">
         <v>429</v>
       </c>
       <c r="K261" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="262" s="1" customFormat="1" ht="32.8">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="262" s="1" customFormat="1" ht="43.25">
       <c r="H262" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I262" s="4" t="s">
         <v>430</v>
@@ -7953,12 +7963,12 @@
         <v>431</v>
       </c>
       <c r="K262" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="263" s="1" customFormat="1" ht="22.35">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="263" s="1" customFormat="1" ht="32.8">
       <c r="H263" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I263" s="4" t="s">
         <v>432</v>
@@ -7967,12 +7977,12 @@
         <v>433</v>
       </c>
       <c r="K263" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="264" s="1" customFormat="1" ht="12.8">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="264" s="1" customFormat="1" ht="22.35">
       <c r="H264" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I264" s="4" t="s">
         <v>434</v>
@@ -7981,57 +7991,57 @@
         <v>435</v>
       </c>
       <c r="K264" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="265" s="1" customFormat="1" ht="12.8">
-      <c r="I265" s="4"/>
-      <c r="J265" s="4"/>
+      <c r="H265" s="1">
+        <v>104</v>
+      </c>
+      <c r="I265" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="J265" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="K265" t="s">
+        <v>741</v>
+      </c>
     </row>
     <row r="266" s="1" customFormat="1" ht="12.8">
-      <c r="B266" s="4" t="s">
+      <c r="I266" s="4"/>
+      <c r="J266" s="4"/>
+    </row>
+    <row r="267" s="1" customFormat="1" ht="12.8">
+      <c r="B267" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="267" s="1" customFormat="1" ht="12.8">
-      <c r="B267" s="4"/>
-    </row>
     <row r="268" s="1" customFormat="1" ht="12.8">
-      <c r="A268" s="4" t="s">
+      <c r="B268" s="4"/>
+    </row>
+    <row r="269" s="1" customFormat="1" ht="12.8">
+      <c r="A269" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="269" s="1" customFormat="1" ht="12.8">
-      <c r="H269" s="1">
-        <v>79</v>
-      </c>
-      <c r="I269" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="J269" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K269" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="1" ht="12.8">
       <c r="H270" s="1">
+        <v>79</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J270" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="K270" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="1" ht="12.8">
+      <c r="H271" s="1">
         <v>80</v>
-      </c>
-      <c r="I270" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="J270" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="K270" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="271" s="1" customFormat="1" ht="43.25">
-      <c r="H271" s="1">
-        <v>81</v>
       </c>
       <c r="I271" s="4" t="s">
         <v>438</v>
@@ -8040,12 +8050,12 @@
         <v>439</v>
       </c>
       <c r="K271" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="272" s="1" customFormat="1" ht="22.35">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="272" s="1" customFormat="1" ht="43.25">
       <c r="H272" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I272" s="4" t="s">
         <v>440</v>
@@ -8054,12 +8064,12 @@
         <v>441</v>
       </c>
       <c r="K272" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="273" s="1" customFormat="1" ht="43.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="273" s="1" customFormat="1" ht="22.35">
       <c r="H273" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I273" s="4" t="s">
         <v>442</v>
@@ -8068,12 +8078,12 @@
         <v>443</v>
       </c>
       <c r="K273" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="274" s="1" customFormat="1" ht="12.8">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="274" s="1" customFormat="1" ht="43.25">
       <c r="H274" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I274" s="4" t="s">
         <v>444</v>
@@ -8082,61 +8092,61 @@
         <v>445</v>
       </c>
       <c r="K274" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="275" ht="12.8">
-      <c r="I275" s="4"/>
-      <c r="J275" s="4"/>
-      <c r="K275" s="1"/>
+        <v>745</v>
+      </c>
+    </row>
+    <row r="275" s="1" customFormat="1" ht="12.8">
+      <c r="H275" s="1">
+        <v>84</v>
+      </c>
+      <c r="I275" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="J275" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="K275" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="276" ht="12.8">
-      <c r="B276" s="4" t="s">
+      <c r="I276" s="4"/>
+      <c r="J276" s="4"/>
+      <c r="K276" s="1"/>
+    </row>
+    <row r="277" ht="12.8">
+      <c r="B277" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K276" s="1"/>
-    </row>
-    <row r="277" ht="12.8">
-      <c r="B277" s="4"/>
       <c r="K277" s="1"/>
     </row>
     <row r="278" ht="12.8">
-      <c r="A278" s="4" t="s">
+      <c r="B278" s="4"/>
+      <c r="K278" s="1"/>
+    </row>
+    <row r="279" ht="12.8">
+      <c r="A279" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K278" s="1"/>
-    </row>
-    <row r="279" ht="12.8">
-      <c r="H279" s="1">
+      <c r="K279" s="1"/>
+    </row>
+    <row r="280" ht="12.8">
+      <c r="H280" s="1">
         <v>85</v>
       </c>
-      <c r="I279" s="4" t="s">
+      <c r="I280" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J279" s="10" t="s">
+      <c r="J280" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K279" s="1" t="s">
+      <c r="K280" s="1" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="280" ht="22.35">
-      <c r="H280" s="1">
-        <v>86</v>
-      </c>
-      <c r="I280" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="J280" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="K280" s="1" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="281" ht="22.35">
       <c r="H281" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I281" s="4" t="s">
         <v>448</v>
@@ -8145,12 +8155,12 @@
         <v>449</v>
       </c>
       <c r="K281" s="1" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="282" ht="43.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="282" ht="22.35">
       <c r="H282" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I282" s="4" t="s">
         <v>450</v>
@@ -8159,12 +8169,12 @@
         <v>451</v>
       </c>
       <c r="K282" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="283" ht="32.8">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="283" ht="43.25">
       <c r="H283" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I283" s="4" t="s">
         <v>452</v>
@@ -8173,12 +8183,12 @@
         <v>453</v>
       </c>
       <c r="K283" s="1" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="284" ht="22.35">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="284" ht="32.8">
       <c r="H284" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I284" s="4" t="s">
         <v>454</v>
@@ -8187,12 +8197,12 @@
         <v>455</v>
       </c>
       <c r="K284" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="285" ht="22.35">
       <c r="H285" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I285" s="4" t="s">
         <v>456</v>
@@ -8201,66 +8211,66 @@
         <v>457</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="286" ht="12.8">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="286" ht="22.35">
       <c r="H286" s="1">
+        <v>91</v>
+      </c>
+      <c r="I286" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="J286" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="K286" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="287" ht="12.8">
+      <c r="H287" s="1">
         <v>92</v>
       </c>
-      <c r="I286" s="4" t="s">
+      <c r="I287" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J286" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="K286" s="1" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="287" ht="12.8">
-      <c r="B287" s="4" t="s">
+      <c r="J287" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="K287" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="288" ht="12.8">
+      <c r="B288" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K287" s="1"/>
-    </row>
-    <row r="289" ht="12.8">
-      <c r="A289" s="4" t="s">
+      <c r="K288" s="1"/>
+    </row>
+    <row r="290" ht="12.8">
+      <c r="A290" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="K289" s="1"/>
-    </row>
-    <row r="290" ht="12.8">
-      <c r="H290" s="1">
+      <c r="K290" s="1"/>
+    </row>
+    <row r="291" ht="12.8">
+      <c r="H291" s="1">
         <v>74</v>
-      </c>
-      <c r="I290" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="J290" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K290" s="1" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="291" ht="32.8">
-      <c r="H291" s="1">
-        <v>75</v>
       </c>
       <c r="I291" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="J291" s="4" t="s">
+      <c r="J291" s="10" t="s">
         <v>462</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="292" ht="43.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="292" ht="32.8">
       <c r="H292" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I292" s="4" t="s">
         <v>463</v>
@@ -8269,12 +8279,12 @@
         <v>464</v>
       </c>
       <c r="K292" s="1" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="293" ht="22.35">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="293" ht="43.25">
       <c r="H293" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I293" s="4" t="s">
         <v>465</v>
@@ -8283,12 +8293,12 @@
         <v>466</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="294" ht="32.8">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="294" ht="22.35">
       <c r="H294" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I294" s="4" t="s">
         <v>467</v>
@@ -8297,61 +8307,61 @@
         <v>468</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="295" ht="12.8">
-      <c r="I295" s="4"/>
-      <c r="J295" s="4"/>
-      <c r="K295" s="1"/>
+        <v>757</v>
+      </c>
+    </row>
+    <row r="295" ht="32.8">
+      <c r="H295" s="1">
+        <v>78</v>
+      </c>
+      <c r="I295" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="J295" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="K295" s="1" t="s">
+        <v>758</v>
+      </c>
     </row>
     <row r="296" ht="12.8">
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
       <c r="K296" s="1"/>
     </row>
-    <row r="297" s="1" customFormat="1" ht="12.8">
-      <c r="B297" s="4" t="s">
+    <row r="297" ht="12.8">
+      <c r="I297" s="4"/>
+      <c r="J297" s="4"/>
+      <c r="K297" s="1"/>
+    </row>
+    <row r="298" s="1" customFormat="1" ht="12.8">
+      <c r="B298" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="298" s="1" customFormat="1" ht="12.8"/>
-    <row r="299" s="1" customFormat="1" ht="12.8">
-      <c r="A299" s="4" t="s">
+    <row r="299" s="1" customFormat="1" ht="12.8"/>
+    <row r="300" s="1" customFormat="1" ht="12.8">
+      <c r="A300" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="300" s="1" customFormat="1" ht="23.85">
-      <c r="H300" s="1">
+    <row r="301" s="1" customFormat="1" ht="23.85">
+      <c r="H301" s="1">
         <v>66</v>
-      </c>
-      <c r="I300" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="J300" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="K300" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="301" s="1" customFormat="1" ht="22.35">
-      <c r="H301" s="1">
-        <v>67</v>
       </c>
       <c r="I301" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="J301" s="4" t="s">
+      <c r="J301" s="10" t="s">
         <v>472</v>
       </c>
       <c r="K301" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="302" s="1" customFormat="1" ht="12.8">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="302" s="1" customFormat="1" ht="22.35">
       <c r="H302" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I302" s="4" t="s">
         <v>473</v>
@@ -8360,12 +8370,12 @@
         <v>474</v>
       </c>
       <c r="K302" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="303" s="1" customFormat="1" ht="22.35">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="303" s="1" customFormat="1" ht="12.8">
       <c r="H303" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I303" s="4" t="s">
         <v>475</v>
@@ -8374,12 +8384,12 @@
         <v>476</v>
       </c>
       <c r="K303" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="304" s="1" customFormat="1" ht="32.8">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="304" s="1" customFormat="1" ht="22.35">
       <c r="H304" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I304" s="4" t="s">
         <v>477</v>
@@ -8388,12 +8398,12 @@
         <v>478</v>
       </c>
       <c r="K304" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="1" ht="32.8">
       <c r="H305" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I305" s="4" t="s">
         <v>479</v>
@@ -8402,12 +8412,12 @@
         <v>480</v>
       </c>
       <c r="K305" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="306" s="1" customFormat="1" ht="22.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="306" s="1" customFormat="1" ht="32.8">
       <c r="H306" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I306" s="4" t="s">
         <v>481</v>
@@ -8416,12 +8426,12 @@
         <v>482</v>
       </c>
       <c r="K306" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="1" ht="22.35">
       <c r="H307" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I307" s="4" t="s">
         <v>483</v>
@@ -8430,50 +8440,50 @@
         <v>484</v>
       </c>
       <c r="K307" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="308" s="1" customFormat="1" ht="12.8">
-      <c r="B308" s="4" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="308" s="1" customFormat="1" ht="22.35">
+      <c r="H308" s="1">
+        <v>73</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J308" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="K308" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="309" s="1" customFormat="1" ht="12.8">
+      <c r="B309" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="309" s="1" customFormat="1" ht="12.8">
-      <c r="A309" s="4" t="s">
+    <row r="310" s="1" customFormat="1" ht="12.8">
+      <c r="A310" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="310" s="1" customFormat="1" ht="12.8">
-      <c r="H310" s="1">
+    <row r="311" s="1" customFormat="1" ht="12.8">
+      <c r="H311" s="1">
         <v>60</v>
-      </c>
-      <c r="I310" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="J310" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="K310" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="311" s="1" customFormat="1" ht="43.25">
-      <c r="H311" s="1">
-        <v>61</v>
       </c>
       <c r="I311" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="J311" s="4" t="s">
+      <c r="J311" s="10" t="s">
         <v>488</v>
       </c>
       <c r="K311" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="312" s="1" customFormat="1" ht="22.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="312" s="1" customFormat="1" ht="43.25">
       <c r="H312" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I312" s="4" t="s">
         <v>489</v>
@@ -8482,12 +8492,12 @@
         <v>490</v>
       </c>
       <c r="K312" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="1" ht="22.35">
       <c r="H313" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I313" s="4" t="s">
         <v>491</v>
@@ -8496,12 +8506,12 @@
         <v>492</v>
       </c>
       <c r="K313" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="314" s="1" customFormat="1" ht="22.35">
       <c r="H314" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I314" s="4" t="s">
         <v>493</v>
@@ -8510,12 +8520,12 @@
         <v>494</v>
       </c>
       <c r="K314" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="315" ht="32.8">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="315" s="1" customFormat="1" ht="22.35">
       <c r="H315" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I315" s="4" t="s">
         <v>495</v>
@@ -8523,40 +8533,40 @@
       <c r="J315" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="K315" s="1" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="316" ht="12.8">
-      <c r="B316" s="4" t="s">
+      <c r="K315" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="316" ht="32.8">
+      <c r="H316" s="1">
+        <v>65</v>
+      </c>
+      <c r="I316" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="J316" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="K316" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="317" ht="12.8">
+      <c r="B317" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K316" s="1"/>
-    </row>
-    <row r="317" s="1" customFormat="1" ht="12.8"/>
+      <c r="K317" s="1"/>
+    </row>
     <row r="318" s="1" customFormat="1" ht="12.8"/>
-    <row r="319" s="1" customFormat="1" ht="12.8">
-      <c r="A319" s="4" t="s">
+    <row r="319" s="1" customFormat="1" ht="12.8"/>
+    <row r="320" s="1" customFormat="1" ht="12.8">
+      <c r="A320" s="4" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="320" s="1" customFormat="1" ht="23.85">
-      <c r="H320" s="1">
-        <v>53</v>
-      </c>
-      <c r="I320" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="J320" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="K320" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="1" ht="23.85">
       <c r="H321" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I321" s="4" t="s">
         <v>499</v>
@@ -8565,12 +8575,12 @@
         <v>500</v>
       </c>
       <c r="K321" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" ht="23.85">
       <c r="H322" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I322" s="4" t="s">
         <v>501</v>
@@ -8579,12 +8589,12 @@
         <v>502</v>
       </c>
       <c r="K322" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="1" ht="23.85">
       <c r="H323" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I323" s="4" t="s">
         <v>503</v>
@@ -8593,95 +8603,95 @@
         <v>504</v>
       </c>
       <c r="K323" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="324" s="1" customFormat="1" ht="12.8">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="324" s="1" customFormat="1" ht="23.85">
       <c r="H324" s="1">
+        <v>56</v>
+      </c>
+      <c r="I324" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="J324" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="K324" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="325" s="1" customFormat="1" ht="12.8">
+      <c r="H325" s="1">
         <v>57</v>
       </c>
-      <c r="I324" s="4" t="s">
+      <c r="I325" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="J324" s="4" t="s">
+      <c r="J325" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K324" t="s">
+      <c r="K325" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="325" s="1" customFormat="1" ht="35.05">
-      <c r="H325" s="1">
+    <row r="326" s="1" customFormat="1" ht="35.05">
+      <c r="H326" s="1">
         <v>58</v>
       </c>
-      <c r="I325" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="J325" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="K325" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="326" ht="12.8">
-      <c r="H326" s="1">
+      <c r="I326" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="J326" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="K326" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="327" ht="12.8">
+      <c r="H327" s="1">
         <v>59</v>
       </c>
-      <c r="I326" s="4" t="s">
+      <c r="I327" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J326" s="10" t="s">
+      <c r="J327" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K326" s="1" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="327" ht="12.8">
-      <c r="B327" s="4" t="s">
+      <c r="K327" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="328" ht="12.8">
+      <c r="B328" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K327" s="1"/>
-    </row>
-    <row r="329" s="1" customFormat="1" ht="12.8"/>
+      <c r="K328" s="1"/>
+    </row>
     <row r="330" s="1" customFormat="1" ht="12.8"/>
-    <row r="331" s="1" customFormat="1" ht="12.8">
-      <c r="A331" s="4" t="s">
+    <row r="331" s="1" customFormat="1" ht="12.8"/>
+    <row r="332" s="1" customFormat="1" ht="12.8">
+      <c r="A332" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="332" s="1" customFormat="1" ht="12.8">
-      <c r="H332" s="1">
+    <row r="333" s="1" customFormat="1" ht="12.8">
+      <c r="H333" s="1">
         <v>45</v>
-      </c>
-      <c r="I332" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="J332" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="K332" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="333" s="1" customFormat="1" ht="22.35">
-      <c r="H333" s="1">
-        <v>46</v>
       </c>
       <c r="I333" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="J333" s="4" t="s">
+      <c r="J333" s="10" t="s">
         <v>510</v>
       </c>
       <c r="K333" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="334" s="1" customFormat="1" ht="32.8">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="334" s="1" customFormat="1" ht="22.35">
       <c r="H334" s="1">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I334" s="4" t="s">
         <v>511</v>
@@ -8690,40 +8700,40 @@
         <v>512</v>
       </c>
       <c r="K334" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="335" s="1" customFormat="1" ht="35.05">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="335" s="1" customFormat="1" ht="32.8">
       <c r="H335" s="1">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I335" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="J335" s="10" t="s">
+      <c r="J335" s="4" t="s">
         <v>514</v>
       </c>
       <c r="K335" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="336" s="1" customFormat="1" ht="43.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="336" s="1" customFormat="1" ht="35.05">
       <c r="H336" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I336" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="J336" s="4" t="s">
+      <c r="J336" s="10" t="s">
         <v>516</v>
       </c>
       <c r="K336" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="337" ht="22.35">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="337" s="1" customFormat="1" ht="43.25">
       <c r="H337" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I337" s="4" t="s">
         <v>517</v>
@@ -8731,40 +8741,40 @@
       <c r="J337" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="K337" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="338" ht="12.8">
-      <c r="B338" s="4" t="s">
+      <c r="K337" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="338" ht="22.35">
+      <c r="H338" s="1">
+        <v>49</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="J338" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="339" ht="12.8">
+      <c r="B339" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K338" s="1"/>
-    </row>
-    <row r="339" s="1" customFormat="1" ht="12.8"/>
+      <c r="K339" s="1"/>
+    </row>
     <row r="340" s="1" customFormat="1" ht="12.8"/>
-    <row r="341" s="1" customFormat="1" ht="12.8">
-      <c r="A341" s="4" t="s">
+    <row r="341" s="1" customFormat="1" ht="12.8"/>
+    <row r="342" s="1" customFormat="1" ht="12.8">
+      <c r="A342" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="342" s="1" customFormat="1" ht="22.35">
-      <c r="H342" s="1">
-        <v>1</v>
-      </c>
-      <c r="I342" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="J342" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="K342" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" ht="22.35">
       <c r="H343" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I343" s="4" t="s">
         <v>521</v>
@@ -8773,12 +8783,12 @@
         <v>522</v>
       </c>
       <c r="K343" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="344" s="1" customFormat="1" ht="32.8">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="344" s="1" customFormat="1" ht="22.35">
       <c r="H344" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I344" s="4" t="s">
         <v>523</v>
@@ -8787,12 +8797,12 @@
         <v>524</v>
       </c>
       <c r="K344" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="345" s="1" customFormat="1" ht="43.25">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="345" s="1" customFormat="1" ht="32.8">
       <c r="H345" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I345" s="4" t="s">
         <v>525</v>
@@ -8801,12 +8811,12 @@
         <v>526</v>
       </c>
       <c r="K345" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="346" s="1" customFormat="1" ht="43.25">
       <c r="H346" s="1">
-        <v>212</v>
+        <v>6</v>
       </c>
       <c r="I346" s="4" t="s">
         <v>527</v>
@@ -8815,12 +8825,12 @@
         <v>528</v>
       </c>
       <c r="K346" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="347" s="1" customFormat="1" ht="22.35">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="347" s="1" customFormat="1" ht="43.25">
       <c r="H347" s="1">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="I347" s="4" t="s">
         <v>529</v>
@@ -8829,12 +8839,12 @@
         <v>530</v>
       </c>
       <c r="K347" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="348" s="1" customFormat="1" ht="74.6">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="348" s="1" customFormat="1" ht="22.35">
       <c r="H348" s="1">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I348" s="4" t="s">
         <v>531</v>
@@ -8843,59 +8853,59 @@
         <v>532</v>
       </c>
       <c r="K348" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="349" ht="12.8">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="349" s="1" customFormat="1" ht="74.6">
       <c r="H349" s="1">
+        <v>17</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="J349" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="K349" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="350" ht="12.8">
+      <c r="H350" s="1">
         <v>7</v>
       </c>
-      <c r="I349" s="4" t="s">
+      <c r="I350" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J349" s="10" t="s">
+      <c r="J350" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K349" s="1" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="350" ht="12.8">
-      <c r="B350" s="4" t="s">
+      <c r="K350" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="351" ht="12.8">
+      <c r="B351" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K350" s="1"/>
-    </row>
-    <row r="352" ht="12.8">
-      <c r="A352" s="1" t="s">
+      <c r="K351" s="1"/>
+    </row>
+    <row r="353" ht="12.8">
+      <c r="A353" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="353" ht="12.8">
-      <c r="D353" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="354" ht="22.35">
-      <c r="H354" s="1">
+    <row r="354" ht="12.8">
+      <c r="D354" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="355" ht="22.35">
+      <c r="H355" s="1">
         <v>8</v>
-      </c>
-      <c r="I354" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="J354" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="K354" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="355" ht="43.25">
-      <c r="H355" s="1">
-        <v>9</v>
       </c>
       <c r="I355" s="4" t="s">
         <v>537</v>
@@ -8904,15 +8914,12 @@
         <v>538</v>
       </c>
       <c r="K355" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="356" ht="22.35">
-      <c r="B356" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>790</v>
+      </c>
+    </row>
+    <row r="356" ht="43.25">
       <c r="H356" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I356" s="4" t="s">
         <v>539</v>
@@ -8921,55 +8928,52 @@
         <v>540</v>
       </c>
       <c r="K356" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="359" ht="12.8">
-      <c r="A359" s="1" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="357" ht="22.35">
+      <c r="B357" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H357" s="1">
+        <v>10</v>
+      </c>
+      <c r="I357" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="H359" s="1">
+      <c r="J357" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="K357" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="360" ht="12.8">
+      <c r="A360" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H360" s="1">
         <v>11</v>
       </c>
-      <c r="I359" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="J359" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="K359" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="360" ht="12.8">
-      <c r="B360" s="1" t="s">
+      <c r="I360" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D360" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H360" s="1">
-        <v>12</v>
-      </c>
-      <c r="I360" s="1" t="s">
+      <c r="J360" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="J360" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="K360" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="361" ht="12.8">
       <c r="B361" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H361" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>547</v>
@@ -8978,80 +8982,100 @@
         <v>548</v>
       </c>
       <c r="K361" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="362" ht="12.8">
       <c r="B362" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H362" s="1">
+        <v>13</v>
+      </c>
+      <c r="I362" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D362" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="H362" s="1">
-        <v>14</v>
-      </c>
-      <c r="I362" s="1" t="s">
+      <c r="J362" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="J362" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="K362" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="363" ht="12.8">
       <c r="B363" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H363" s="1">
+        <v>14</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="J363" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="K363" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="364" ht="12.8">
+      <c r="B364" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D363" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="367" ht="12.8">
-      <c r="A367" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H367" s="1">
+      <c r="D364" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="368" ht="12.8">
+      <c r="A368" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H368" s="1">
         <v>15</v>
       </c>
-      <c r="I367" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="J367" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="K367" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="368" ht="12.8">
-      <c r="B368" s="1" t="s">
+      <c r="I368" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="K368" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="369" ht="12.8">
+      <c r="B369" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="371" ht="12.8">
-      <c r="A371" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
     <row r="372" ht="12.8">
-      <c r="H372" s="1">
+      <c r="A372" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="373" ht="12.8">
+      <c r="H373" s="1">
         <v>16</v>
       </c>
-      <c r="I372" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="J372" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="K372" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="373" ht="12.8">
-      <c r="B373" s="1" t="s">
+      <c r="I373" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="J373" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="K373" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="374" ht="12.8">
+      <c r="B374" s="1" t="s">
         <v>138</v>
       </c>
     </row>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="index" sheetId="1" r:id="rId3"/>
-    <sheet name="nerun" sheetId="2" r:id="rId4"/>
+    <sheet name="index" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="nerun" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="559">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -2283,955 +2283,6 @@
   <si>
     <t xml:space="preserve">Don't disturb me for nothing.</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">冒险的开始</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工具的使用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">十分重要的事情</t>
-  </si>
-  <si>
-    <t xml:space="preserve">装备的重要性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">食物相关</t>
-  </si>
-  <si>
-    <t xml:space="preserve">素材硬度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡眠和休息</t>
-  </si>
-  <si>
-    <t xml:space="preserve">道具特性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">世界地图</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成长和专长</t>
-  </si>
-  <si>
-    <t xml:space="preserve">善恶值</t>
-  </si>
-  <si>
-    <t xml:space="preserve">弱化和恢复</t>
-  </si>
-  <si>
-    <t xml:space="preserve">酸和装备的劣化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信仰和祈祷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">死亡和惩罚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同伴与居民的复活</t>
-  </si>
-  <si>
-    <t xml:space="preserve">童年的结束</t>
-  </si>
-  <si>
-    <t xml:space="preserve">危险的水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">场地效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">以太病</t>
-  </si>
-  <si>
-    <t xml:space="preserve">旅行商人营地</t>
-  </si>
-  <si>
-    <t xml:space="preserve">城镇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">影响度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快递箱</t>
-  </si>
-  <si>
-    <t xml:space="preserve">盟约之石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">居民的工作与兴趣</t>
-  </si>
-  <si>
-    <t xml:space="preserve">牧草和家畜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">垃圾问题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">季节</t>
-  </si>
-  <si>
-    <t xml:space="preserve">冬季预警</t>
-  </si>
-  <si>
-    <t xml:space="preserve">世界终末之时</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你感觉到了吗？
-这种诡异的气氛…有什么特别的「法则」在起作用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这一定是…没错，是「场地效果」的影响。
-虽然从前听说过，但实际体验还是第一次。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">场地效果是仅适用于现在所在地图的特殊规则。
-看到时钟右侧那个之前没见过的图标了吗？
-调查这个图标你就能知道是什么效果了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">足以改写世界法则的力量在此处生效…
-想必这背后定有相应的缘由。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…小心前进吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">叮铃！ 
-自从你开始冒险后…
-居然已经过了两千年的时间！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">您还真是长寿啊？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我？　
-…真没礼貌。我当然是永远朝气蓬勃的妖精少女啊。
-所谓妖精，就是这种生物啦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是不得了啦！
-这个世界也不是能永远持续下去的。
-毁灭的时刻，正在逐渐逼近。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">据说会有世界终末之时…
-我也不清楚具体的情况。
-但传闻如果经历了四千年，这个世界就会开裂。
-并发生各种异常现象。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">遗憾的是，直到现在都没发现规避开裂的方法。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想让与你的冒险永远继续下去…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所以…
-让今后的时间推进速度变慢一点吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">发现药草了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有时在野外会发现带颜色的草
-那就是药草
-吃了它们对健康有好处。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当然，药草也可以作为调味料使用
-用「石磨」把它们磨成粉
-也可以作为很多药材的原料。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">打开你的背包
-观察一下刚才摘取的药草吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能看到带着像是【止血】这样被【】围住的效果对吧？
-这种效果就被称为「道具特性」
-用它们进行制造时，成品就会继承那个特征。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">例如，用有止血效果、解毒效果的药草制作绷带…
-怎么样，豁然开朗吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草的颜色不同其效果也会不同
-请收集各种颜色的药草吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要带颜色的哦…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">叮铃！
-冬天…马上要冬天 了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">记得把田里的作物都要收获完哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已经秋天了…
-时间过的真快啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">北提里斯毕竟是北方大陆
-就算是阳光暴晒的夏天
-也不至于热到不能出门。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是冬天会对生活有各种影响
-现在就开始做准备比较好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果有种植作物
-它们到了冬天就会枯萎
-在那之前记得要好好收获哦？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无论是湖泊还是海洋都会结冰，结冰后当然也不能钓鱼了。
-如果你以钓鱼为生，那就要多加注意了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了，到了十二月，在东边一个叫诺耶尔的村子里
-会举办有名的节日庆典。
-小摊贩会卖非常美味的点心
-绝对要去看看！要记住哦！？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">除了冬天以外，每个季节各地都会举办庆典。
-有时间的话顺便去看看吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…你会用斧头吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点击游戏画面中的背包标志，会显示持有物品对吧？
-从那里找到斧头之后点击右键，就能手持它。
-在手持斧头的状态下右键点击地面上的树，就能伐木了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…咦？你已经会了？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…啊哈哈…
-别在意啦…不管是谁最初都是新手嘛。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">顺带一提，画面右下角有带数字的栏位吧？
-你可以把斧子拖动到那里
-然后用鼠标滚轮切换手持工具，非常方便哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嗯，哦…你已经会用了呢！
-我也觉得你会，只是以防万一…以防万一啦？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么再见…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">话说你听说过影响力吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">完成委托，进行投资
-只要对城镇有贡献，你的对城镇的「影响力」就会提升。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">影响力增高之后，就可以刷新委托
-立刻让商店进货
-大家会同意你的各种不讲道理的要求.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">而·且·呢…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">影响力还能当作货币使用。
-例如城镇上的秘书贩卖的「家具征收券」
-就是备受欢迎的交换品之一。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对城镇里的家具使用征收券的话，就可以将其强制没收。
-想要收集只有特定城镇才有的家具时就用它吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快看，那里有快递箱！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">带了太多道具难以移动…
-但是，又不想把东西扔掉…
-快递箱就是为这样的冒险者解决烦恼的便利服务。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">只要把道具放入这个箱子内
-道具就会自动送到你下一次到达的据点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">可以寄送在城镇中购买的沉重家具
-可以用于据点间搬运物品
-熟练使用的话会很方便哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">早上好，瞌睡虫。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…别担心，我不是什么幻觉。
-我是向导诺伦，帮助你冒险就是我的职责。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好了，既然你醒过来了
-今天就送给你「冒险之书」吧。
-这是能随时回放我们对话的好东西。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，今后再会了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呀啊啊啊啊啊啊啊
-啊啊啊啊啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不好了，装备被酸腐蚀了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">装备被腐蚀之后会有-1，-2这样的减益
-性能也会降低。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在这个世界里，有只要接触就会喷一身酸液
-或患上奇怪的疾病，或破坏装备的讨厌生物
-要多加小心哦。
-…要从失败中学习经验呀冒险者！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…话说回来，腐蚀后难以使用的装备
-可以用砂轮来恢复原状
-所以不要扔掉带在身上更好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是你据点的居民一览。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在名字的右边可以看到一个提包图标吧？
-把鼠标放在那里，就能看到居民的兴趣和工作。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">居民的工作多种多样，
-其中有能提高据点的治安和肥沃度的人，
-也有能生产贵重道具的人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但要注意的是，如果不具备环境条件居民就不会工作。
-工作名称显示为黄色就代表着现在无法执行该工作。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大部分情况下，只要把工作所要用到的家具安装在据点，
-就可以进行工作了。
-例如研究工作就需要安装书架。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工作效率也会随着居民的成长提高。
-还有床的质量影响也会影响效率，所以请准备好居民数量对应的床会比较好呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是牧草呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这是一种随处可见的的牧草
-是家畜的好饲料。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">把牧草放在地上或者放在公用箱子里，
-据点中的家畜就会每天去自己吃。
-吃饱牧草的家畜就会偶尔生产蛋和奶。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了，把种子带回去，
-在你的据点也栽培一些怎么样？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是水啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你现在肯定是一脸“这不是明摆着”的表情吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…罢了，看来你只有亲自领教一下深水区的厉害才会知道恐怖。
-一旦进去马上就会窒息而死，可别怪我没警告过你啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#pc啊
-怎么这么丢人地死掉了呀…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">究竟是怎么死的呢？
-不过没关系啦
-不论多少次我都会让你复活的！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当然死亡也是有代价的。
-死亡时身上持有的一部分金钱会在原地掉落
-能力值也会有所降低
-所以请尽量避免死亡。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是，在你到达这里最初的90天里
-并不会受到死亡的惩罚效果。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所以趁此机会去挑战各种事物
-亲身体验各种事情吧，哈哈哈。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你的同伴死掉了呢…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">放心啦，你也不必那么失落。
-只要过一周左右
-它们就会精神饱满地回来了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">死去的同伴会暂时离开你的队伍
-被传送到同伴所属的据点中去。
-等过一段时间再回到据点确认同伴的情况吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果等不及的话，可以去找各个城镇的酒保对话
-虽然得花点钱，但是可以立刻召回同伴。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了，如果是从菲亚玛那里得到的宠物
-据说只要和她对话，就能随时将其复活哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我知道你一定很难过，不过还请继续加油吧…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">叮铃！
-你的冒险者新手保护期结束咯～！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦，你居然一次也没死过呢？
-了不起。来，摸摸头～摸摸头～！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在这段时间里你死了#1次…
-你到底在搞什么啊？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">就算是我都从没见过你这样的冒险者…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接下来如果死掉
-就会有惩罚了，要小心哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">讨厌，到处都是垃圾！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你就是传说中的…不收拾家的冒险者吗？
-不好好打扫垃圾的话会出大问题的哦？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">随着居民人数的增加，产生的垃圾也会增加
-所以需要采取一些对策！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最快的解决方法是实施
-「严惩乱扔垃圾法」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">实施这个政策的话，基本就不会出现垃圾了。
-但是，这会让居民素质降低，之后还是要
-换成更好的垃圾应对措施。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">立起垃圾场标志，或者安装垃圾箱的话
-居民会根据居民素质的高低
-自动去倒垃圾。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">而且，如果有负责打扫的居民
-把垃圾分类的概率也会大幅增加。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">垃圾经过分解能成为宝贵的资源
-所以要有效利用才对呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，探索洞穴？
-你也变得像个真正的冒险者了呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过，前往深处之前请先自我检查一下。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…你这身装备没问题吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">洞窟里的敌人会更加的多。
-如果还有3到4个部位没有装备的话
-为了生命安全，还是重新考虑一下比较好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在据点可以制作简单的武器和防具
-也可以去城镇的商店购买。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特别是防御力(PV），是减轻敌人伤害的重要属性
-如果感觉到敌人的攻击难以抵挡
-请试着提高防御力。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">太好了，你家园中的盟约之石成长了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没错，这神秘的石头是会成长的。
-随着盟约之石的成长，你的据点能获得各种恩惠。
-比如提升可容纳居民的数量，学会新的政策之类的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">再有就是，成长后的盟约之石能保护家园内的道具不被那些能使用麻烦属性攻击的敌人破坏。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">盟约之石会随着出货和时间经过自动成长。
-…不过需要注意的是，盟约之石等级提升之后也会引起一些更加危险的家伙的注意…也就是说可能会有更强的敌人前来袭击。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果对出现在据点里的敌人感到棘手的话。
-可以通过实施「抑制成长」的政策让盟约之石停止成长。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜你获得了专长点数！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…嗯？你不知道什么是专长？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">让速度更快，让力量更强
-这类特质就是所谓的专长
-只要使用专长点数就能获得这些特质哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在画面下面有蓝色羽毛标志的图标计量表对吧？
-在你采取行动获得相应成长后，这个计量表就会增加。
-当计量表满后就会得到专长点数。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点击这个计量表，就能查看你所能获得的专长一览表了
-你可以在里面选择你认为有用的专长。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果觉得目前没有特别需要的专长
-将专长点数存起来也是不错的选择。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">顺便说一下，学习某些专长可能会需要前置条件。
-例如「美食家」专长
-必须有「烹饪」技能才能显示出来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不错，你拿到了原木呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原木老师不仅是基础的制造素材
-还是优秀的篝火燃料呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…不仅如此！
-原木老师还能经过加工
-进化为「厚板」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎…？你问该怎么加工？
-嗯，不如问问原木老师如何？
-提示是「加工设备」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…顺便说一下，石头也可以加工成「石料」
-要记住哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真棒，你制造了道具呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">所有的道具都是由「素材」构成的。
-然后每种「素材」都有特质。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">例如纸质道具很轻
-铁质道具虽然很重但不易燃烧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">素材还有一种重要的特质指标，那就是「硬度」
-尤其对于镐子一类的工具
-素材的硬度会影响能挖掘到的石头和矿石的种类
-所以「硬度」十分重要。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果出现用现在的镐挖不动的石头的话
-用更硬的素材重新做镐就好了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不过…提高开采技能
-用更大力挖也是可以的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真棒，你做出制作台了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我教你一件重要的事情。
-为了成为独当一面的冒险者，这件事你一定要记住…
-那就是…「中键点击」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">背包的物品，地图上的生物和道具
-都可以通过中键点击来「干涉」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">比如踢开碍事的生物
-打开机器的开关
-混合药水
-打开同伴的背包
-平时做不到的各种行动，都可以通过中键点击来互动。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还有在安装家具和墙壁等的时候
-如果进行中键点击就可以旋转对象…
-不懂这个技巧的冒险者，可没法在这个世界活下去哟。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…怎样？中键点击…记住了吗…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了对了
-中键点击也可以用键盘的「R」键代替。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，再会了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇…是蘑菇吗，可以给我点么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不行</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊呜啊呜。真好吃～。
-这是我最喜欢的东西。要记好哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蘑菇虽然很好吃，但是并不耐饥
-时间一长还会腐烂。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没错，食物一直放着就会腐烂的。
-你不知道吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吃腐烂的东西会弄坏肚子
-所以绝对不可以吃哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鱼和生食特别容易腐烂。
-相对的，树木的果实和烹饪后的食物能保存很久。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果有石磨的话，也能做像干粮那样完全不腐烂的料理。
-长途旅行之前，一定要准备好足够的耐储食品
-这是冒险者的铁则哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小气！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇，快看，有好多商人啊！
-他们在卖各种商品呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">简直就像是小镇的一角。
-看，那边的委托告示板
-发布了好多面向冒险者的委托。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">完成委托能得到各种报酬
-要记得仔细检查委托告示板！
-要注意的是★数越多的委托就会越难。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呀，这个营地有治疗师啊。
-治疗师能治愈异常状态，那边的魔术师能够鉴定未鉴定品…虽然不是免费的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那个商队的队长…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好…好可爱！
-戴着猫的帽子。
-嗯，要不要走近了看看？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是城镇～！
-人来人往得很有活力呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">买卖道具、训练、交易、赌博、委托、恢复…
-城镇上有各种服务。
-迷路了也没关系。
-和警卫搭话就可以让他给我们带路啦。嘿嘿。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还有哦，北提里斯各个城镇的发展度不同
-所以能买卖的东西，接受的服务，训练的技能也不同。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不同城镇在委托告示板上刊登的委托倾向也不一样
-去各种各样的城镇看看也不错呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总之，先试着探索这个城镇吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你刚才干了坏事吧…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">唉…你的善恶值降低了。
-在这个世界作恶就会降低善恶值
-善恶值到达0以下就会成为犯罪者。
-…成为犯罪者的话是很难活下去的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">处理委托，归还失物
-平日行善，善恶值就会提升。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…顺便说下
-在这个世界最重的罪就是滞纳税金。
-连续四个月不交税的话马上就会被通缉
-可是会被盯上性命的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">千万要注意…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">讨厌…！
-别过来，变态！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竟然堕落成了犯罪者，
-真是看错你了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…哼，善恶值降到0以下，你就会被通缉了。
-守卫会追赶你，商人们会拒绝与你交易，妹们也会对你冷眼相待
-被当作社会的敌人，度过悲惨地一生！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是的…不过你也还有重新做人的机会啦。
-善恶值为负数时，善恶值会缓缓上升。
-停止做坏事，老实待着，总有一天风头会过去…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">去流氓聚集的无法之城特尔斐
-可以补缴税金，也会有商人愿意和你交易。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没问题，我相信你
-好好赎罪后再回来吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我就说这么多了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你终于还是病倒了呢… </t>
-  </si>
-  <si>
-    <t xml:space="preserve">没什么好惊讶的。
-即使什么也不做以太也会慢慢侵蚀你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然现在的症状很轻可以无视
-但如果放任疾病发展，症状就会不断恶化最后致死。
-…所以必须找到延缓病情的方法。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘿嘿，不用那么担心。
-时间很充裕，肯定能找解决办法的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">说起来，诺耶尔南面的雪原工房里
-有位丘陵人在收集奇怪的道具。
-如果是他的话，可能会有一些线索…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咦，你信仰了神么…？
-哼哼…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告诉我嘛！你信仰了谁？
-你初次信仰的是谁？呵呵呵。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你果然是有这样的兴趣啊。
-哼～…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信仰神之后，根据信仰的虔诚度会得到各种各样的恩惠。
-信仰会随着供奉和时间的流逝而加深。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">另外，也可以对神使用一天一次的「祈祷」能力。
-根据神明的心情，可能会为你恢复体力，也可能会给你一些礼物。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过「祈祷」可以锻炼你的信仰技能
-可以试着每日进行一次祈祷看看呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还有要小心不能惹#god生气哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊…你变弱了吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咦？你还问怎么回事…
-稍微确认下自己的主能力吧？
-是不是比平时更低了？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有些敌人的攻击会削弱你的能力。
-稍微弱化点倒是没什么问题，不过积累起来的话还是会很棘手。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果有肉体复苏或者精神复苏的药水的话
-喝掉就可以恢复弱化状态。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没有恢复手段的时候，可以去找镇上的治疗师
-花钱来治疗…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，当然不被攻击到是最好的。
-那些近身搏斗起来很棘手的敌人，就用远程攻击解决吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哇，得到名声了！
-恭喜～！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名声会在达成委托任务
-还有通关奈菲亚时获得。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名声提升后，就能接到更难的委托任务
-也会出现更高难度的奈菲亚。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赚取更多的名声
-早点成为优秀的冒险者吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">顺便说一下…
-如果名声太高让冒险变得很辛苦的话
-也可以找城镇的情报商去售卖自己的名声哟…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你看起来很累啊，没事吧…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想消除疲劳，最好是躺在松软的床上
-好好的睡一觉。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要是能美美的睡一觉
-可能会灵光一闪想到配方，也可能会让潜在能力得到提升
-又或是在梦中学会魔法，可谓好处多多哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果还没有做床的话
-也可以用「休息」的能力来睡眠。
-不过比在床上睡觉效果要差就是了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">休息中体力和魔力的自然恢复量也会提升
-所以战斗后也可以靠休息能力来恢复。
-但如果此时还处于过劳和饥饿状态
-可是不会进行自然恢复的哟。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，要记得好好睡觉哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喂，稍微等下啊。
-…别跑了啊喂！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈啊哈啊…咳咳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你现在位于「世界地图」哦。 
-在世界地图上的行走会移动更远的距离 
-移动时，时间流逝的也越快。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">如果携带的食物不够
-要小心路上可能会被饿死哦。
-在「世界地图」移动时异常状态也会迅速生效
-可别在中毒时移动哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没有吃的东西又不知道怎么办好时
-试着点击自己所在的场所。
-会立刻进入与当前对应地形的「野外地图」。
-如果是在森林或平原的话，应该能找到丰富的野生食材。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了，在「世界地图」上移动
-还可能会被怪物袭击。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看到你右边的那条大路了吗？
-在道路上不会那么频繁遭受袭击，会相对安全点。
-需要注意的是，离路越远就越有可能遇到难缠的敌人
-对于新人来说，沿着大路移动会是个好主意。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对了对了
-Demo就到此为止了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然也可以访问前面的城镇和各种各样的地方
-但还有很多未实装的部分
-这会透支以后的乐趣和惊喜
-所以不太推荐去哦。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">稍微逛一逛之后
-就把游戏关闭吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明天的天气是？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我今天的运势如何？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没什么</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...谁知道呢?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没什么事就别叫我啊。</t>
-  </si>
 </sst>
 </file>
 
@@ -3252,19 +2303,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3277,7 +2328,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -3305,7 +2356,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -3324,7 +2375,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -3333,90 +2384,90 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3430,13 +2481,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -3612,20 +2663,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O39"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="4" width="8.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26" style="2" customWidth="1"/>
-    <col min="6" max="6" width="62.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="62.98" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="62.98"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3651,8 +2702,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
-      <c r="B5" s="1">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
         <v>800</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3670,12 +2721,9 @@
       <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="6" ht="12.8">
-      <c r="B6" s="1">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
         <v>801</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -3693,9 +2741,7 @@
       <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>561</v>
-      </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -3704,8 +2750,8 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="12.8">
-      <c r="B7" s="1">
+    <row r="7" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
         <v>802</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -3723,12 +2769,9 @@
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="12.8">
-      <c r="B8" s="1">
+    </row>
+    <row r="8" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
         <v>804</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -3746,12 +2789,9 @@
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H8" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="12.8">
-      <c r="B9" s="1">
+    </row>
+    <row r="9" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
         <v>805</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -3769,12 +2809,9 @@
       <c r="G9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H9" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="10" ht="12.8">
-      <c r="B10" s="1">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
         <v>806</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -3792,12 +2829,10 @@
       <c r="G10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
-      <c r="B11" s="1">
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
         <v>807</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -3815,12 +2850,10 @@
       <c r="G11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="12.8">
-      <c r="B12" s="1">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
         <v>808</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -3838,12 +2871,9 @@
       <c r="G12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H12" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
-      <c r="B13" s="1">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
         <v>809</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -3861,9 +2891,7 @@
       <c r="G13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>567</v>
-      </c>
+      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -3872,8 +2900,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" ht="12.8">
-      <c r="B14" s="1">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
         <v>810</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -3891,12 +2919,9 @@
       <c r="G14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H14" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="15" ht="12.8">
-      <c r="B15" s="1">
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
         <v>811</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -3914,12 +2939,9 @@
       <c r="G15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H15" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
-      <c r="B16" s="1">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="n">
         <v>812</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -3937,12 +2959,9 @@
       <c r="G16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
-      <c r="B17" s="1">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="n">
         <v>813</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -3960,12 +2979,9 @@
       <c r="G17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H17" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
-      <c r="B18" s="1">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="n">
         <v>814</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -3983,12 +2999,9 @@
       <c r="G18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
-      <c r="B19" s="1">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="n">
         <v>815</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -4006,12 +3019,9 @@
       <c r="G19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H19" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="20" ht="12.8">
-      <c r="B20" s="1">
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="1" t="n">
         <v>816</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -4029,12 +3039,9 @@
       <c r="G20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H20" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="21" ht="12.8">
-      <c r="B21" s="1">
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="n">
         <v>818</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -4052,12 +3059,9 @@
       <c r="G21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H21" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="22" ht="12.8">
-      <c r="B22" s="1">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="n">
         <v>819</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -4075,12 +3079,9 @@
       <c r="G22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H22" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="23" ht="13.8">
-      <c r="B23" s="1">
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="n">
         <v>820</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -4098,12 +3099,9 @@
       <c r="G23" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H23" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="24" ht="13.8">
-      <c r="B24" s="1">
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="n">
         <v>822</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -4121,12 +3119,9 @@
       <c r="G24" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H24" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="25" ht="13.8">
-      <c r="B25" s="1">
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="n">
         <v>825</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -4144,12 +3139,9 @@
       <c r="G25" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H25" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="26" ht="13.8">
-      <c r="B26" s="1">
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="n">
         <v>827</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -4167,12 +3159,9 @@
       <c r="G26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H26" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
-      <c r="B27" s="1">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="n">
         <v>830</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -4190,12 +3179,9 @@
       <c r="G27" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H27" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
-      <c r="B28" s="1">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="n">
         <v>850</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -4213,13 +3199,10 @@
       <c r="G28" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H28" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
-      <c r="B29" s="4">
+      <c r="B29" s="4" t="n">
         <v>851</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -4237,9 +3220,7 @@
       <c r="G29" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>581</v>
-      </c>
+      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -4248,9 +3229,9 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
-      <c r="B30" s="4">
+      <c r="B30" s="4" t="n">
         <v>855</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -4268,9 +3249,7 @@
       <c r="G30" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>582</v>
-      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -4279,9 +3258,9 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
-      <c r="B31" s="4">
+      <c r="B31" s="4" t="n">
         <v>860</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -4299,13 +3278,11 @@
       <c r="G31" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
-      <c r="B32" s="4">
+      <c r="B32" s="4" t="n">
         <v>870</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -4323,9 +3300,7 @@
       <c r="G32" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>584</v>
-      </c>
+      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -4334,9 +3309,9 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
-      <c r="B33" s="4">
+      <c r="B33" s="4" t="n">
         <v>875</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -4354,13 +3329,11 @@
       <c r="G33" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="34" ht="12.8">
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
-      <c r="B34" s="4">
+      <c r="B34" s="4" t="n">
         <v>879</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -4378,13 +3351,11 @@
       <c r="G34" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="35" ht="12.8">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
-      <c r="B35" s="4">
+      <c r="B35" s="4" t="n">
         <v>880</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -4402,9 +3373,7 @@
       <c r="G35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>587</v>
-      </c>
+      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -4413,9 +3382,9 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
-      <c r="B36" s="4">
+      <c r="B36" s="4" t="n">
         <v>890</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -4433,9 +3402,7 @@
       <c r="G36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>588</v>
-      </c>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -4444,8 +3411,8 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" ht="12.8">
-      <c r="B37" s="1">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="1" t="n">
         <v>899</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -4463,12 +3430,9 @@
       <c r="G37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" ht="12.8">
-      <c r="B38" s="1">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="n">
         <v>950</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -4486,12 +3450,9 @@
       <c r="G38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H38" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="39" ht="12.8">
-      <c r="B39" s="1">
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="n">
         <v>990</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -4509,15 +3470,12 @@
       <c r="G39" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H39" t="s">
-        <v>590</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -4525,23 +3483,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K374"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="3" width="8.83" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
-    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
-    <col min="9" max="9" width="74.84" style="1" customWidth="1"/>
-    <col min="10" max="10" width="88.2" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="74.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="88.2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4576,13 +3534,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>327</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>118</v>
       </c>
@@ -4590,7 +3548,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>120</v>
       </c>
@@ -4598,7 +3556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="1" t="s">
         <v>121</v>
       </c>
@@ -4606,7 +3564,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="1" t="s">
         <v>123</v>
       </c>
@@ -4614,18 +3572,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>72</v>
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="4" t="s">
         <v>126</v>
       </c>
@@ -4634,8 +3592,8 @@
       </c>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" ht="22.35">
-      <c r="H14" s="1">
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="1" t="n">
         <v>233</v>
       </c>
       <c r="I14" s="4" t="s">
@@ -4644,12 +3602,10 @@
       <c r="J14" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="15" ht="23.85">
-      <c r="H15" s="1">
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="1" t="n">
         <v>234</v>
       </c>
       <c r="I15" s="4" t="s">
@@ -4658,12 +3614,10 @@
       <c r="J15" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="16" ht="35.05">
-      <c r="H16" s="1">
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="1" t="n">
         <v>235</v>
       </c>
       <c r="I16" s="4" t="s">
@@ -4672,12 +3626,10 @@
       <c r="J16" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="17" ht="23.85">
-      <c r="H17" s="1">
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="1" t="n">
         <v>236</v>
       </c>
       <c r="I17" s="4" t="s">
@@ -4686,12 +3638,10 @@
       <c r="J17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
-      <c r="H18" s="1">
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="1" t="n">
         <v>327</v>
       </c>
       <c r="I18" s="4" t="s">
@@ -4700,21 +3650,19 @@
       <c r="J18" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I19" s="4"/>
       <c r="J19" s="10"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="4"/>
       <c r="J20" s="10"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
         <v>138</v>
       </c>
@@ -4722,14 +3670,14 @@
       <c r="J21" s="4"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>110</v>
       </c>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" ht="35.05">
-      <c r="H23" s="1">
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="1" t="n">
         <v>220</v>
       </c>
       <c r="I23" s="4" t="s">
@@ -4738,12 +3686,10 @@
       <c r="J23" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="24" ht="12.8">
-      <c r="H24" s="1">
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="1" t="n">
         <v>221</v>
       </c>
       <c r="I24" s="4" t="s">
@@ -4752,12 +3698,10 @@
       <c r="J24" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" ht="12.8">
-      <c r="H25" s="1">
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="1" t="n">
         <v>222</v>
       </c>
       <c r="I25" s="4" t="s">
@@ -4766,12 +3710,10 @@
       <c r="J25" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="26" ht="35.05">
-      <c r="H26" s="1">
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
         <v>223</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -4780,12 +3722,10 @@
       <c r="J26" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="27" ht="35.05">
-      <c r="H27" s="1">
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="1" t="n">
         <v>224</v>
       </c>
       <c r="I27" s="4" t="s">
@@ -4794,12 +3734,10 @@
       <c r="J27" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="28" ht="46.25">
-      <c r="H28" s="1">
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="1" t="n">
         <v>225</v>
       </c>
       <c r="I28" s="4" t="s">
@@ -4808,12 +3746,10 @@
       <c r="J28" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="29" ht="22.35">
-      <c r="H29" s="1">
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="1" t="n">
         <v>226</v>
       </c>
       <c r="I29" s="4" t="s">
@@ -4822,12 +3758,10 @@
       <c r="J29" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="30" ht="12.8">
-      <c r="H30" s="1">
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="1" t="n">
         <v>227</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -4836,12 +3770,10 @@
       <c r="J30" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" ht="12.8">
-      <c r="H31" s="1">
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="1" t="n">
         <v>228</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -4850,12 +3782,10 @@
       <c r="J31" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="32" ht="23.85">
-      <c r="H32" s="1">
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="1" t="n">
         <v>229</v>
       </c>
       <c r="I32" s="4" t="s">
@@ -4864,11 +3794,9 @@
       <c r="J32" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
         <v>138</v>
       </c>
@@ -4876,14 +3804,14 @@
       <c r="J33" s="4"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" ht="12.8">
-      <c r="H35" s="1">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="1" t="n">
         <v>200</v>
       </c>
       <c r="I35" s="4" t="s">
@@ -4892,12 +3820,10 @@
       <c r="J35" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="36" ht="35.05">
-      <c r="H36" s="1">
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="1" t="n">
         <v>201</v>
       </c>
       <c r="I36" s="4" t="s">
@@ -4906,12 +3832,10 @@
       <c r="J36" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="37" ht="35.05">
-      <c r="H37" s="1">
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="1" t="n">
         <v>202</v>
       </c>
       <c r="I37" s="4" t="s">
@@ -4920,12 +3844,10 @@
       <c r="J37" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="38" ht="23.85">
-      <c r="H38" s="1">
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="1" t="n">
         <v>203</v>
       </c>
       <c r="I38" s="4" t="s">
@@ -4934,12 +3856,10 @@
       <c r="J38" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="39" ht="35.05">
-      <c r="H39" s="1">
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="1" t="n">
         <v>204</v>
       </c>
       <c r="I39" s="4" t="s">
@@ -4948,12 +3868,10 @@
       <c r="J39" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="40" ht="34.3">
-      <c r="H40" s="1">
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="1" t="n">
         <v>205</v>
       </c>
       <c r="I40" s="4" t="s">
@@ -4962,12 +3880,10 @@
       <c r="J40" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="41" ht="35.05">
-      <c r="H41" s="1">
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="1" t="n">
         <v>206</v>
       </c>
       <c r="I41" s="4" t="s">
@@ -4976,12 +3892,10 @@
       <c r="J41" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
-      <c r="H42" s="1">
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="1" t="n">
         <v>207</v>
       </c>
       <c r="I42" s="4" t="s">
@@ -4990,12 +3904,10 @@
       <c r="J42" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="43" ht="12.8">
-      <c r="H43" s="1">
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="1" t="n">
         <v>208</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -5004,11 +3916,9 @@
       <c r="J43" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
         <v>138</v>
       </c>
@@ -5016,20 +3926,20 @@
       <c r="J44" s="4"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
         <v>107</v>
       </c>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" ht="23.85">
-      <c r="H47" s="1">
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="1" t="n">
         <v>210</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -5038,12 +3948,10 @@
       <c r="J47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="48" ht="12.8">
-      <c r="H48" s="1">
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="1" t="n">
         <v>211</v>
       </c>
       <c r="I48" s="4" t="s">
@@ -5052,21 +3960,19 @@
       <c r="J48" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="49" ht="12.8">
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="4"/>
       <c r="J49" s="10"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
         <v>138</v>
       </c>
@@ -5074,19 +3980,19 @@
       <c r="J51" s="4"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" ht="12.8">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="12.8">
+    <row r="53" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="23.85">
-      <c r="H54" s="1">
+    <row r="54" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="1" t="n">
         <v>193</v>
       </c>
       <c r="I54" s="4" t="s">
@@ -5095,12 +4001,9 @@
       <c r="J54" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="K54" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="35.05">
-      <c r="H55" s="1">
+    </row>
+    <row r="55" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H55" s="1" t="n">
         <v>194</v>
       </c>
       <c r="I55" s="4" t="s">
@@ -5109,12 +4012,9 @@
       <c r="J55" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="K55" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="23.85">
-      <c r="H56" s="1">
+    </row>
+    <row r="56" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="1" t="n">
         <v>195</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -5123,12 +4023,9 @@
       <c r="J56" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K56" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="32.8">
-      <c r="H57" s="1">
+    </row>
+    <row r="57" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="1" t="n">
         <v>196</v>
       </c>
       <c r="I57" s="4" t="s">
@@ -5137,12 +4034,9 @@
       <c r="J57" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K57" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="35.05">
-      <c r="H58" s="1">
+    </row>
+    <row r="58" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H58" s="1" t="n">
         <v>197</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -5151,12 +4045,9 @@
       <c r="J58" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="K58" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="46.25">
-      <c r="H59" s="1">
+    </row>
+    <row r="59" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H59" s="1" t="n">
         <v>198</v>
       </c>
       <c r="I59" s="4" t="s">
@@ -5165,12 +4056,9 @@
       <c r="J59" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K59" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="23.85">
-      <c r="H60" s="1">
+    </row>
+    <row r="60" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H60" s="1" t="n">
         <v>199</v>
       </c>
       <c r="I60" s="4" t="s">
@@ -5179,38 +4067,35 @@
       <c r="J60" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="K60" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="61" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="4"/>
       <c r="J61" s="10"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="12.8">
+    <row r="62" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="12.8">
+    <row r="63" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
         <v>138</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" ht="12.8">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="12.8">
+    <row r="65" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" ht="12.8">
-      <c r="H66" s="1">
+    <row r="66" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>184</v>
       </c>
       <c r="I66" s="4" t="s">
@@ -5219,12 +4104,9 @@
       <c r="J66" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="K66" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="35.05">
-      <c r="H67" s="1">
+    </row>
+    <row r="67" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H67" s="1" t="n">
         <v>185</v>
       </c>
       <c r="I67" s="4" t="s">
@@ -5233,12 +4115,9 @@
       <c r="J67" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="K67" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="12.8">
-      <c r="H68" s="1">
+    </row>
+    <row r="68" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H68" s="1" t="n">
         <v>186</v>
       </c>
       <c r="I68" s="4" t="s">
@@ -5247,12 +4126,9 @@
       <c r="J68" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="K68" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" ht="23.85">
-      <c r="H69" s="1">
+    </row>
+    <row r="69" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="1" t="n">
         <v>187</v>
       </c>
       <c r="I69" s="4" t="s">
@@ -5261,12 +4137,9 @@
       <c r="J69" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="K69" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="12.8">
-      <c r="H70" s="1">
+    </row>
+    <row r="70" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="1" t="n">
         <v>188</v>
       </c>
       <c r="I70" s="4" t="s">
@@ -5275,12 +4148,9 @@
       <c r="J70" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K70" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" ht="46.25">
-      <c r="H71" s="1">
+    </row>
+    <row r="71" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H71" s="1" t="n">
         <v>189</v>
       </c>
       <c r="I71" s="4" t="s">
@@ -5289,12 +4159,9 @@
       <c r="J71" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="K71" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" ht="12.8">
-      <c r="H72" s="1">
+    </row>
+    <row r="72" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H72" s="1" t="n">
         <v>190</v>
       </c>
       <c r="I72" s="4" t="s">
@@ -5303,12 +4170,9 @@
       <c r="J72" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K72" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="23.85">
-      <c r="H73" s="1">
+    </row>
+    <row r="73" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H73" s="1" t="n">
         <v>191</v>
       </c>
       <c r="I73" s="4" t="s">
@@ -5317,12 +4181,9 @@
       <c r="J73" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="K73" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" ht="12.8">
-      <c r="H74" s="1">
+    </row>
+    <row r="74" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="1" t="n">
         <v>192</v>
       </c>
       <c r="I74" s="4" t="s">
@@ -5331,37 +4192,34 @@
       <c r="J74" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K74" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="75" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" s="1" customFormat="1" ht="12.8">
+    <row r="76" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
         <v>138</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" ht="12.8">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" ht="12.8">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" ht="12.8">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K79" s="1"/>
     </row>
-    <row r="80" s="1" customFormat="1" ht="12.8">
-      <c r="H80" s="1">
+    <row r="80" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="1" t="n">
         <v>174</v>
       </c>
       <c r="I80" s="4" t="s">
@@ -5370,12 +4228,9 @@
       <c r="J80" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="K80" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" ht="22.35">
-      <c r="H81" s="1">
+    </row>
+    <row r="81" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H81" s="1" t="n">
         <v>175</v>
       </c>
       <c r="I81" s="4" t="s">
@@ -5384,12 +4239,9 @@
       <c r="J81" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="K81" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" ht="32.8">
-      <c r="H82" s="1">
+    </row>
+    <row r="82" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H82" s="1" t="n">
         <v>176</v>
       </c>
       <c r="I82" s="4" t="s">
@@ -5398,12 +4250,9 @@
       <c r="J82" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="K82" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" ht="12.8">
-      <c r="H83" s="1">
+    </row>
+    <row r="83" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H83" s="1" t="n">
         <v>177</v>
       </c>
       <c r="I83" s="4" t="s">
@@ -5412,12 +4261,9 @@
       <c r="J83" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="K83" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" ht="32.8">
-      <c r="H84" s="1">
+    </row>
+    <row r="84" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H84" s="1" t="n">
         <v>178</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -5426,12 +4272,9 @@
       <c r="J84" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="K84" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" ht="22.35">
-      <c r="H85" s="1">
+    </row>
+    <row r="85" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="1" t="n">
         <v>179</v>
       </c>
       <c r="I85" s="4" t="s">
@@ -5440,27 +4283,24 @@
       <c r="J85" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="K85" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="86" ht="12.8">
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K86" s="1"/>
     </row>
-    <row r="88" ht="22.35">
+    <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" ht="12.8">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K89" s="1"/>
     </row>
-    <row r="90" ht="12.8">
-      <c r="H90" s="1">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H90" s="1" t="n">
         <v>180</v>
       </c>
       <c r="I90" s="4" t="s">
@@ -5469,12 +4309,10 @@
       <c r="J90" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="91" ht="35.05">
-      <c r="H91" s="1">
+      <c r="K90" s="1"/>
+    </row>
+    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="1" t="n">
         <v>181</v>
       </c>
       <c r="I91" s="4" t="s">
@@ -5483,12 +4321,10 @@
       <c r="J91" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="92" ht="23.85">
-      <c r="H92" s="1">
+      <c r="K91" s="1"/>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="1" t="n">
         <v>182</v>
       </c>
       <c r="I92" s="4" t="s">
@@ -5497,12 +4333,10 @@
       <c r="J92" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="93" ht="35.05">
-      <c r="H93" s="1">
+      <c r="K92" s="1"/>
+    </row>
+    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H93" s="1" t="n">
         <v>183</v>
       </c>
       <c r="I93" s="4" t="s">
@@ -5511,24 +4345,22 @@
       <c r="J93" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="94" ht="12.8">
+      <c r="K93" s="1"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K94" s="1"/>
     </row>
-    <row r="97" s="1" customFormat="1" ht="12.8">
+    <row r="97" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" ht="12.8"/>
-    <row r="99" s="1" customFormat="1" ht="12.8">
-      <c r="H99" s="1">
+    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="99" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H99" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I99" s="4" t="s">
@@ -5537,12 +4369,9 @@
       <c r="J99" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="K99" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" ht="32.8">
-      <c r="H100" s="1">
+    </row>
+    <row r="100" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H100" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I100" s="4" t="s">
@@ -5551,12 +4380,9 @@
       <c r="J100" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="K100" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" ht="32.8">
-      <c r="H101" s="1">
+    </row>
+    <row r="101" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H101" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I101" s="4" t="s">
@@ -5565,12 +4391,9 @@
       <c r="J101" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="K101" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" ht="12.8">
-      <c r="H102" s="1">
+    </row>
+    <row r="102" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H102" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I102" s="4" t="s">
@@ -5579,19 +4402,16 @@
       <c r="J102" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="K102" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="103" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="104" ht="15.65" customHeight="1">
+    <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J104" s="4"/>
     </row>
-    <row r="105" ht="12.8">
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
         <v>54</v>
       </c>
@@ -5605,7 +4425,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" ht="23.85">
+    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -5613,7 +4433,7 @@
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
-      <c r="H106" s="1">
+      <c r="H106" s="1" t="n">
         <v>169</v>
       </c>
       <c r="I106" s="12" t="s">
@@ -5622,11 +4442,9 @@
       <c r="J106" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="K106" s="4" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="107" ht="13.8">
+      <c r="K106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -5634,7 +4452,7 @@
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
-      <c r="H107" s="1">
+      <c r="H107" s="1" t="n">
         <v>170</v>
       </c>
       <c r="I107" s="12" t="s">
@@ -5643,11 +4461,9 @@
       <c r="J107" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K107" s="4" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="108" ht="23.85">
+      <c r="K107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -5655,7 +4471,7 @@
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
-      <c r="H108" s="1">
+      <c r="H108" s="1" t="n">
         <v>171</v>
       </c>
       <c r="I108" s="12" t="s">
@@ -5664,11 +4480,9 @@
       <c r="J108" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="K108" s="4" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="109" ht="46.25">
+      <c r="K108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -5676,7 +4490,7 @@
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
-      <c r="H109" s="1">
+      <c r="H109" s="1" t="n">
         <v>172</v>
       </c>
       <c r="I109" s="12" t="s">
@@ -5685,11 +4499,9 @@
       <c r="J109" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="K109" s="4" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="110" ht="35.05">
+      <c r="K109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -5697,7 +4509,7 @@
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
-      <c r="H110" s="1">
+      <c r="H110" s="1" t="n">
         <v>173</v>
       </c>
       <c r="I110" s="12" t="s">
@@ -5706,11 +4518,9 @@
       <c r="J110" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="K110" s="4" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="111" ht="13.8">
+      <c r="K110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -5722,7 +4532,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" ht="12.8">
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4"/>
       <c r="B112" s="4" t="s">
         <v>138</v>
@@ -5736,7 +4546,7 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
     </row>
-    <row r="113" s="1" customFormat="1" ht="12.8">
+    <row r="113" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
         <v>93</v>
       </c>
@@ -5750,7 +4560,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" s="1" customFormat="1" ht="13.8">
+    <row r="114" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -5758,7 +4568,7 @@
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="1">
+      <c r="H114" s="1" t="n">
         <v>155</v>
       </c>
       <c r="I114" s="13" t="s">
@@ -5767,11 +4577,9 @@
       <c r="J114" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="K114" s="4" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="115" s="1" customFormat="1" ht="23.85">
+      <c r="K114" s="4"/>
+    </row>
+    <row r="115" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -5779,7 +4587,7 @@
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
-      <c r="H115" s="1">
+      <c r="H115" s="1" t="n">
         <v>156</v>
       </c>
       <c r="I115" s="12" t="s">
@@ -5788,11 +4596,9 @@
       <c r="J115" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="K115" s="4" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="1" ht="35.05">
+      <c r="K115" s="4"/>
+    </row>
+    <row r="116" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -5800,7 +4606,7 @@
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="1">
+      <c r="H116" s="1" t="n">
         <v>157</v>
       </c>
       <c r="I116" s="12" t="s">
@@ -5809,11 +4615,9 @@
       <c r="J116" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="K116" s="4" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="1" ht="23.85">
+      <c r="K116" s="4"/>
+    </row>
+    <row r="117" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -5821,7 +4625,7 @@
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
-      <c r="H117" s="1">
+      <c r="H117" s="1" t="n">
         <v>158</v>
       </c>
       <c r="I117" s="12" t="s">
@@ -5830,11 +4634,9 @@
       <c r="J117" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="K117" s="4" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="1" ht="35.05">
+      <c r="K117" s="4"/>
+    </row>
+    <row r="118" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5842,7 +4644,7 @@
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
-      <c r="H118" s="1">
+      <c r="H118" s="1" t="n">
         <v>159</v>
       </c>
       <c r="I118" s="12" t="s">
@@ -5851,11 +4653,9 @@
       <c r="J118" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="K118" s="4" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="119" s="1" customFormat="1" ht="35.05">
+      <c r="K118" s="4"/>
+    </row>
+    <row r="119" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5863,7 +4663,7 @@
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
-      <c r="H119" s="1">
+      <c r="H119" s="1" t="n">
         <v>160</v>
       </c>
       <c r="I119" s="12" t="s">
@@ -5872,11 +4672,9 @@
       <c r="J119" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="K119" s="4" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="1" ht="12.8">
+      <c r="K119" s="4"/>
+    </row>
+    <row r="120" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
         <v>138</v>
@@ -5890,7 +4688,7 @@
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
     </row>
-    <row r="121" s="1" customFormat="1" ht="12.8">
+    <row r="121" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
         <v>96</v>
       </c>
@@ -5904,7 +4702,7 @@
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
     </row>
-    <row r="122" s="1" customFormat="1" ht="13.8">
+    <row r="122" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -5912,7 +4710,7 @@
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
-      <c r="H122" s="1">
+      <c r="H122" s="1" t="n">
         <v>161</v>
       </c>
       <c r="I122" s="13" t="s">
@@ -5921,11 +4719,9 @@
       <c r="J122" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="K122" s="4" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="123" s="1" customFormat="1" ht="23.85">
+      <c r="K122" s="4"/>
+    </row>
+    <row r="123" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -5933,7 +4729,7 @@
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
-      <c r="H123" s="1">
+      <c r="H123" s="1" t="n">
         <v>162</v>
       </c>
       <c r="I123" s="12" t="s">
@@ -5942,11 +4738,9 @@
       <c r="J123" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="K123" s="4" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="124" s="1" customFormat="1" ht="35.05">
+      <c r="K123" s="4"/>
+    </row>
+    <row r="124" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5954,7 +4748,7 @@
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
-      <c r="H124" s="1">
+      <c r="H124" s="1" t="n">
         <v>163</v>
       </c>
       <c r="I124" s="12" t="s">
@@ -5963,11 +4757,9 @@
       <c r="J124" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="K124" s="4" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="1" ht="23.85">
+      <c r="K124" s="4"/>
+    </row>
+    <row r="125" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -5975,7 +4767,7 @@
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
-      <c r="H125" s="1">
+      <c r="H125" s="1" t="n">
         <v>164</v>
       </c>
       <c r="I125" s="12" t="s">
@@ -5984,11 +4776,9 @@
       <c r="J125" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="K125" s="4" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="126" s="1" customFormat="1" ht="12.8">
+      <c r="K125" s="4"/>
+    </row>
+    <row r="126" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
         <v>138</v>
@@ -6002,7 +4792,7 @@
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" s="1" customFormat="1" ht="12.8">
+    <row r="127" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
         <v>69</v>
       </c>
@@ -6016,7 +4806,7 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
     </row>
-    <row r="128" s="1" customFormat="1" ht="13.8">
+    <row r="128" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -6024,7 +4814,7 @@
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
-      <c r="H128" s="1">
+      <c r="H128" s="1" t="n">
         <v>165</v>
       </c>
       <c r="I128" s="13" t="s">
@@ -6033,11 +4823,9 @@
       <c r="J128" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="K128" s="4" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="129" s="1" customFormat="1" ht="13.8">
+      <c r="K128" s="4"/>
+    </row>
+    <row r="129" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -6045,7 +4833,7 @@
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="1">
+      <c r="H129" s="1" t="n">
         <v>166</v>
       </c>
       <c r="I129" s="13" t="s">
@@ -6054,11 +4842,9 @@
       <c r="J129" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K129" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="130" s="1" customFormat="1" ht="23.85">
+      <c r="K129" s="4"/>
+    </row>
+    <row r="130" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -6066,7 +4852,7 @@
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
-      <c r="H130" s="1">
+      <c r="H130" s="1" t="n">
         <v>167</v>
       </c>
       <c r="I130" s="13" t="s">
@@ -6075,11 +4861,9 @@
       <c r="J130" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="K130" s="4" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="131" s="1" customFormat="1" ht="23.85">
+      <c r="K130" s="4"/>
+    </row>
+    <row r="131" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -6087,7 +4871,7 @@
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="1">
+      <c r="H131" s="1" t="n">
         <v>168</v>
       </c>
       <c r="I131" s="12" t="s">
@@ -6096,11 +4880,9 @@
       <c r="J131" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K131" s="4" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="132" s="1" customFormat="1" ht="12.8">
+      <c r="K131" s="4"/>
+    </row>
+    <row r="132" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
         <v>138</v>
@@ -6114,7 +4896,7 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" s="1" customFormat="1" ht="12.8">
+    <row r="133" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="s">
         <v>60</v>
       </c>
@@ -6128,7 +4910,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" s="1" customFormat="1" ht="23.85">
+    <row r="134" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -6136,7 +4918,7 @@
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="1">
+      <c r="H134" s="1" t="n">
         <v>116</v>
       </c>
       <c r="I134" s="12" t="s">
@@ -6145,11 +4927,9 @@
       <c r="J134" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K134" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="135" s="1" customFormat="1" ht="35.05">
+      <c r="K134" s="4"/>
+    </row>
+    <row r="135" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -6157,7 +4937,7 @@
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="1">
+      <c r="H135" s="1" t="n">
         <v>117</v>
       </c>
       <c r="I135" s="12" t="s">
@@ -6166,11 +4946,9 @@
       <c r="J135" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="K135" s="4" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="1" ht="46.25">
+      <c r="K135" s="4"/>
+    </row>
+    <row r="136" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -6178,7 +4956,7 @@
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
-      <c r="H136" s="1">
+      <c r="H136" s="1" t="n">
         <v>118</v>
       </c>
       <c r="I136" s="12" t="s">
@@ -6187,11 +4965,9 @@
       <c r="J136" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="K136" s="4" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="137" s="1" customFormat="1" ht="35.05">
+      <c r="K136" s="4"/>
+    </row>
+    <row r="137" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -6199,7 +4975,7 @@
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="1">
+      <c r="H137" s="1" t="n">
         <v>119</v>
       </c>
       <c r="I137" s="12" t="s">
@@ -6208,11 +4984,9 @@
       <c r="J137" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="K137" s="4" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="138" s="1" customFormat="1" ht="23.85">
+      <c r="K137" s="4"/>
+    </row>
+    <row r="138" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -6220,7 +4994,7 @@
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="1">
+      <c r="H138" s="1" t="n">
         <v>120</v>
       </c>
       <c r="I138" s="12" t="s">
@@ -6229,11 +5003,9 @@
       <c r="J138" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="K138" s="4" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="139" s="1" customFormat="1" ht="12.8">
+      <c r="K138" s="4"/>
+    </row>
+    <row r="139" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
         <v>138</v>
@@ -6247,7 +5019,7 @@
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
     </row>
-    <row r="140" s="1" customFormat="1" ht="12.8">
+    <row r="140" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -6259,7 +5031,7 @@
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
     </row>
-    <row r="141" s="1" customFormat="1" ht="22.35">
+    <row r="141" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="s">
         <v>63</v>
       </c>
@@ -6273,7 +5045,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" s="1" customFormat="1" ht="13.8">
+    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -6281,7 +5053,7 @@
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
-      <c r="H142" s="1">
+      <c r="H142" s="1" t="n">
         <v>121</v>
       </c>
       <c r="I142" s="12" t="s">
@@ -6290,11 +5062,9 @@
       <c r="J142" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="K142" s="4" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="143" s="1" customFormat="1" ht="35.05">
+      <c r="K142" s="4"/>
+    </row>
+    <row r="143" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -6302,7 +5072,7 @@
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
-      <c r="H143" s="1">
+      <c r="H143" s="1" t="n">
         <v>122</v>
       </c>
       <c r="I143" s="12" t="s">
@@ -6311,11 +5081,9 @@
       <c r="J143" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="K143" s="4" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="144" s="1" customFormat="1" ht="35.05">
+      <c r="K143" s="4"/>
+    </row>
+    <row r="144" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -6323,7 +5091,7 @@
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
-      <c r="H144" s="1">
+      <c r="H144" s="1" t="n">
         <v>123</v>
       </c>
       <c r="I144" s="12" t="s">
@@ -6332,11 +5100,9 @@
       <c r="J144" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="K144" s="4" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="145" s="1" customFormat="1" ht="23.85">
+      <c r="K144" s="4"/>
+    </row>
+    <row r="145" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -6344,7 +5110,7 @@
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
-      <c r="H145" s="1">
+      <c r="H145" s="1" t="n">
         <v>124</v>
       </c>
       <c r="I145" s="12" t="s">
@@ -6353,11 +5119,9 @@
       <c r="J145" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="K145" s="4" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="146" s="1" customFormat="1" ht="23.85">
+      <c r="K145" s="4"/>
+    </row>
+    <row r="146" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -6365,7 +5129,7 @@
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
-      <c r="H146" s="1">
+      <c r="H146" s="1" t="n">
         <v>125</v>
       </c>
       <c r="I146" s="12" t="s">
@@ -6374,11 +5138,9 @@
       <c r="J146" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="K146" s="4" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="147" s="1" customFormat="1" ht="22.35">
+      <c r="K146" s="4"/>
+    </row>
+    <row r="147" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -6386,7 +5148,7 @@
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
-      <c r="H147" s="1">
+      <c r="H147" s="1" t="n">
         <v>126</v>
       </c>
       <c r="I147" s="4" t="s">
@@ -6395,11 +5157,9 @@
       <c r="J147" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="K147" s="4" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="148" s="1" customFormat="1" ht="12.8">
+      <c r="K147" s="4"/>
+    </row>
+    <row r="148" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -6411,7 +5171,7 @@
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
     </row>
-    <row r="149" s="1" customFormat="1" ht="12.8">
+    <row r="149" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4"/>
       <c r="B149" s="4" t="s">
         <v>138</v>
@@ -6425,7 +5185,7 @@
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
     </row>
-    <row r="150" s="1" customFormat="1" ht="12.8">
+    <row r="150" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -6437,7 +5197,7 @@
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" s="1" customFormat="1" ht="22.35">
+    <row r="151" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
         <v>66</v>
       </c>
@@ -6451,7 +5211,7 @@
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" s="1" customFormat="1" ht="23.85">
+    <row r="152" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -6459,7 +5219,7 @@
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
-      <c r="H152" s="1">
+      <c r="H152" s="1" t="n">
         <v>127</v>
       </c>
       <c r="I152" s="12" t="s">
@@ -6468,11 +5228,9 @@
       <c r="J152" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="K152" s="4" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="153" s="1" customFormat="1" ht="23.85">
+      <c r="K152" s="4"/>
+    </row>
+    <row r="153" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4" t="s">
@@ -6482,7 +5240,7 @@
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
-      <c r="H153" s="1">
+      <c r="H153" s="1" t="n">
         <v>230</v>
       </c>
       <c r="I153" s="12" t="s">
@@ -6491,11 +5249,9 @@
       <c r="J153" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="K153" s="4" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="154" s="1" customFormat="1" ht="22.35">
+      <c r="K153" s="4"/>
+    </row>
+    <row r="154" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
@@ -6513,7 +5269,7 @@
       <c r="J154" s="10"/>
       <c r="K154" s="4"/>
     </row>
-    <row r="155" s="1" customFormat="1" ht="23.85">
+    <row r="155" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
@@ -6523,7 +5279,7 @@
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
-      <c r="H155" s="1">
+      <c r="H155" s="1" t="n">
         <v>231</v>
       </c>
       <c r="I155" s="12" t="s">
@@ -6532,11 +5288,9 @@
       <c r="J155" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="K155" s="4" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="156" s="1" customFormat="1" ht="22.35">
+      <c r="K155" s="4"/>
+    </row>
+    <row r="156" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4" t="s">
@@ -6546,7 +5300,7 @@
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
-      <c r="H156" s="1">
+      <c r="H156" s="1" t="n">
         <v>232</v>
       </c>
       <c r="I156" s="12" t="s">
@@ -6555,11 +5309,9 @@
       <c r="J156" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="K156" s="4" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="157" s="1" customFormat="1" ht="23.85">
+      <c r="K156" s="4"/>
+    </row>
+    <row r="157" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -6567,7 +5319,7 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="H157" s="1">
+      <c r="H157" s="1" t="n">
         <v>128</v>
       </c>
       <c r="I157" s="14" t="s">
@@ -6576,11 +5328,9 @@
       <c r="J157" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="K157" s="4" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="158" s="1" customFormat="1" ht="12.8">
+      <c r="K157" s="4"/>
+    </row>
+    <row r="158" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -6592,7 +5342,7 @@
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
     </row>
-    <row r="159" s="1" customFormat="1" ht="12.8">
+    <row r="159" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
         <v>138</v>
@@ -6606,7 +5356,7 @@
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
     </row>
-    <row r="160" s="1" customFormat="1" ht="12.8">
+    <row r="160" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -6618,7 +5368,7 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="1" ht="12.8">
+    <row r="161" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
         <v>99</v>
       </c>
@@ -6632,7 +5382,7 @@
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
     </row>
-    <row r="162" s="1" customFormat="1" ht="13.8">
+    <row r="162" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6640,7 +5390,7 @@
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
-      <c r="H162" s="1">
+      <c r="H162" s="1" t="n">
         <v>129</v>
       </c>
       <c r="I162" s="12" t="s">
@@ -6649,11 +5399,9 @@
       <c r="J162" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="K162" s="4" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="163" s="1" customFormat="1" ht="23.85">
+      <c r="K162" s="4"/>
+    </row>
+    <row r="163" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -6661,7 +5409,7 @@
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
-      <c r="H163" s="1">
+      <c r="H163" s="1" t="n">
         <v>130</v>
       </c>
       <c r="I163" s="12" t="s">
@@ -6670,11 +5418,9 @@
       <c r="J163" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="K163" s="4" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="164" s="1" customFormat="1" ht="23.85">
+      <c r="K163" s="4"/>
+    </row>
+    <row r="164" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -6682,7 +5428,7 @@
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
-      <c r="H164" s="1">
+      <c r="H164" s="1" t="n">
         <v>131</v>
       </c>
       <c r="I164" s="12" t="s">
@@ -6691,11 +5437,9 @@
       <c r="J164" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="K164" s="4" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="1" ht="23.85">
+      <c r="K164" s="4"/>
+    </row>
+    <row r="165" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -6703,7 +5447,7 @@
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
-      <c r="H165" s="1">
+      <c r="H165" s="1" t="n">
         <v>132</v>
       </c>
       <c r="I165" s="12" t="s">
@@ -6712,11 +5456,9 @@
       <c r="J165" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K165" s="4" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="166" s="1" customFormat="1" ht="35.05">
+      <c r="K165" s="4"/>
+    </row>
+    <row r="166" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -6724,7 +5466,7 @@
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
-      <c r="H166" s="1">
+      <c r="H166" s="1" t="n">
         <v>133</v>
       </c>
       <c r="I166" s="12" t="s">
@@ -6733,11 +5475,9 @@
       <c r="J166" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="K166" s="4" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="167" s="1" customFormat="1" ht="35.05">
+      <c r="K166" s="4"/>
+    </row>
+    <row r="167" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -6745,7 +5485,7 @@
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
-      <c r="H167" s="1">
+      <c r="H167" s="1" t="n">
         <v>134</v>
       </c>
       <c r="I167" s="12" t="s">
@@ -6754,11 +5494,9 @@
       <c r="J167" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="K167" s="4" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="168" s="1" customFormat="1" ht="23.85">
+      <c r="K167" s="4"/>
+    </row>
+    <row r="168" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -6766,7 +5504,7 @@
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
-      <c r="H168" s="1">
+      <c r="H168" s="1" t="n">
         <v>135</v>
       </c>
       <c r="I168" s="14" t="s">
@@ -6775,11 +5513,9 @@
       <c r="J168" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="K168" s="4" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="169" s="1" customFormat="1" ht="23.85">
+      <c r="K168" s="4"/>
+    </row>
+    <row r="169" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -6787,7 +5523,7 @@
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="H169" s="1">
+      <c r="H169" s="1" t="n">
         <v>136</v>
       </c>
       <c r="I169" s="14" t="s">
@@ -6796,11 +5532,9 @@
       <c r="J169" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="K169" s="4" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="170" s="1" customFormat="1" ht="12.8">
+      <c r="K169" s="4"/>
+    </row>
+    <row r="170" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
       <c r="B170" s="4" t="s">
         <v>138</v>
@@ -6814,7 +5548,7 @@
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
     </row>
-    <row r="171" s="1" customFormat="1" ht="12.8">
+    <row r="171" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -6826,7 +5560,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="1" ht="12.8">
+    <row r="172" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="s">
         <v>18</v>
       </c>
@@ -6840,7 +5574,7 @@
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
     </row>
-    <row r="173" s="1" customFormat="1" ht="23.85">
+    <row r="173" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6848,7 +5582,7 @@
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
-      <c r="H173" s="1">
+      <c r="H173" s="1" t="n">
         <v>137</v>
       </c>
       <c r="I173" s="12" t="s">
@@ -6857,11 +5591,9 @@
       <c r="J173" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="K173" s="4" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="174" s="1" customFormat="1" ht="13.8">
+      <c r="K173" s="4"/>
+    </row>
+    <row r="174" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6869,7 +5601,7 @@
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
-      <c r="H174" s="1">
+      <c r="H174" s="1" t="n">
         <v>138</v>
       </c>
       <c r="I174" s="12" t="s">
@@ -6878,11 +5610,9 @@
       <c r="J174" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="K174" s="4" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="175" s="1" customFormat="1" ht="13.8">
+      <c r="K174" s="4"/>
+    </row>
+    <row r="175" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6890,7 +5620,7 @@
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
-      <c r="H175" s="1">
+      <c r="H175" s="1" t="n">
         <v>139</v>
       </c>
       <c r="I175" s="12" t="s">
@@ -6899,11 +5629,9 @@
       <c r="J175" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="K175" s="4" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="176" s="1" customFormat="1" ht="35.05">
+      <c r="K175" s="4"/>
+    </row>
+    <row r="176" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6911,7 +5639,7 @@
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
-      <c r="H176" s="1">
+      <c r="H176" s="1" t="n">
         <v>140</v>
       </c>
       <c r="I176" s="12" t="s">
@@ -6920,11 +5648,9 @@
       <c r="J176" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="K176" s="4" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="177" s="1" customFormat="1" ht="23.85">
+      <c r="K176" s="4"/>
+    </row>
+    <row r="177" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -6932,7 +5658,7 @@
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
-      <c r="H177" s="1">
+      <c r="H177" s="1" t="n">
         <v>141</v>
       </c>
       <c r="I177" s="12" t="s">
@@ -6941,11 +5667,9 @@
       <c r="J177" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="K177" s="4" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="178" s="1" customFormat="1" ht="35.05">
+      <c r="K177" s="4"/>
+    </row>
+    <row r="178" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -6953,7 +5677,7 @@
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="H178" s="1">
+      <c r="H178" s="1" t="n">
         <v>142</v>
       </c>
       <c r="I178" s="12" t="s">
@@ -6962,11 +5686,9 @@
       <c r="J178" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="K178" s="4" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="179" s="1" customFormat="1" ht="12.8">
+      <c r="K178" s="4"/>
+    </row>
+    <row r="179" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4"/>
       <c r="B179" s="4" t="s">
         <v>138</v>
@@ -6980,7 +5702,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="1" ht="12.8">
+    <row r="180" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
         <v>90</v>
       </c>
@@ -6994,7 +5716,7 @@
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" s="1" customFormat="1" ht="13.8">
+    <row r="181" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7002,7 +5724,7 @@
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
-      <c r="H181" s="1">
+      <c r="H181" s="1" t="n">
         <v>143</v>
       </c>
       <c r="I181" s="12" t="s">
@@ -7011,11 +5733,9 @@
       <c r="J181" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="K181" s="4" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="182" s="1" customFormat="1" ht="35.05">
+      <c r="K181" s="4"/>
+    </row>
+    <row r="182" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7023,7 +5743,7 @@
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
-      <c r="H182" s="1">
+      <c r="H182" s="1" t="n">
         <v>144</v>
       </c>
       <c r="I182" s="12" t="s">
@@ -7032,11 +5752,9 @@
       <c r="J182" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="K182" s="4" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="183" s="1" customFormat="1" ht="35.05">
+      <c r="K182" s="4"/>
+    </row>
+    <row r="183" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -7044,7 +5762,7 @@
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
-      <c r="H183" s="1">
+      <c r="H183" s="1" t="n">
         <v>145</v>
       </c>
       <c r="I183" s="12" t="s">
@@ -7053,11 +5771,9 @@
       <c r="J183" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="K183" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="184" s="1" customFormat="1" ht="35.05">
+      <c r="K183" s="4"/>
+    </row>
+    <row r="184" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7065,7 +5781,7 @@
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
-      <c r="H184" s="1">
+      <c r="H184" s="1" t="n">
         <v>146</v>
       </c>
       <c r="I184" s="12" t="s">
@@ -7074,11 +5790,9 @@
       <c r="J184" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="K184" s="4" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="185" s="1" customFormat="1" ht="46.25">
+      <c r="K184" s="4"/>
+    </row>
+    <row r="185" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -7086,7 +5800,7 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="H185" s="1">
+      <c r="H185" s="1" t="n">
         <v>147</v>
       </c>
       <c r="I185" s="12" t="s">
@@ -7095,11 +5809,9 @@
       <c r="J185" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="K185" s="4" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="186" s="1" customFormat="1" ht="12.8">
+      <c r="K185" s="4"/>
+    </row>
+    <row r="186" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -7111,7 +5823,7 @@
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
     </row>
-    <row r="187" s="1" customFormat="1" ht="12.8">
+    <row r="187" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -7123,7 +5835,7 @@
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
     </row>
-    <row r="188" s="1" customFormat="1" ht="12.8">
+    <row r="188" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="4"/>
       <c r="B188" s="4" t="s">
         <v>138</v>
@@ -7137,7 +5849,7 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" s="1" customFormat="1" ht="12.8">
+    <row r="189" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="s">
         <v>39</v>
       </c>
@@ -7151,7 +5863,7 @@
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
     </row>
-    <row r="190" s="1" customFormat="1" ht="12.8">
+    <row r="190" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7159,7 +5871,7 @@
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
-      <c r="H190" s="1">
+      <c r="H190" s="1" t="n">
         <v>148</v>
       </c>
       <c r="I190" s="4" t="s">
@@ -7168,11 +5880,9 @@
       <c r="J190" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="K190" s="4" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="191" s="1" customFormat="1" ht="12.8">
+      <c r="K190" s="4"/>
+    </row>
+    <row r="191" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7180,7 +5890,7 @@
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
-      <c r="H191" s="1">
+      <c r="H191" s="1" t="n">
         <v>149</v>
       </c>
       <c r="I191" s="4" t="s">
@@ -7189,11 +5899,9 @@
       <c r="J191" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="K191" s="4" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="192" s="1" customFormat="1" ht="32.8">
+      <c r="K191" s="4"/>
+    </row>
+    <row r="192" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7201,7 +5909,7 @@
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
-      <c r="H192" s="1">
+      <c r="H192" s="1" t="n">
         <v>150</v>
       </c>
       <c r="I192" s="4" t="s">
@@ -7210,11 +5918,9 @@
       <c r="J192" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="K192" s="4" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="193" s="1" customFormat="1" ht="32.8">
+      <c r="K192" s="4"/>
+    </row>
+    <row r="193" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7222,7 +5928,7 @@
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
-      <c r="H193" s="1">
+      <c r="H193" s="1" t="n">
         <v>151</v>
       </c>
       <c r="I193" s="4" t="s">
@@ -7231,11 +5937,9 @@
       <c r="J193" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="K193" s="4" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="194" s="1" customFormat="1" ht="43.25">
+      <c r="K193" s="4"/>
+    </row>
+    <row r="194" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7243,7 +5947,7 @@
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
-      <c r="H194" s="1">
+      <c r="H194" s="1" t="n">
         <v>152</v>
       </c>
       <c r="I194" s="4" t="s">
@@ -7252,11 +5956,9 @@
       <c r="J194" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="K194" s="4" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="195" s="1" customFormat="1" ht="32.8">
+      <c r="K194" s="4"/>
+    </row>
+    <row r="195" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7264,7 +5966,7 @@
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
-      <c r="H195" s="1">
+      <c r="H195" s="1" t="n">
         <v>153</v>
       </c>
       <c r="I195" s="4" t="s">
@@ -7273,11 +5975,9 @@
       <c r="J195" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="K195" s="4" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="196" ht="32.8">
+      <c r="K195" s="4"/>
+    </row>
+    <row r="196" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -7285,7 +5985,7 @@
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="H196" s="1">
+      <c r="H196" s="1" t="n">
         <v>154</v>
       </c>
       <c r="I196" s="4" t="s">
@@ -7294,11 +5994,9 @@
       <c r="J196" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K196" s="4" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="197" s="1" customFormat="1" ht="12.8">
+      <c r="K196" s="4"/>
+    </row>
+    <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="4"/>
       <c r="B197" s="4" t="s">
         <v>138</v>
@@ -7312,17 +6010,17 @@
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
     </row>
-    <row r="198" s="1" customFormat="1" ht="12.8">
+    <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B198" s="4"/>
     </row>
-    <row r="199" s="1" customFormat="1" ht="12.8">
+    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="200" s="1" customFormat="1" ht="12.8"/>
-    <row r="201" s="1" customFormat="1" ht="12.8">
-      <c r="H201" s="1">
+    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="201" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H201" s="1" t="n">
         <v>105</v>
       </c>
       <c r="I201" s="4" t="s">
@@ -7331,12 +6029,9 @@
       <c r="J201" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="K201" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="202" s="1" customFormat="1" ht="22.35">
-      <c r="H202" s="1">
+    </row>
+    <row r="202" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H202" s="1" t="n">
         <v>106</v>
       </c>
       <c r="I202" s="4" t="s">
@@ -7345,12 +6040,9 @@
       <c r="J202" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="K202" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="203" s="1" customFormat="1" ht="32.8">
-      <c r="H203" s="1">
+    </row>
+    <row r="203" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H203" s="1" t="n">
         <v>107</v>
       </c>
       <c r="I203" s="4" t="s">
@@ -7359,12 +6051,9 @@
       <c r="J203" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="K203" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="204" s="1" customFormat="1" ht="32.8">
-      <c r="H204" s="1">
+    </row>
+    <row r="204" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H204" s="1" t="n">
         <v>108</v>
       </c>
       <c r="I204" s="4" t="s">
@@ -7373,12 +6062,9 @@
       <c r="J204" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="K204" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="205" s="1" customFormat="1" ht="22.35">
-      <c r="H205" s="1">
+    </row>
+    <row r="205" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H205" s="1" t="n">
         <v>109</v>
       </c>
       <c r="I205" s="4" t="s">
@@ -7387,23 +6073,20 @@
       <c r="J205" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="K205" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="206" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B206" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="207" s="1" customFormat="1" ht="12.8">
+    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="208" s="1" customFormat="1" ht="12.8"/>
-    <row r="209" s="1" customFormat="1" ht="12.8">
-      <c r="H209" s="1">
+    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="209" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H209" s="1" t="n">
         <v>110</v>
       </c>
       <c r="I209" s="4" t="s">
@@ -7412,12 +6095,9 @@
       <c r="J209" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="K209" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="210" s="1" customFormat="1" ht="23.85">
-      <c r="H210" s="1">
+    </row>
+    <row r="210" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H210" s="1" t="n">
         <v>111</v>
       </c>
       <c r="I210" s="4" t="s">
@@ -7426,12 +6106,9 @@
       <c r="J210" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="K210" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="211" s="1" customFormat="1" ht="23.85">
-      <c r="H211" s="1">
+    </row>
+    <row r="211" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H211" s="1" t="n">
         <v>112</v>
       </c>
       <c r="I211" s="4" t="s">
@@ -7440,12 +6117,9 @@
       <c r="J211" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="K211" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="212" s="1" customFormat="1" ht="46.25">
-      <c r="H212" s="1">
+    </row>
+    <row r="212" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H212" s="1" t="n">
         <v>113</v>
       </c>
       <c r="I212" s="4" t="s">
@@ -7454,12 +6128,9 @@
       <c r="J212" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="K212" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="213" s="1" customFormat="1" ht="23.85">
-      <c r="H213" s="1">
+    </row>
+    <row r="213" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H213" s="1" t="n">
         <v>114</v>
       </c>
       <c r="I213" s="4" t="s">
@@ -7468,12 +6139,9 @@
       <c r="J213" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="K213" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="214" ht="23.85">
-      <c r="H214" s="1">
+    </row>
+    <row r="214" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H214" s="1" t="n">
         <v>115</v>
       </c>
       <c r="I214" s="4" t="s">
@@ -7482,26 +6150,24 @@
       <c r="J214" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="K214" s="1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="215" s="1" customFormat="1" ht="12.8">
+      <c r="K214" s="1"/>
+    </row>
+    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B215" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="216" s="1" customFormat="1" ht="12.8">
+    <row r="216" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B216" s="4"/>
     </row>
-    <row r="217" s="1" customFormat="1" ht="22.35">
+    <row r="217" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="218" s="1" customFormat="1" ht="12.8"/>
-    <row r="219" s="1" customFormat="1" ht="12.8">
-      <c r="H219" s="1">
+    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H219" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I219" s="4" t="s">
@@ -7510,12 +6176,9 @@
       <c r="J219" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="K219" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="220" s="1" customFormat="1" ht="32.8">
-      <c r="H220" s="1">
+    </row>
+    <row r="220" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H220" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I220" s="4" t="s">
@@ -7524,12 +6187,9 @@
       <c r="J220" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="K220" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="221" s="1" customFormat="1" ht="22.35">
-      <c r="H221" s="1">
+    </row>
+    <row r="221" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H221" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I221" s="4" t="s">
@@ -7538,12 +6198,9 @@
       <c r="J221" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="K221" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="222" s="1" customFormat="1" ht="64.15">
-      <c r="H222" s="1">
+    </row>
+    <row r="222" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H222" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I222" s="4" t="s">
@@ -7552,12 +6209,9 @@
       <c r="J222" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="K222" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="223" s="1" customFormat="1" ht="32.8">
-      <c r="H223" s="1">
+    </row>
+    <row r="223" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H223" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I223" s="4" t="s">
@@ -7566,12 +6220,9 @@
       <c r="J223" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="K223" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="224" s="1" customFormat="1" ht="12.8">
-      <c r="H224" s="1">
+    </row>
+    <row r="224" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H224" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I224" s="4" t="s">
@@ -7580,12 +6231,9 @@
       <c r="J224" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="K224" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="225" s="1" customFormat="1" ht="12.8">
-      <c r="H225" s="1">
+    </row>
+    <row r="225" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H225" s="1" t="n">
         <v>32</v>
       </c>
       <c r="I225" s="4" t="s">
@@ -7594,12 +6242,9 @@
       <c r="J225" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K225" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="226" s="1" customFormat="1" ht="22.35">
-      <c r="H226" s="1">
+    </row>
+    <row r="226" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H226" s="1" t="n">
         <v>33</v>
       </c>
       <c r="I226" s="4" t="s">
@@ -7608,12 +6253,9 @@
       <c r="J226" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="K226" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="227" ht="12.8">
-      <c r="H227" s="1">
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H227" s="1" t="n">
         <v>34</v>
       </c>
       <c r="I227" s="4" t="s">
@@ -7622,26 +6264,24 @@
       <c r="J227" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="K227" s="1" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="228" ht="12.8">
+      <c r="K227" s="1"/>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K228" s="1"/>
     </row>
-    <row r="229" ht="15.65" customHeight="1"/>
-    <row r="230" ht="15.65" customHeight="1"/>
-    <row r="231" ht="15.65" customHeight="1"/>
-    <row r="232" ht="12.8">
+    <row r="229" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="234" ht="12.8">
-      <c r="H234" s="1">
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H234" s="1" t="n">
         <v>35</v>
       </c>
       <c r="I234" s="4" t="s">
@@ -7650,18 +6290,15 @@
       <c r="J234" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="K234" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="235" ht="12.8">
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="1" t="s">
         <v>395</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H235" s="1">
+      <c r="H235" s="1" t="n">
         <v>36</v>
       </c>
       <c r="I235" s="4" t="s">
@@ -7670,18 +6307,15 @@
       <c r="J235" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="K235" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="236" ht="12.8">
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B236" s="1" t="s">
         <v>399</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H236" s="1">
+      <c r="H236" s="1" t="n">
         <v>37</v>
       </c>
       <c r="I236" s="4" t="s">
@@ -7690,23 +6324,20 @@
       <c r="J236" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="K236" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="237" ht="12.8">
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" ht="12.8">
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
         <v>395</v>
       </c>
       <c r="I238" s="4"/>
       <c r="J238" s="10"/>
     </row>
-    <row r="239" ht="22.35">
-      <c r="H239" s="1">
+    <row r="239" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H239" s="1" t="n">
         <v>38</v>
       </c>
       <c r="I239" s="4" t="s">
@@ -7715,12 +6346,9 @@
       <c r="J239" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="K239" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="240" s="1" customFormat="1" ht="22.35">
-      <c r="H240" s="1">
+    </row>
+    <row r="240" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H240" s="1" t="n">
         <v>39</v>
       </c>
       <c r="I240" s="4" t="s">
@@ -7729,12 +6357,9 @@
       <c r="J240" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="K240" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="241" ht="22.35">
-      <c r="H241" s="1">
+    </row>
+    <row r="241" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H241" s="1" t="n">
         <v>40</v>
       </c>
       <c r="I241" s="4" t="s">
@@ -7743,12 +6368,9 @@
       <c r="J241" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="K241" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="242" ht="22.35">
-      <c r="H242" s="1">
+    </row>
+    <row r="242" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H242" s="1" t="n">
         <v>41</v>
       </c>
       <c r="I242" s="4" t="s">
@@ -7757,12 +6379,10 @@
       <c r="J242" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K242" s="1" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="243" ht="22.35">
-      <c r="H243" s="1">
+      <c r="K242" s="1"/>
+    </row>
+    <row r="243" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H243" s="1" t="n">
         <v>42</v>
       </c>
       <c r="I243" s="4" t="s">
@@ -7771,12 +6391,9 @@
       <c r="J243" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="K243" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="244" ht="32.8">
-      <c r="H244" s="1">
+    </row>
+    <row r="244" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H244" s="1" t="n">
         <v>43</v>
       </c>
       <c r="I244" s="4" t="s">
@@ -7785,24 +6402,21 @@
       <c r="J244" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="K244" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="245" ht="12.8">
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B245" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J245" s="4"/>
     </row>
-    <row r="246" ht="12.8">
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
         <v>399</v>
       </c>
       <c r="J246" s="4"/>
     </row>
-    <row r="247" ht="12.8">
-      <c r="H247" s="1">
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H247" s="1" t="n">
         <v>44</v>
       </c>
       <c r="I247" s="4" t="s">
@@ -7811,23 +6425,20 @@
       <c r="J247" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="K247" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="248" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B248" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="249" s="1" customFormat="1" ht="12.8"/>
-    <row r="250" s="1" customFormat="1" ht="12.8">
+    <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="250" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="251" s="1" customFormat="1" ht="23.85">
-      <c r="H251" s="1">
+    <row r="251" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H251" s="1" t="n">
         <v>93</v>
       </c>
       <c r="I251" s="4" t="s">
@@ -7836,12 +6447,9 @@
       <c r="J251" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="K251" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="252" s="1" customFormat="1" ht="32.8">
-      <c r="H252" s="1">
+    </row>
+    <row r="252" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H252" s="1" t="n">
         <v>94</v>
       </c>
       <c r="I252" s="4" t="s">
@@ -7850,12 +6458,9 @@
       <c r="J252" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="K252" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="253" s="1" customFormat="1" ht="32.8">
-      <c r="H253" s="1">
+    </row>
+    <row r="253" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H253" s="1" t="n">
         <v>95</v>
       </c>
       <c r="I253" s="4" t="s">
@@ -7864,12 +6469,9 @@
       <c r="J253" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="K253" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="254" s="1" customFormat="1" ht="32.8">
-      <c r="H254" s="1">
+    </row>
+    <row r="254" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H254" s="1" t="n">
         <v>96</v>
       </c>
       <c r="I254" s="4" t="s">
@@ -7878,12 +6480,9 @@
       <c r="J254" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="K254" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="255" s="1" customFormat="1" ht="12.8">
-      <c r="H255" s="1">
+    </row>
+    <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H255" s="1" t="n">
         <v>97</v>
       </c>
       <c r="I255" s="4" t="s">
@@ -7892,12 +6491,9 @@
       <c r="J255" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K255" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="256" s="1" customFormat="1" ht="12.8">
-      <c r="H256" s="1">
+    </row>
+    <row r="256" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H256" s="1" t="n">
         <v>98</v>
       </c>
       <c r="I256" s="4" t="s">
@@ -7906,12 +6502,9 @@
       <c r="J256" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="K256" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="257" s="1" customFormat="1" ht="32.8">
-      <c r="H257" s="1">
+    </row>
+    <row r="257" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H257" s="1" t="n">
         <v>99</v>
       </c>
       <c r="I257" s="4" t="s">
@@ -7920,26 +6513,23 @@
       <c r="J257" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="K257" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="258" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I258" s="4"/>
       <c r="J258" s="4"/>
     </row>
-    <row r="259" s="1" customFormat="1" ht="12.8">
+    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B259" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="260" s="1" customFormat="1" ht="12.8">
+    <row r="260" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="261" s="1" customFormat="1" ht="23.85">
-      <c r="H261" s="1">
+    <row r="261" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H261" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I261" s="4" t="s">
@@ -7948,12 +6538,9 @@
       <c r="J261" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="K261" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="262" s="1" customFormat="1" ht="43.25">
-      <c r="H262" s="1">
+    </row>
+    <row r="262" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H262" s="1" t="n">
         <v>101</v>
       </c>
       <c r="I262" s="4" t="s">
@@ -7962,12 +6549,9 @@
       <c r="J262" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="K262" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="263" s="1" customFormat="1" ht="32.8">
-      <c r="H263" s="1">
+    </row>
+    <row r="263" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H263" s="1" t="n">
         <v>102</v>
       </c>
       <c r="I263" s="4" t="s">
@@ -7976,12 +6560,9 @@
       <c r="J263" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="K263" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="264" s="1" customFormat="1" ht="22.35">
-      <c r="H264" s="1">
+    </row>
+    <row r="264" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H264" s="1" t="n">
         <v>103</v>
       </c>
       <c r="I264" s="4" t="s">
@@ -7990,12 +6571,9 @@
       <c r="J264" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="K264" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="265" s="1" customFormat="1" ht="12.8">
-      <c r="H265" s="1">
+    </row>
+    <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H265" s="1" t="n">
         <v>104</v>
       </c>
       <c r="I265" s="4" t="s">
@@ -8004,29 +6582,26 @@
       <c r="J265" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="K265" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="266" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="266" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I266" s="4"/>
       <c r="J266" s="4"/>
     </row>
-    <row r="267" s="1" customFormat="1" ht="12.8">
+    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B267" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="268" s="1" customFormat="1" ht="12.8">
+    <row r="268" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B268" s="4"/>
     </row>
-    <row r="269" s="1" customFormat="1" ht="12.8">
+    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="270" s="1" customFormat="1" ht="12.8">
-      <c r="H270" s="1">
+    <row r="270" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H270" s="1" t="n">
         <v>79</v>
       </c>
       <c r="I270" s="4" t="s">
@@ -8035,12 +6610,9 @@
       <c r="J270" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K270" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="271" s="1" customFormat="1" ht="12.8">
-      <c r="H271" s="1">
+    </row>
+    <row r="271" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H271" s="1" t="n">
         <v>80</v>
       </c>
       <c r="I271" s="4" t="s">
@@ -8049,12 +6621,9 @@
       <c r="J271" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="K271" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="272" s="1" customFormat="1" ht="43.25">
-      <c r="H272" s="1">
+    </row>
+    <row r="272" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H272" s="1" t="n">
         <v>81</v>
       </c>
       <c r="I272" s="4" t="s">
@@ -8063,12 +6632,9 @@
       <c r="J272" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="K272" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="273" s="1" customFormat="1" ht="22.35">
-      <c r="H273" s="1">
+    </row>
+    <row r="273" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H273" s="1" t="n">
         <v>82</v>
       </c>
       <c r="I273" s="4" t="s">
@@ -8077,12 +6643,9 @@
       <c r="J273" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="K273" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="274" s="1" customFormat="1" ht="43.25">
-      <c r="H274" s="1">
+    </row>
+    <row r="274" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H274" s="1" t="n">
         <v>83</v>
       </c>
       <c r="I274" s="4" t="s">
@@ -8091,12 +6654,9 @@
       <c r="J274" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="K274" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="275" s="1" customFormat="1" ht="12.8">
-      <c r="H275" s="1">
+    </row>
+    <row r="275" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H275" s="1" t="n">
         <v>84</v>
       </c>
       <c r="I275" s="4" t="s">
@@ -8105,33 +6665,30 @@
       <c r="J275" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="K275" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="276" ht="12.8">
+    </row>
+    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I276" s="4"/>
       <c r="J276" s="4"/>
       <c r="K276" s="1"/>
     </row>
-    <row r="277" ht="12.8">
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K277" s="1"/>
     </row>
-    <row r="278" ht="12.8">
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B278" s="4"/>
       <c r="K278" s="1"/>
     </row>
-    <row r="279" ht="12.8">
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="4" t="s">
         <v>48</v>
       </c>
       <c r="K279" s="1"/>
     </row>
-    <row r="280" ht="12.8">
-      <c r="H280" s="1">
+    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H280" s="1" t="n">
         <v>85</v>
       </c>
       <c r="I280" s="4" t="s">
@@ -8140,12 +6697,10 @@
       <c r="J280" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K280" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="281" ht="22.35">
-      <c r="H281" s="1">
+      <c r="K280" s="1"/>
+    </row>
+    <row r="281" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H281" s="1" t="n">
         <v>86</v>
       </c>
       <c r="I281" s="4" t="s">
@@ -8154,12 +6709,10 @@
       <c r="J281" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="K281" s="1" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="282" ht="22.35">
-      <c r="H282" s="1">
+      <c r="K281" s="1"/>
+    </row>
+    <row r="282" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H282" s="1" t="n">
         <v>87</v>
       </c>
       <c r="I282" s="4" t="s">
@@ -8168,12 +6721,10 @@
       <c r="J282" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="K282" s="1" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="283" ht="43.25">
-      <c r="H283" s="1">
+      <c r="K282" s="1"/>
+    </row>
+    <row r="283" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H283" s="1" t="n">
         <v>88</v>
       </c>
       <c r="I283" s="4" t="s">
@@ -8182,12 +6733,10 @@
       <c r="J283" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="K283" s="1" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="284" ht="32.8">
-      <c r="H284" s="1">
+      <c r="K283" s="1"/>
+    </row>
+    <row r="284" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H284" s="1" t="n">
         <v>89</v>
       </c>
       <c r="I284" s="4" t="s">
@@ -8196,12 +6745,10 @@
       <c r="J284" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="K284" s="1" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="285" ht="22.35">
-      <c r="H285" s="1">
+      <c r="K284" s="1"/>
+    </row>
+    <row r="285" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H285" s="1" t="n">
         <v>90</v>
       </c>
       <c r="I285" s="4" t="s">
@@ -8210,12 +6757,10 @@
       <c r="J285" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="K285" s="1" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="286" ht="22.35">
-      <c r="H286" s="1">
+      <c r="K285" s="1"/>
+    </row>
+    <row r="286" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H286" s="1" t="n">
         <v>91</v>
       </c>
       <c r="I286" s="4" t="s">
@@ -8224,12 +6769,10 @@
       <c r="J286" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="K286" s="1" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="287" ht="12.8">
-      <c r="H287" s="1">
+      <c r="K286" s="1"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H287" s="1" t="n">
         <v>92</v>
       </c>
       <c r="I287" s="4" t="s">
@@ -8238,24 +6781,22 @@
       <c r="J287" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="K287" s="1" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="288" ht="12.8">
+      <c r="K287" s="1"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B288" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K288" s="1"/>
     </row>
-    <row r="290" ht="12.8">
+    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K290" s="1"/>
     </row>
-    <row r="291" ht="12.8">
-      <c r="H291" s="1">
+    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H291" s="1" t="n">
         <v>74</v>
       </c>
       <c r="I291" s="4" t="s">
@@ -8264,12 +6805,10 @@
       <c r="J291" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="K291" s="1" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="292" ht="32.8">
-      <c r="H292" s="1">
+      <c r="K291" s="1"/>
+    </row>
+    <row r="292" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H292" s="1" t="n">
         <v>75</v>
       </c>
       <c r="I292" s="4" t="s">
@@ -8278,12 +6817,10 @@
       <c r="J292" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="K292" s="1" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="293" ht="43.25">
-      <c r="H293" s="1">
+      <c r="K292" s="1"/>
+    </row>
+    <row r="293" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H293" s="1" t="n">
         <v>76</v>
       </c>
       <c r="I293" s="4" t="s">
@@ -8292,12 +6829,10 @@
       <c r="J293" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="K293" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="294" ht="22.35">
-      <c r="H294" s="1">
+      <c r="K293" s="1"/>
+    </row>
+    <row r="294" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H294" s="1" t="n">
         <v>77</v>
       </c>
       <c r="I294" s="4" t="s">
@@ -8306,12 +6841,10 @@
       <c r="J294" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="K294" s="1" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="295" ht="32.8">
-      <c r="H295" s="1">
+      <c r="K294" s="1"/>
+    </row>
+    <row r="295" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H295" s="1" t="n">
         <v>78</v>
       </c>
       <c r="I295" s="4" t="s">
@@ -8320,33 +6853,31 @@
       <c r="J295" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="K295" s="1" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="296" ht="12.8">
+      <c r="K295" s="1"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
       <c r="K296" s="1"/>
     </row>
-    <row r="297" ht="12.8">
+    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I297" s="4"/>
       <c r="J297" s="4"/>
       <c r="K297" s="1"/>
     </row>
-    <row r="298" s="1" customFormat="1" ht="12.8">
+    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B298" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="299" s="1" customFormat="1" ht="12.8"/>
-    <row r="300" s="1" customFormat="1" ht="12.8">
+    <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="300" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="301" s="1" customFormat="1" ht="23.85">
-      <c r="H301" s="1">
+    <row r="301" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H301" s="1" t="n">
         <v>66</v>
       </c>
       <c r="I301" s="4" t="s">
@@ -8355,12 +6886,9 @@
       <c r="J301" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="K301" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="302" s="1" customFormat="1" ht="22.35">
-      <c r="H302" s="1">
+    </row>
+    <row r="302" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H302" s="1" t="n">
         <v>67</v>
       </c>
       <c r="I302" s="4" t="s">
@@ -8369,12 +6897,9 @@
       <c r="J302" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="K302" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="303" s="1" customFormat="1" ht="12.8">
-      <c r="H303" s="1">
+    </row>
+    <row r="303" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H303" s="1" t="n">
         <v>68</v>
       </c>
       <c r="I303" s="4" t="s">
@@ -8383,12 +6908,9 @@
       <c r="J303" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="K303" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="304" s="1" customFormat="1" ht="22.35">
-      <c r="H304" s="1">
+    </row>
+    <row r="304" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H304" s="1" t="n">
         <v>69</v>
       </c>
       <c r="I304" s="4" t="s">
@@ -8397,12 +6919,9 @@
       <c r="J304" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="K304" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="305" s="1" customFormat="1" ht="32.8">
-      <c r="H305" s="1">
+    </row>
+    <row r="305" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H305" s="1" t="n">
         <v>70</v>
       </c>
       <c r="I305" s="4" t="s">
@@ -8411,12 +6930,9 @@
       <c r="J305" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="K305" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="306" s="1" customFormat="1" ht="32.8">
-      <c r="H306" s="1">
+    </row>
+    <row r="306" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H306" s="1" t="n">
         <v>71</v>
       </c>
       <c r="I306" s="4" t="s">
@@ -8425,12 +6941,9 @@
       <c r="J306" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="K306" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="307" s="1" customFormat="1" ht="22.35">
-      <c r="H307" s="1">
+    </row>
+    <row r="307" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H307" s="1" t="n">
         <v>72</v>
       </c>
       <c r="I307" s="4" t="s">
@@ -8439,12 +6952,9 @@
       <c r="J307" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="K307" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="308" s="1" customFormat="1" ht="22.35">
-      <c r="H308" s="1">
+    </row>
+    <row r="308" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H308" s="1" t="n">
         <v>73</v>
       </c>
       <c r="I308" s="4" t="s">
@@ -8453,22 +6963,19 @@
       <c r="J308" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="K308" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="309" s="1" customFormat="1" ht="12.8">
+    </row>
+    <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B309" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="310" s="1" customFormat="1" ht="12.8">
+    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="311" s="1" customFormat="1" ht="12.8">
-      <c r="H311" s="1">
+    <row r="311" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H311" s="1" t="n">
         <v>60</v>
       </c>
       <c r="I311" s="4" t="s">
@@ -8477,12 +6984,9 @@
       <c r="J311" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="K311" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="312" s="1" customFormat="1" ht="43.25">
-      <c r="H312" s="1">
+    </row>
+    <row r="312" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H312" s="1" t="n">
         <v>61</v>
       </c>
       <c r="I312" s="4" t="s">
@@ -8491,12 +6995,9 @@
       <c r="J312" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="K312" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="313" s="1" customFormat="1" ht="22.35">
-      <c r="H313" s="1">
+    </row>
+    <row r="313" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H313" s="1" t="n">
         <v>62</v>
       </c>
       <c r="I313" s="4" t="s">
@@ -8505,12 +7006,9 @@
       <c r="J313" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="K313" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="314" s="1" customFormat="1" ht="22.35">
-      <c r="H314" s="1">
+    </row>
+    <row r="314" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H314" s="1" t="n">
         <v>63</v>
       </c>
       <c r="I314" s="4" t="s">
@@ -8519,12 +7017,9 @@
       <c r="J314" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="K314" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="315" s="1" customFormat="1" ht="22.35">
-      <c r="H315" s="1">
+    </row>
+    <row r="315" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H315" s="1" t="n">
         <v>64</v>
       </c>
       <c r="I315" s="4" t="s">
@@ -8533,12 +7028,9 @@
       <c r="J315" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="K315" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="316" ht="32.8">
-      <c r="H316" s="1">
+    </row>
+    <row r="316" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H316" s="1" t="n">
         <v>65</v>
       </c>
       <c r="I316" s="4" t="s">
@@ -8547,25 +7039,23 @@
       <c r="J316" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="K316" s="1" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="317" ht="12.8">
+      <c r="K316" s="1"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B317" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K317" s="1"/>
     </row>
-    <row r="318" s="1" customFormat="1" ht="12.8"/>
-    <row r="319" s="1" customFormat="1" ht="12.8"/>
-    <row r="320" s="1" customFormat="1" ht="12.8">
+    <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="320" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="321" s="1" customFormat="1" ht="23.85">
-      <c r="H321" s="1">
+    <row r="321" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H321" s="1" t="n">
         <v>53</v>
       </c>
       <c r="I321" s="4" t="s">
@@ -8574,12 +7064,9 @@
       <c r="J321" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="K321" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="322" s="1" customFormat="1" ht="23.85">
-      <c r="H322" s="1">
+    </row>
+    <row r="322" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H322" s="1" t="n">
         <v>54</v>
       </c>
       <c r="I322" s="4" t="s">
@@ -8588,12 +7075,9 @@
       <c r="J322" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="K322" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="323" s="1" customFormat="1" ht="23.85">
-      <c r="H323" s="1">
+    </row>
+    <row r="323" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H323" s="1" t="n">
         <v>55</v>
       </c>
       <c r="I323" s="4" t="s">
@@ -8602,12 +7086,9 @@
       <c r="J323" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="K323" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="324" s="1" customFormat="1" ht="23.85">
-      <c r="H324" s="1">
+    </row>
+    <row r="324" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H324" s="1" t="n">
         <v>56</v>
       </c>
       <c r="I324" s="4" t="s">
@@ -8616,12 +7097,9 @@
       <c r="J324" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="K324" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="325" s="1" customFormat="1" ht="12.8">
-      <c r="H325" s="1">
+    </row>
+    <row r="325" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H325" s="1" t="n">
         <v>57</v>
       </c>
       <c r="I325" s="4" t="s">
@@ -8630,12 +7108,9 @@
       <c r="J325" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K325" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="326" s="1" customFormat="1" ht="35.05">
-      <c r="H326" s="1">
+    </row>
+    <row r="326" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H326" s="1" t="n">
         <v>58</v>
       </c>
       <c r="I326" s="4" t="s">
@@ -8644,12 +7119,9 @@
       <c r="J326" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="K326" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="327" ht="12.8">
-      <c r="H327" s="1">
+    </row>
+    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H327" s="1" t="n">
         <v>59</v>
       </c>
       <c r="I327" s="4" t="s">
@@ -8658,25 +7130,23 @@
       <c r="J327" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K327" s="1" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="328" ht="12.8">
+      <c r="K327" s="1"/>
+    </row>
+    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B328" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K328" s="1"/>
     </row>
-    <row r="330" s="1" customFormat="1" ht="12.8"/>
-    <row r="331" s="1" customFormat="1" ht="12.8"/>
-    <row r="332" s="1" customFormat="1" ht="12.8">
+    <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="333" s="1" customFormat="1" ht="12.8">
-      <c r="H333" s="1">
+    <row r="333" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H333" s="1" t="n">
         <v>45</v>
       </c>
       <c r="I333" s="4" t="s">
@@ -8685,12 +7155,9 @@
       <c r="J333" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="K333" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="334" s="1" customFormat="1" ht="22.35">
-      <c r="H334" s="1">
+    </row>
+    <row r="334" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H334" s="1" t="n">
         <v>46</v>
       </c>
       <c r="I334" s="4" t="s">
@@ -8699,12 +7166,9 @@
       <c r="J334" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="K334" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="335" s="1" customFormat="1" ht="32.8">
-      <c r="H335" s="1">
+    </row>
+    <row r="335" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H335" s="1" t="n">
         <v>50</v>
       </c>
       <c r="I335" s="4" t="s">
@@ -8713,12 +7177,9 @@
       <c r="J335" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="K335" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="336" s="1" customFormat="1" ht="35.05">
-      <c r="H336" s="1">
+    </row>
+    <row r="336" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H336" s="1" t="n">
         <v>47</v>
       </c>
       <c r="I336" s="4" t="s">
@@ -8727,12 +7188,9 @@
       <c r="J336" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="K336" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="337" s="1" customFormat="1" ht="43.25">
-      <c r="H337" s="1">
+    </row>
+    <row r="337" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H337" s="1" t="n">
         <v>48</v>
       </c>
       <c r="I337" s="4" t="s">
@@ -8741,12 +7199,9 @@
       <c r="J337" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="K337" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="338" ht="22.35">
-      <c r="H338" s="1">
+    </row>
+    <row r="338" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H338" s="1" t="n">
         <v>49</v>
       </c>
       <c r="I338" s="4" t="s">
@@ -8755,25 +7210,23 @@
       <c r="J338" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="K338" s="1" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="339" ht="12.8">
+      <c r="K338" s="1"/>
+    </row>
+    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B339" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K339" s="1"/>
     </row>
-    <row r="340" s="1" customFormat="1" ht="12.8"/>
-    <row r="341" s="1" customFormat="1" ht="12.8"/>
-    <row r="342" s="1" customFormat="1" ht="12.8">
+    <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="342" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="343" s="1" customFormat="1" ht="22.35">
-      <c r="H343" s="1">
+    <row r="343" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H343" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I343" s="4" t="s">
@@ -8782,12 +7235,9 @@
       <c r="J343" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="K343" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="344" s="1" customFormat="1" ht="22.35">
-      <c r="H344" s="1">
+    </row>
+    <row r="344" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H344" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I344" s="4" t="s">
@@ -8796,12 +7246,9 @@
       <c r="J344" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="K344" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="345" s="1" customFormat="1" ht="32.8">
-      <c r="H345" s="1">
+    </row>
+    <row r="345" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H345" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I345" s="4" t="s">
@@ -8810,12 +7257,9 @@
       <c r="J345" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="K345" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="346" s="1" customFormat="1" ht="43.25">
-      <c r="H346" s="1">
+    </row>
+    <row r="346" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H346" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I346" s="4" t="s">
@@ -8824,12 +7268,9 @@
       <c r="J346" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="K346" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="347" s="1" customFormat="1" ht="43.25">
-      <c r="H347" s="1">
+    </row>
+    <row r="347" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H347" s="1" t="n">
         <v>212</v>
       </c>
       <c r="I347" s="4" t="s">
@@ -8838,12 +7279,9 @@
       <c r="J347" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="K347" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="348" s="1" customFormat="1" ht="22.35">
-      <c r="H348" s="1">
+    </row>
+    <row r="348" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H348" s="1" t="n">
         <v>52</v>
       </c>
       <c r="I348" s="4" t="s">
@@ -8852,12 +7290,9 @@
       <c r="J348" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="K348" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="349" s="1" customFormat="1" ht="74.6">
-      <c r="H349" s="1">
+    </row>
+    <row r="349" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H349" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I349" s="4" t="s">
@@ -8866,12 +7301,9 @@
       <c r="J349" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="K349" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="350" ht="12.8">
-      <c r="H350" s="1">
+    </row>
+    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H350" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I350" s="4" t="s">
@@ -8880,22 +7312,20 @@
       <c r="J350" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K350" s="1" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="351" ht="12.8">
+      <c r="K350" s="1"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B351" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K351" s="1"/>
     </row>
-    <row r="353" ht="12.8">
+    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="354" ht="12.8">
+    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D354" s="1" t="s">
         <v>535</v>
       </c>
@@ -8903,8 +7333,8 @@
         <v>536</v>
       </c>
     </row>
-    <row r="355" ht="22.35">
-      <c r="H355" s="1">
+    <row r="355" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H355" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I355" s="4" t="s">
@@ -8913,12 +7343,9 @@
       <c r="J355" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="K355" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="356" ht="43.25">
-      <c r="H356" s="1">
+    </row>
+    <row r="356" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H356" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I356" s="4" t="s">
@@ -8927,15 +7354,12 @@
       <c r="J356" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="K356" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="357" ht="22.35">
+    </row>
+    <row r="357" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B357" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H357" s="1">
+      <c r="H357" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I357" s="4" t="s">
@@ -8944,15 +7368,12 @@
       <c r="J357" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="K357" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="360" ht="12.8">
+    </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="H360" s="1">
+      <c r="H360" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I360" s="1" t="s">
@@ -8961,18 +7382,15 @@
       <c r="J360" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="K360" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="361" ht="12.8">
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B361" s="1" t="s">
         <v>546</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H361" s="1">
+      <c r="H361" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I361" s="1" t="s">
@@ -8981,18 +7399,15 @@
       <c r="J361" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="K361" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="362" ht="12.8">
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B362" s="1" t="s">
         <v>546</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H362" s="1">
+      <c r="H362" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I362" s="1" t="s">
@@ -9001,18 +7416,15 @@
       <c r="J362" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="K362" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="363" ht="12.8">
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B363" s="1" t="s">
         <v>551</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H363" s="1">
+      <c r="H363" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I363" s="1" t="s">
@@ -9021,11 +7433,8 @@
       <c r="J363" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="K363" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="364" ht="12.8">
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B364" s="1" t="s">
         <v>138</v>
       </c>
@@ -9033,11 +7442,11 @@
         <v>554</v>
       </c>
     </row>
-    <row r="368" ht="12.8">
+    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="H368" s="1">
+      <c r="H368" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I368" s="1" t="s">
@@ -9046,22 +7455,19 @@
       <c r="J368" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="K368" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="369" ht="12.8">
+    </row>
+    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B369" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="372" ht="12.8">
+    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="373" ht="12.8">
-      <c r="H373" s="1">
+    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H373" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I373" s="1" t="s">
@@ -9070,23 +7476,20 @@
       <c r="J373" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="K373" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="374" ht="12.8">
+    </row>
+    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B374" s="1" t="s">
         <v>138</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_tutorial.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="index" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="nerun" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="index" sheetId="1" r:id="rId3"/>
+    <sheet name="nerun" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="799">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -2283,6 +2283,955 @@
   <si>
     <t xml:space="preserve">Don't disturb me for nothing.</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">冒险的开始</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工具的使用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">十分重要的事情</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装备的重要性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食物相关</t>
+  </si>
+  <si>
+    <t xml:space="preserve">素材硬度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">睡眠和休息</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道具特性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">世界地图</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成长和专长</t>
+  </si>
+  <si>
+    <t xml:space="preserve">善恶值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弱化和恢复</t>
+  </si>
+  <si>
+    <t xml:space="preserve">酸和装备的劣化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信仰和祈祷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死亡和惩罚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同伴与居民的复活</t>
+  </si>
+  <si>
+    <t xml:space="preserve">童年的结束</t>
+  </si>
+  <si>
+    <t xml:space="preserve">危险的水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">场地效果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以太病</t>
+  </si>
+  <si>
+    <t xml:space="preserve">旅行商人营地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">城镇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影响度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">快递箱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盟约之石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">居民的工作与兴趣</t>
+  </si>
+  <si>
+    <t xml:space="preserve">牧草和家畜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">垃圾问题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">季节</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冬季预警</t>
+  </si>
+  <si>
+    <t xml:space="preserve">世界终末之时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你感觉到了吗？
+这种诡异的气氛…有什么特别的「法则」在起作用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这一定是…没错，是「场地效果」的影响。
+虽然从前听说过，但实际体验还是第一次。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">场地效果是仅适用于现在所在地图的特殊规则。
+看到时钟右侧那个之前没见过的图标了吗？
+调查这个图标你就能知道是什么效果了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">足以改写世界法则的力量在此处生效…
+想必这背后定有相应的缘由。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…小心前进吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">叮铃！ 
+自从你开始冒险后…
+居然已经过了两千年的时间！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">您还真是长寿啊？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我？　
+…真没礼貌。我当然是永远朝气蓬勃的妖精少女啊。
+所谓妖精，就是这种生物啦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是不得了啦！
+这个世界也不是能永远持续下去的。
+毁灭的时刻，正在逐渐逼近。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">据说会有世界终末之时…
+我也不清楚具体的情况。
+但传闻如果经历了四千年，这个世界就会开裂。
+并发生各种异常现象。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遗憾的是，直到现在都没发现规避开裂的方法。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想让与你的冒险永远继续下去…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所以…
+让今后的时间推进速度变慢一点吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发现药草了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有时在野外会发现带颜色的草
+那就是药草
+吃了它们对健康有好处。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当然，药草也可以作为调味料使用
+用「石磨」把它们磨成粉
+也可以作为很多药材的原料。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">打开你的背包
+观察一下刚才摘取的药草吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能看到带着像是【止血】这样被【】围住的效果对吧？
+这种效果就被称为「道具特性」
+用它们进行制造时，成品就会继承那个特征。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">例如，用有止血效果、解毒效果的药草制作绷带…
+怎么样，豁然开朗吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草的颜色不同其效果也会不同
+请收集各种颜色的药草吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要带颜色的哦…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">叮铃！
+冬天…马上要冬天 了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">记得把田里的作物都要收获完哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已经秋天了…
+时间过的真快啊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">北提里斯毕竟是北方大陆
+就算是阳光暴晒的夏天
+也不至于热到不能出门。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是冬天会对生活有各种影响
+现在就开始做准备比较好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果有种植作物
+它们到了冬天就会枯萎
+在那之前记得要好好收获哦？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无论是湖泊还是海洋都会结冰，结冰后当然也不能钓鱼了。
+如果你以钓鱼为生，那就要多加注意了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了，到了十二月，在东边一个叫诺耶尔的村子里
+会举办有名的节日庆典。
+小摊贩会卖非常美味的点心
+绝对要去看看！要记住哦！？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">除了冬天以外，每个季节各地都会举办庆典。
+有时间的话顺便去看看吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…你会用斧头吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击游戏画面中的背包标志，会显示持有物品对吧？
+从那里找到斧头之后点击右键，就能手持它。
+在手持斧头的状态下右键点击地面上的树，就能伐木了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…咦？你已经会了？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…啊哈哈…
+别在意啦…不管是谁最初都是新手嘛。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顺带一提，画面右下角有带数字的栏位吧？
+你可以把斧子拖动到那里
+然后用鼠标滚轮切换手持工具，非常方便哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嗯，哦…你已经会用了呢！
+我也觉得你会，只是以防万一…以防万一啦？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么再见…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">话说你听说过影响力吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完成委托，进行投资
+只要对城镇有贡献，你的对城镇的「影响力」就会提升。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影响力增高之后，就可以刷新委托
+立刻让商店进货
+大家会同意你的各种不讲道理的要求.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">而·且·呢…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影响力还能当作货币使用。
+例如城镇上的秘书贩卖的「家具征收券」
+就是备受欢迎的交换品之一。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对城镇里的家具使用征收券的话，就可以将其强制没收。
+想要收集只有特定城镇才有的家具时就用它吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">快看，那里有快递箱！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">带了太多道具难以移动…
+但是，又不想把东西扔掉…
+快递箱就是为这样的冒险者解决烦恼的便利服务。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只要把道具放入这个箱子内
+道具就会自动送到你下一次到达的据点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可以寄送在城镇中购买的沉重家具
+可以用于据点间搬运物品
+熟练使用的话会很方便哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">早上好，瞌睡虫。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…别担心，我不是什么幻觉。
+我是向导诺伦，帮助你冒险就是我的职责。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好了，既然你醒过来了
+今天就送给你「冒险之书」吧。
+这是能随时回放我们对话的好东西。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，今后再会了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呀啊啊啊啊啊啊啊
+啊啊啊啊啊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不好了，装备被酸腐蚀了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装备被腐蚀之后会有-1，-2这样的减益
+性能也会降低。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在这个世界里，有只要接触就会喷一身酸液
+或患上奇怪的疾病，或破坏装备的讨厌生物
+要多加小心哦。
+…要从失败中学习经验呀冒险者！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…话说回来，腐蚀后难以使用的装备
+可以用砂轮来恢复原状
+所以不要扔掉带在身上更好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是你据点的居民一览。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在名字的右边可以看到一个提包图标吧？
+把鼠标放在那里，就能看到居民的兴趣和工作。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">居民的工作多种多样，
+其中有能提高据点的治安和肥沃度的人，
+也有能生产贵重道具的人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但要注意的是，如果不具备环境条件居民就不会工作。
+工作名称显示为黄色就代表着现在无法执行该工作。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大部分情况下，只要把工作所要用到的家具安装在据点，
+就可以进行工作了。
+例如研究工作就需要安装书架。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工作效率也会随着居民的成长提高。
+还有床的质量影响也会影响效率，所以请准备好居民数量对应的床会比较好呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是牧草呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这是一种随处可见的的牧草
+是家畜的好饲料。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">把牧草放在地上或者放在公用箱子里，
+据点中的家畜就会每天去自己吃。
+吃饱牧草的家畜就会偶尔生产蛋和奶。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了，把种子带回去，
+在你的据点也栽培一些怎么样？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是水啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你现在肯定是一脸“这不是明摆着”的表情吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…罢了，看来你只有亲自领教一下深水区的厉害才会知道恐怖。
+一旦进去马上就会窒息而死，可别怪我没警告过你啊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#pc啊
+怎么这么丢人地死掉了呀…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">究竟是怎么死的呢？
+不过没关系啦
+不论多少次我都会让你复活的！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当然死亡也是有代价的。
+死亡时身上持有的一部分金钱会在原地掉落
+能力值也会有所降低
+所以请尽量避免死亡。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是，在你到达这里最初的90天里
+并不会受到死亡的惩罚效果。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所以趁此机会去挑战各种事物
+亲身体验各种事情吧，哈哈哈。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你的同伴死掉了呢…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">放心啦，你也不必那么失落。
+只要过一周左右
+它们就会精神饱满地回来了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死去的同伴会暂时离开你的队伍
+被传送到同伴所属的据点中去。
+等过一段时间再回到据点确认同伴的情况吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果等不及的话，可以去找各个城镇的酒保对话
+虽然得花点钱，但是可以立刻召回同伴。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了，如果是从菲亚玛那里得到的宠物
+据说只要和她对话，就能随时将其复活哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我知道你一定很难过，不过还请继续加油吧…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">叮铃！
+你的冒险者新手保护期结束咯～！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦，你居然一次也没死过呢？
+了不起。来，摸摸头～摸摸头～！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在这段时间里你死了#1次…
+你到底在搞什么啊？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">就算是我都从没见过你这样的冒险者…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接下来如果死掉
+就会有惩罚了，要小心哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">讨厌，到处都是垃圾！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你就是传说中的…不收拾家的冒险者吗？
+不好好打扫垃圾的话会出大问题的哦？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">随着居民人数的增加，产生的垃圾也会增加
+所以需要采取一些对策！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最快的解决方法是实施
+「严惩乱扔垃圾法」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实施这个政策的话，基本就不会出现垃圾了。
+但是，这会让居民素质降低，之后还是要
+换成更好的垃圾应对措施。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">立起垃圾场标志，或者安装垃圾箱的话
+居民会根据居民素质的高低
+自动去倒垃圾。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">而且，如果有负责打扫的居民
+把垃圾分类的概率也会大幅增加。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">垃圾经过分解能成为宝贵的资源
+所以要有效利用才对呢！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯，探索洞穴？
+你也变得像个真正的冒险者了呢！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过，前往深处之前请先自我检查一下。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…你这身装备没问题吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洞窟里的敌人会更加的多。
+如果还有3到4个部位没有装备的话
+为了生命安全，还是重新考虑一下比较好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在据点可以制作简单的武器和防具
+也可以去城镇的商店购买。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特别是防御力(PV），是减轻敌人伤害的重要属性
+如果感觉到敌人的攻击难以抵挡
+请试着提高防御力。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太好了，你家园中的盟约之石成长了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没错，这神秘的石头是会成长的。
+随着盟约之石的成长，你的据点能获得各种恩惠。
+比如提升可容纳居民的数量，学会新的政策之类的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再有就是，成长后的盟约之石能保护家园内的道具不被那些能使用麻烦属性攻击的敌人破坏。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盟约之石会随着出货和时间经过自动成长。
+…不过需要注意的是，盟约之石等级提升之后也会引起一些更加危险的家伙的注意…也就是说可能会有更强的敌人前来袭击。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果对出现在据点里的敌人感到棘手的话。
+可以通过实施「抑制成长」的政策让盟约之石停止成长。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜你获得了专长点数！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…嗯？你不知道什么是专长？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">让速度更快，让力量更强
+这类特质就是所谓的专长
+只要使用专长点数就能获得这些特质哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在画面下面有蓝色羽毛标志的图标计量表对吧？
+在你采取行动获得相应成长后，这个计量表就会增加。
+当计量表满后就会得到专长点数。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点击这个计量表，就能查看你所能获得的专长一览表了
+你可以在里面选择你认为有用的专长。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果觉得目前没有特别需要的专长
+将专长点数存起来也是不错的选择。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顺便说一下，学习某些专长可能会需要前置条件。
+例如「美食家」专长
+必须有「烹饪」技能才能显示出来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不错，你拿到了原木呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原木老师不仅是基础的制造素材
+还是优秀的篝火燃料呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…不仅如此！
+原木老师还能经过加工
+进化为「厚板」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎…？你问该怎么加工？
+嗯，不如问问原木老师如何？
+提示是「加工设备」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…顺便说一下，石头也可以加工成「石料」
+要记住哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真棒，你制造了道具呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所有的道具都是由「素材」构成的。
+然后每种「素材」都有特质。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">例如纸质道具很轻
+铁质道具虽然很重但不易燃烧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">素材还有一种重要的特质指标，那就是「硬度」
+尤其对于镐子一类的工具
+素材的硬度会影响能挖掘到的石头和矿石的种类
+所以「硬度」十分重要。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果出现用现在的镐挖不动的石头的话
+用更硬的素材重新做镐就好了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不过…提高开采技能
+用更大力挖也是可以的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真棒，你做出制作台了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我教你一件重要的事情。
+为了成为独当一面的冒险者，这件事你一定要记住…
+那就是…「中键点击」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">背包的物品，地图上的生物和道具
+都可以通过中键点击来「干涉」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">比如踢开碍事的生物
+打开机器的开关
+混合药水
+打开同伴的背包
+平时做不到的各种行动，都可以通过中键点击来互动。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还有在安装家具和墙壁等的时候
+如果进行中键点击就可以旋转对象…
+不懂这个技巧的冒险者，可没法在这个世界活下去哟。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…怎样？中键点击…记住了吗…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了对了
+中键点击也可以用键盘的「R」键代替。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，再会了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哇…是蘑菇吗，可以给我点么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊呜啊呜。真好吃～。
+这是我最喜欢的东西。要记好哦！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蘑菇虽然很好吃，但是并不耐饥
+时间一长还会腐烂。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没错，食物一直放着就会腐烂的。
+你不知道吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吃腐烂的东西会弄坏肚子
+所以绝对不可以吃哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱼和生食特别容易腐烂。
+相对的，树木的果实和烹饪后的食物能保存很久。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果有石磨的话，也能做像干粮那样完全不腐烂的料理。
+长途旅行之前，一定要准备好足够的耐储食品
+这是冒险者的铁则哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小气！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哇，快看，有好多商人啊！
+他们在卖各种商品呢！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">简直就像是小镇的一角。
+看，那边的委托告示板
+发布了好多面向冒险者的委托。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完成委托能得到各种报酬
+要记得仔细检查委托告示板！
+要注意的是★数越多的委托就会越难。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呀，这个营地有治疗师啊。
+治疗师能治愈异常状态，那边的魔术师能够鉴定未鉴定品…虽然不是免费的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那个商队的队长…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好…好可爱！
+戴着猫的帽子。
+嗯，要不要走近了看看？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是城镇～！
+人来人往得很有活力呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">买卖道具、训练、交易、赌博、委托、恢复…
+城镇上有各种服务。
+迷路了也没关系。
+和警卫搭话就可以让他给我们带路啦。嘿嘿。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还有哦，北提里斯各个城镇的发展度不同
+所以能买卖的东西，接受的服务，训练的技能也不同。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不同城镇在委托告示板上刊登的委托倾向也不一样
+去各种各样的城镇看看也不错呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总之，先试着探索这个城镇吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你刚才干了坏事吧…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唉…你的善恶值降低了。
+在这个世界作恶就会降低善恶值
+善恶值到达0以下就会成为犯罪者。
+…成为犯罪者的话是很难活下去的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">处理委托，归还失物
+平日行善，善恶值就会提升。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…顺便说下
+在这个世界最重的罪就是滞纳税金。
+连续四个月不交税的话马上就会被通缉
+可是会被盯上性命的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">千万要注意…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">讨厌…！
+别过来，变态！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竟然堕落成了犯罪者，
+真是看错你了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…哼，善恶值降到0以下，你就会被通缉了。
+守卫会追赶你，商人们会拒绝与你交易，妹们也会对你冷眼相待
+被当作社会的敌人，度过悲惨地一生！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真是的…不过你也还有重新做人的机会啦。
+善恶值为负数时，善恶值会缓缓上升。
+停止做坏事，老实待着，总有一天风头会过去…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去流氓聚集的无法之城特尔斐
+可以补缴税金，也会有商人愿意和你交易。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没问题，我相信你
+好好赎罪后再回来吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我就说这么多了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你终于还是病倒了呢… </t>
+  </si>
+  <si>
+    <t xml:space="preserve">没什么好惊讶的。
+即使什么也不做以太也会慢慢侵蚀你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然现在的症状很轻可以无视
+但如果放任疾病发展，症状就会不断恶化最后致死。
+…所以必须找到延缓病情的方法。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘿嘿，不用那么担心。
+时间很充裕，肯定能找解决办法的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">说起来，诺耶尔南面的雪原工房里
+有位丘陵人在收集奇怪的道具。
+如果是他的话，可能会有一些线索…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咦，你信仰了神么…？
+哼哼…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告诉我嘛！你信仰了谁？
+你初次信仰的是谁？呵呵呵。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你果然是有这样的兴趣啊。
+哼～…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信仰神之后，根据信仰的虔诚度会得到各种各样的恩惠。
+信仰会随着供奉和时间的流逝而加深。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">另外，也可以对神使用一天一次的「祈祷」能力。
+根据神明的心情，可能会为你恢复体力，也可能会给你一些礼物。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过「祈祷」可以锻炼你的信仰技能
+可以试着每日进行一次祈祷看看呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还有要小心不能惹#god生气哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊…你变弱了吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咦？你还问怎么回事…
+稍微确认下自己的主能力吧？
+是不是比平时更低了？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有些敌人的攻击会削弱你的能力。
+稍微弱化点倒是没什么问题，不过积累起来的话还是会很棘手。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果有肉体复苏或者精神复苏的药水的话
+喝掉就可以恢复弱化状态。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有恢复手段的时候，可以去找镇上的治疗师
+花钱来治疗…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯，当然不被攻击到是最好的。
+那些近身搏斗起来很棘手的敌人，就用远程攻击解决吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哇，得到名声了！
+恭喜～！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名声会在达成委托任务
+还有通关奈菲亚时获得。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名声提升后，就能接到更难的委托任务
+也会出现更高难度的奈菲亚。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赚取更多的名声
+早点成为优秀的冒险者吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顺便说一下…
+如果名声太高让冒险变得很辛苦的话
+也可以找城镇的情报商去售卖自己的名声哟…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你看起来很累啊，没事吧…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想消除疲劳，最好是躺在松软的床上
+好好的睡一觉。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要是能美美的睡一觉
+可能会灵光一闪想到配方，也可能会让潜在能力得到提升
+又或是在梦中学会魔法，可谓好处多多哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果还没有做床的话
+也可以用「休息」的能力来睡眠。
+不过比在床上睡觉效果要差就是了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">休息中体力和魔力的自然恢复量也会提升
+所以战斗后也可以靠休息能力来恢复。
+但如果此时还处于过劳和饥饿状态
+可是不会进行自然恢复的哟。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，要记得好好睡觉哦！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">喂，稍微等下啊。
+…别跑了啊喂！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈啊哈啊…咳咳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你现在位于「世界地图」哦。 
+在世界地图上的行走会移动更远的距离 
+移动时，时间流逝的也越快。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">如果携带的食物不够
+要小心路上可能会被饿死哦。
+在「世界地图」移动时异常状态也会迅速生效
+可别在中毒时移动哦！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有吃的东西又不知道怎么办好时
+试着点击自己所在的场所。
+会立刻进入与当前对应地形的「野外地图」。
+如果是在森林或平原的话，应该能找到丰富的野生食材。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了，在「世界地图」上移动
+还可能会被怪物袭击。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看到你右边的那条大路了吗？
+在道路上不会那么频繁遭受袭击，会相对安全点。
+需要注意的是，离路越远就越有可能遇到难缠的敌人
+对于新人来说，沿着大路移动会是个好主意。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了对了
+Demo就到此为止了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然也可以访问前面的城镇和各种各样的地方
+但还有很多未实装的部分
+这会透支以后的乐趣和惊喜
+所以不太推荐去哦。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稍微逛一逛之后
+就把游戏关闭吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明天的天气是？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我今天的运势如何？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没什么</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...谁知道呢?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没什么事就别叫我啊。</t>
+  </si>
 </sst>
 </file>
 
@@ -2303,19 +3252,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -2328,7 +3277,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -2356,7 +3305,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -2375,7 +3324,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -2384,90 +3333,90 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2481,13 +3430,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -2663,20 +3612,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O39"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="62.98"/>
+    <col min="1" max="4" width="8.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.26" style="2" customWidth="1"/>
+    <col min="6" max="6" width="62.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="62.98" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2702,8 +3651,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+    <row r="5" ht="12.8">
+      <c r="B5" s="1">
         <v>800</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2721,9 +3670,12 @@
       <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+      <c r="H5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="6" ht="12.8">
+      <c r="B6" s="1">
         <v>801</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -2741,7 +3693,9 @@
       <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>561</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -2750,8 +3704,8 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+    <row r="7" s="1" customFormat="1" ht="12.8">
+      <c r="B7" s="1">
         <v>802</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -2769,9 +3723,12 @@
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+      <c r="H7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="12.8">
+      <c r="B8" s="1">
         <v>804</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -2789,9 +3746,12 @@
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
+      <c r="H8" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="12.8">
+      <c r="B9" s="1">
         <v>805</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -2809,9 +3769,12 @@
       <c r="G9" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="n">
+      <c r="H9" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="10" ht="12.8">
+      <c r="B10" s="1">
         <v>806</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -2829,10 +3792,12 @@
       <c r="G10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="n">
+      <c r="H10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
+      <c r="B11" s="1">
         <v>807</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -2850,10 +3815,12 @@
       <c r="G11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="n">
+      <c r="H11" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="12.8">
+      <c r="B12" s="1">
         <v>808</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2871,9 +3838,12 @@
       <c r="G12" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="n">
+      <c r="H12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
+      <c r="B13" s="1">
         <v>809</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -2891,7 +3861,9 @@
       <c r="G13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>567</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -2900,8 +3872,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="n">
+    <row r="14" ht="12.8">
+      <c r="B14" s="1">
         <v>810</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -2919,9 +3891,12 @@
       <c r="G14" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="n">
+      <c r="H14" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="15" ht="12.8">
+      <c r="B15" s="1">
         <v>811</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2939,9 +3914,12 @@
       <c r="G15" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="n">
+      <c r="H15" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
+      <c r="B16" s="1">
         <v>812</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2959,9 +3937,12 @@
       <c r="G16" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="n">
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
+      <c r="B17" s="1">
         <v>813</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2979,9 +3960,12 @@
       <c r="G17" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="n">
+      <c r="H17" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
+      <c r="B18" s="1">
         <v>814</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -2999,9 +3983,12 @@
       <c r="G18" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="n">
+      <c r="H18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
+      <c r="B19" s="1">
         <v>815</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -3019,9 +4006,12 @@
       <c r="G19" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="n">
+      <c r="H19" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="20" ht="12.8">
+      <c r="B20" s="1">
         <v>816</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -3039,9 +4029,12 @@
       <c r="G20" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="n">
+      <c r="H20" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="21" ht="12.8">
+      <c r="B21" s="1">
         <v>818</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -3059,9 +4052,12 @@
       <c r="G21" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="n">
+      <c r="H21" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="22" ht="12.8">
+      <c r="B22" s="1">
         <v>819</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -3079,9 +4075,12 @@
       <c r="G22" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="n">
+      <c r="H22" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="23" ht="13.8">
+      <c r="B23" s="1">
         <v>820</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -3099,9 +4098,12 @@
       <c r="G23" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="n">
+      <c r="H23" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="24" ht="13.8">
+      <c r="B24" s="1">
         <v>822</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -3119,9 +4121,12 @@
       <c r="G24" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="n">
+      <c r="H24" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="25" ht="13.8">
+      <c r="B25" s="1">
         <v>825</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -3139,9 +4144,12 @@
       <c r="G25" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="n">
+      <c r="H25" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="26" ht="13.8">
+      <c r="B26" s="1">
         <v>827</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -3159,9 +4167,12 @@
       <c r="G26" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="1" t="n">
+      <c r="H26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
+      <c r="B27" s="1">
         <v>830</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -3179,9 +4190,12 @@
       <c r="G27" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="n">
+      <c r="H27" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
+      <c r="B28" s="1">
         <v>850</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -3199,10 +4213,13 @@
       <c r="G28" s="8" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
       <c r="A29" s="4"/>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="4">
         <v>851</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -3220,7 +4237,9 @@
       <c r="G29" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="1"/>
+      <c r="H29" s="1" t="s">
+        <v>581</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -3229,9 +4248,9 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="A30" s="4"/>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="4">
         <v>855</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -3249,7 +4268,9 @@
       <c r="G30" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="1"/>
+      <c r="H30" s="1" t="s">
+        <v>582</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -3258,9 +4279,9 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="A31" s="4"/>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="4">
         <v>860</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -3278,11 +4299,13 @@
       <c r="G31" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
       <c r="A32" s="4"/>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="4">
         <v>870</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -3300,7 +4323,9 @@
       <c r="G32" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="H32" s="1" t="s">
+        <v>584</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -3309,9 +4334,9 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="A33" s="4"/>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="4">
         <v>875</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -3329,11 +4354,13 @@
       <c r="G33" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="34" ht="12.8">
       <c r="A34" s="4"/>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="4">
         <v>879</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -3351,11 +4378,13 @@
       <c r="G34" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="35" ht="12.8">
       <c r="A35" s="4"/>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="4">
         <v>880</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -3373,7 +4402,9 @@
       <c r="G35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H35" s="1"/>
+      <c r="H35" s="1" t="s">
+        <v>587</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -3382,9 +4413,9 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="A36" s="4"/>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="4">
         <v>890</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -3402,7 +4433,9 @@
       <c r="G36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1" t="s">
+        <v>588</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -3411,8 +4444,8 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="1" t="n">
+    <row r="37" ht="12.8">
+      <c r="B37" s="1">
         <v>899</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -3430,9 +4463,12 @@
       <c r="G37" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="n">
+      <c r="H37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
+      <c r="B38" s="1">
         <v>950</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -3450,9 +4486,12 @@
       <c r="G38" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="n">
+      <c r="H38" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="39" ht="12.8">
+      <c r="B39" s="1">
         <v>990</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -3470,12 +4509,15 @@
       <c r="G39" s="6" t="s">
         <v>112</v>
       </c>
+      <c r="H39" t="s">
+        <v>590</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -3483,23 +4525,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K374"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="6.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="74.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="88.2"/>
+    <col min="1" max="3" width="8.83" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83" style="1" customWidth="1"/>
+    <col min="7" max="8" width="6.66" style="1" customWidth="1"/>
+    <col min="9" max="9" width="74.84" style="1" customWidth="1"/>
+    <col min="10" max="10" width="88.2" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -3534,13 +4576,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>327</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>118</v>
       </c>
@@ -3548,7 +4590,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>120</v>
       </c>
@@ -3556,7 +4598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="D7" s="1" t="s">
         <v>121</v>
       </c>
@@ -3564,7 +4606,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="1" t="s">
         <v>123</v>
       </c>
@@ -3572,18 +4614,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="B9" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="A12" s="4" t="s">
         <v>72</v>
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="I13" s="4" t="s">
         <v>126</v>
       </c>
@@ -3592,8 +4634,8 @@
       </c>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="1" t="n">
+    <row r="14" ht="22.35">
+      <c r="H14" s="1">
         <v>233</v>
       </c>
       <c r="I14" s="4" t="s">
@@ -3602,10 +4644,12 @@
       <c r="J14" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="1" t="n">
+      <c r="K14" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="15" ht="23.85">
+      <c r="H15" s="1">
         <v>234</v>
       </c>
       <c r="I15" s="4" t="s">
@@ -3614,10 +4658,12 @@
       <c r="J15" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="1" t="n">
+      <c r="K15" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="16" ht="35.05">
+      <c r="H16" s="1">
         <v>235</v>
       </c>
       <c r="I16" s="4" t="s">
@@ -3626,10 +4672,12 @@
       <c r="J16" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H17" s="1" t="n">
+      <c r="K16" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="17" ht="23.85">
+      <c r="H17" s="1">
         <v>236</v>
       </c>
       <c r="I17" s="4" t="s">
@@ -3638,10 +4686,12 @@
       <c r="J17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H18" s="1" t="n">
+      <c r="K17" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
+      <c r="H18" s="1">
         <v>327</v>
       </c>
       <c r="I18" s="4" t="s">
@@ -3650,19 +4700,21 @@
       <c r="J18" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="I19" s="4"/>
       <c r="J19" s="10"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="I20" s="4"/>
       <c r="J20" s="10"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="B21" s="4" t="s">
         <v>138</v>
       </c>
@@ -3670,14 +4722,14 @@
       <c r="J21" s="4"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="A22" s="4" t="s">
         <v>110</v>
       </c>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H23" s="1" t="n">
+    <row r="23" ht="35.05">
+      <c r="H23" s="1">
         <v>220</v>
       </c>
       <c r="I23" s="4" t="s">
@@ -3686,10 +4738,12 @@
       <c r="J23" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H24" s="1" t="n">
+      <c r="K23" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="24" ht="12.8">
+      <c r="H24" s="1">
         <v>221</v>
       </c>
       <c r="I24" s="4" t="s">
@@ -3698,10 +4752,12 @@
       <c r="J24" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="1" t="n">
+      <c r="K24" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" ht="12.8">
+      <c r="H25" s="1">
         <v>222</v>
       </c>
       <c r="I25" s="4" t="s">
@@ -3710,10 +4766,12 @@
       <c r="J25" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="1" t="n">
+      <c r="K25" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="26" ht="35.05">
+      <c r="H26" s="1">
         <v>223</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -3722,10 +4780,12 @@
       <c r="J26" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="1" t="n">
+      <c r="K26" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="27" ht="35.05">
+      <c r="H27" s="1">
         <v>224</v>
       </c>
       <c r="I27" s="4" t="s">
@@ -3734,10 +4794,12 @@
       <c r="J27" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H28" s="1" t="n">
+      <c r="K27" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="28" ht="46.25">
+      <c r="H28" s="1">
         <v>225</v>
       </c>
       <c r="I28" s="4" t="s">
@@ -3746,10 +4808,12 @@
       <c r="J28" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H29" s="1" t="n">
+      <c r="K28" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" ht="22.35">
+      <c r="H29" s="1">
         <v>226</v>
       </c>
       <c r="I29" s="4" t="s">
@@ -3758,10 +4822,12 @@
       <c r="J29" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H30" s="1" t="n">
+      <c r="K29" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
+      <c r="H30" s="1">
         <v>227</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -3770,10 +4836,12 @@
       <c r="J30" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H31" s="1" t="n">
+      <c r="K30" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" ht="12.8">
+      <c r="H31" s="1">
         <v>228</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -3782,10 +4850,12 @@
       <c r="J31" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H32" s="1" t="n">
+      <c r="K31" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="32" ht="23.85">
+      <c r="H32" s="1">
         <v>229</v>
       </c>
       <c r="I32" s="4" t="s">
@@ -3794,9 +4864,11 @@
       <c r="J32" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="B33" s="4" t="s">
         <v>138</v>
       </c>
@@ -3804,14 +4876,14 @@
       <c r="J33" s="4"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H35" s="1" t="n">
+    <row r="35" ht="12.8">
+      <c r="H35" s="1">
         <v>200</v>
       </c>
       <c r="I35" s="4" t="s">
@@ -3820,10 +4892,12 @@
       <c r="J35" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H36" s="1" t="n">
+      <c r="K35" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="36" ht="35.05">
+      <c r="H36" s="1">
         <v>201</v>
       </c>
       <c r="I36" s="4" t="s">
@@ -3832,10 +4906,12 @@
       <c r="J36" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H37" s="1" t="n">
+      <c r="K36" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="37" ht="35.05">
+      <c r="H37" s="1">
         <v>202</v>
       </c>
       <c r="I37" s="4" t="s">
@@ -3844,10 +4920,12 @@
       <c r="J37" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H38" s="1" t="n">
+      <c r="K37" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="38" ht="23.85">
+      <c r="H38" s="1">
         <v>203</v>
       </c>
       <c r="I38" s="4" t="s">
@@ -3856,10 +4934,12 @@
       <c r="J38" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H39" s="1" t="n">
+      <c r="K38" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="39" ht="35.05">
+      <c r="H39" s="1">
         <v>204</v>
       </c>
       <c r="I39" s="4" t="s">
@@ -3868,10 +4948,12 @@
       <c r="J39" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H40" s="1" t="n">
+      <c r="K39" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="40" ht="34.3">
+      <c r="H40" s="1">
         <v>205</v>
       </c>
       <c r="I40" s="4" t="s">
@@ -3880,10 +4962,12 @@
       <c r="J40" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H41" s="1" t="n">
+      <c r="K40" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="41" ht="35.05">
+      <c r="H41" s="1">
         <v>206</v>
       </c>
       <c r="I41" s="4" t="s">
@@ -3892,10 +4976,12 @@
       <c r="J41" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H42" s="1" t="n">
+      <c r="K41" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
+      <c r="H42" s="1">
         <v>207</v>
       </c>
       <c r="I42" s="4" t="s">
@@ -3904,10 +4990,12 @@
       <c r="J42" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H43" s="1" t="n">
+      <c r="K42" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="43" ht="12.8">
+      <c r="H43" s="1">
         <v>208</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -3916,9 +5004,11 @@
       <c r="J43" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="K43" s="1"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" ht="12.8">
       <c r="B44" s="4" t="s">
         <v>138</v>
       </c>
@@ -3926,20 +5016,20 @@
       <c r="J44" s="4"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="B45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="A46" s="4" t="s">
         <v>107</v>
       </c>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H47" s="1" t="n">
+    <row r="47" ht="23.85">
+      <c r="H47" s="1">
         <v>210</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -3948,10 +5038,12 @@
       <c r="J47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="K47" s="1"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H48" s="1" t="n">
+      <c r="K47" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="48" ht="12.8">
+      <c r="H48" s="1">
         <v>211</v>
       </c>
       <c r="I48" s="4" t="s">
@@ -3960,19 +5052,21 @@
       <c r="J48" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K48" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="49" ht="12.8">
       <c r="I49" s="4"/>
       <c r="J49" s="10"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="B51" s="4" t="s">
         <v>138</v>
       </c>
@@ -3980,19 +5074,19 @@
       <c r="J51" s="4"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.8">
       <c r="B52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="1" customFormat="1" ht="12.8">
       <c r="A53" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H54" s="1" t="n">
+    <row r="54" s="1" customFormat="1" ht="23.85">
+      <c r="H54" s="1">
         <v>193</v>
       </c>
       <c r="I54" s="4" t="s">
@@ -4001,9 +5095,12 @@
       <c r="J54" s="10" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="55" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H55" s="1" t="n">
+      <c r="K54" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="35.05">
+      <c r="H55" s="1">
         <v>194</v>
       </c>
       <c r="I55" s="4" t="s">
@@ -4012,9 +5109,12 @@
       <c r="J55" s="10" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="56" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H56" s="1" t="n">
+      <c r="K55" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="23.85">
+      <c r="H56" s="1">
         <v>195</v>
       </c>
       <c r="I56" s="4" t="s">
@@ -4023,9 +5123,12 @@
       <c r="J56" s="10" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="57" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H57" s="1" t="n">
+      <c r="K56" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="32.8">
+      <c r="H57" s="1">
         <v>196</v>
       </c>
       <c r="I57" s="4" t="s">
@@ -4034,9 +5137,12 @@
       <c r="J57" s="10" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="58" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H58" s="1" t="n">
+      <c r="K57" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="35.05">
+      <c r="H58" s="1">
         <v>197</v>
       </c>
       <c r="I58" s="4" t="s">
@@ -4045,9 +5151,12 @@
       <c r="J58" s="10" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="59" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H59" s="1" t="n">
+      <c r="K58" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="46.25">
+      <c r="H59" s="1">
         <v>198</v>
       </c>
       <c r="I59" s="4" t="s">
@@ -4056,9 +5165,12 @@
       <c r="J59" s="10" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="60" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H60" s="1" t="n">
+      <c r="K59" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="23.85">
+      <c r="H60" s="1">
         <v>199</v>
       </c>
       <c r="I60" s="4" t="s">
@@ -4067,35 +5179,38 @@
       <c r="J60" s="10" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="61" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K60" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="12.8">
       <c r="I61" s="4"/>
       <c r="J61" s="10"/>
     </row>
-    <row r="62" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" s="1" customFormat="1" ht="12.8">
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="1" customFormat="1" ht="12.8">
       <c r="B63" s="4" t="s">
         <v>138</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.8">
       <c r="B64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="1" customFormat="1" ht="12.8">
       <c r="A65" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+    <row r="66" s="1" customFormat="1" ht="12.8">
+      <c r="H66" s="1">
         <v>184</v>
       </c>
       <c r="I66" s="4" t="s">
@@ -4104,9 +5219,12 @@
       <c r="J66" s="10" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="67" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H67" s="1" t="n">
+      <c r="K66" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="35.05">
+      <c r="H67" s="1">
         <v>185</v>
       </c>
       <c r="I67" s="4" t="s">
@@ -4115,9 +5233,12 @@
       <c r="J67" s="10" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="68" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H68" s="1" t="n">
+      <c r="K67" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="12.8">
+      <c r="H68" s="1">
         <v>186</v>
       </c>
       <c r="I68" s="4" t="s">
@@ -4126,9 +5247,12 @@
       <c r="J68" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="69" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H69" s="1" t="n">
+      <c r="K68" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="23.85">
+      <c r="H69" s="1">
         <v>187</v>
       </c>
       <c r="I69" s="4" t="s">
@@ -4137,9 +5261,12 @@
       <c r="J69" s="10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="70" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H70" s="1" t="n">
+      <c r="K69" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="12.8">
+      <c r="H70" s="1">
         <v>188</v>
       </c>
       <c r="I70" s="4" t="s">
@@ -4148,9 +5275,12 @@
       <c r="J70" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="71" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H71" s="1" t="n">
+      <c r="K70" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="46.25">
+      <c r="H71" s="1">
         <v>189</v>
       </c>
       <c r="I71" s="4" t="s">
@@ -4159,9 +5289,12 @@
       <c r="J71" s="10" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="72" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H72" s="1" t="n">
+      <c r="K71" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="12.8">
+      <c r="H72" s="1">
         <v>190</v>
       </c>
       <c r="I72" s="4" t="s">
@@ -4170,9 +5303,12 @@
       <c r="J72" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="73" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H73" s="1" t="n">
+      <c r="K72" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="23.85">
+      <c r="H73" s="1">
         <v>191</v>
       </c>
       <c r="I73" s="4" t="s">
@@ -4181,9 +5317,12 @@
       <c r="J73" s="10" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="74" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H74" s="1" t="n">
+      <c r="K73" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="12.8">
+      <c r="H74" s="1">
         <v>192</v>
       </c>
       <c r="I74" s="4" t="s">
@@ -4192,34 +5331,37 @@
       <c r="J74" s="10" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="75" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K74" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="12.8">
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" s="1" customFormat="1" ht="12.8">
       <c r="B76" s="4" t="s">
         <v>138</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="12.8">
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.8">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.8">
       <c r="K79" s="1"/>
     </row>
-    <row r="80" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="1" t="n">
+    <row r="80" s="1" customFormat="1" ht="12.8">
+      <c r="H80" s="1">
         <v>174</v>
       </c>
       <c r="I80" s="4" t="s">
@@ -4228,9 +5370,12 @@
       <c r="J80" s="10" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="81" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H81" s="1" t="n">
+      <c r="K80" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" ht="22.35">
+      <c r="H81" s="1">
         <v>175</v>
       </c>
       <c r="I81" s="4" t="s">
@@ -4239,9 +5384,12 @@
       <c r="J81" s="4" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="82" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H82" s="1" t="n">
+      <c r="K81" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="32.8">
+      <c r="H82" s="1">
         <v>176</v>
       </c>
       <c r="I82" s="4" t="s">
@@ -4250,9 +5398,12 @@
       <c r="J82" s="4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="83" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H83" s="1" t="n">
+      <c r="K82" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="12.8">
+      <c r="H83" s="1">
         <v>177</v>
       </c>
       <c r="I83" s="4" t="s">
@@ -4261,9 +5412,12 @@
       <c r="J83" s="4" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="84" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H84" s="1" t="n">
+      <c r="K83" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="32.8">
+      <c r="H84" s="1">
         <v>178</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -4272,9 +5426,12 @@
       <c r="J84" s="4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="85" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H85" s="1" t="n">
+      <c r="K84" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="22.35">
+      <c r="H85" s="1">
         <v>179</v>
       </c>
       <c r="I85" s="4" t="s">
@@ -4283,24 +5440,27 @@
       <c r="J85" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K85" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="86" ht="12.8">
       <c r="B86" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K86" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="22.35">
       <c r="A88" s="4" t="s">
         <v>87</v>
       </c>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" ht="12.8">
       <c r="K89" s="1"/>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H90" s="1" t="n">
+    <row r="90" ht="12.8">
+      <c r="H90" s="1">
         <v>180</v>
       </c>
       <c r="I90" s="4" t="s">
@@ -4309,10 +5469,12 @@
       <c r="J90" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="K90" s="1"/>
-    </row>
-    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H91" s="1" t="n">
+      <c r="K90" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="91" ht="35.05">
+      <c r="H91" s="1">
         <v>181</v>
       </c>
       <c r="I91" s="4" t="s">
@@ -4321,10 +5483,12 @@
       <c r="J91" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="K91" s="1"/>
-    </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H92" s="1" t="n">
+      <c r="K91" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="92" ht="23.85">
+      <c r="H92" s="1">
         <v>182</v>
       </c>
       <c r="I92" s="4" t="s">
@@ -4333,10 +5497,12 @@
       <c r="J92" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="K92" s="1"/>
-    </row>
-    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H93" s="1" t="n">
+      <c r="K92" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="93" ht="35.05">
+      <c r="H93" s="1">
         <v>183</v>
       </c>
       <c r="I93" s="4" t="s">
@@ -4345,22 +5511,24 @@
       <c r="J93" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="K93" s="1"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K93" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="94" ht="12.8">
       <c r="B94" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K94" s="1"/>
     </row>
-    <row r="97" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" s="1" customFormat="1" ht="12.8">
       <c r="A97" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="99" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H99" s="1" t="n">
+    <row r="98" s="1" customFormat="1" ht="12.8"/>
+    <row r="99" s="1" customFormat="1" ht="12.8">
+      <c r="H99" s="1">
         <v>22</v>
       </c>
       <c r="I99" s="4" t="s">
@@ -4369,9 +5537,12 @@
       <c r="J99" s="10" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="100" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H100" s="1" t="n">
+      <c r="K99" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" ht="32.8">
+      <c r="H100" s="1">
         <v>23</v>
       </c>
       <c r="I100" s="4" t="s">
@@ -4380,9 +5551,12 @@
       <c r="J100" s="4" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="101" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H101" s="1" t="n">
+      <c r="K100" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" ht="32.8">
+      <c r="H101" s="1">
         <v>24</v>
       </c>
       <c r="I101" s="4" t="s">
@@ -4391,9 +5565,12 @@
       <c r="J101" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="102" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H102" s="1" t="n">
+      <c r="K101" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" ht="12.8">
+      <c r="H102" s="1">
         <v>25</v>
       </c>
       <c r="I102" s="4" t="s">
@@ -4402,16 +5579,19 @@
       <c r="J102" s="10" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="103" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K102" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" ht="12.8">
       <c r="B103" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" ht="15.65" customHeight="1">
       <c r="J104" s="4"/>
     </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" ht="12.8">
       <c r="A105" s="4" t="s">
         <v>54</v>
       </c>
@@ -4425,7 +5605,7 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
     </row>
-    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" ht="23.85">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4433,7 +5613,7 @@
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
-      <c r="H106" s="1" t="n">
+      <c r="H106" s="1">
         <v>169</v>
       </c>
       <c r="I106" s="12" t="s">
@@ -4442,9 +5622,11 @@
       <c r="J106" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="K106" s="4"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K106" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="107" ht="13.8">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4452,7 +5634,7 @@
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
-      <c r="H107" s="1" t="n">
+      <c r="H107" s="1">
         <v>170</v>
       </c>
       <c r="I107" s="12" t="s">
@@ -4461,9 +5643,11 @@
       <c r="J107" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K107" s="4"/>
-    </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K107" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="108" ht="23.85">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4471,7 +5655,7 @@
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
-      <c r="H108" s="1" t="n">
+      <c r="H108" s="1">
         <v>171</v>
       </c>
       <c r="I108" s="12" t="s">
@@ -4480,9 +5664,11 @@
       <c r="J108" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="K108" s="4"/>
-    </row>
-    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K108" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="109" ht="46.25">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4490,7 +5676,7 @@
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
-      <c r="H109" s="1" t="n">
+      <c r="H109" s="1">
         <v>172</v>
       </c>
       <c r="I109" s="12" t="s">
@@ -4499,9 +5685,11 @@
       <c r="J109" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="K109" s="4"/>
-    </row>
-    <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K109" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="110" ht="35.05">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4509,7 +5697,7 @@
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
-      <c r="H110" s="1" t="n">
+      <c r="H110" s="1">
         <v>173</v>
       </c>
       <c r="I110" s="12" t="s">
@@ -4518,9 +5706,11 @@
       <c r="J110" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="K110" s="4"/>
-    </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K110" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="111" ht="13.8">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4532,7 +5722,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" ht="12.8">
       <c r="A112" s="4"/>
       <c r="B112" s="4" t="s">
         <v>138</v>
@@ -4546,7 +5736,7 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
     </row>
-    <row r="113" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" s="1" customFormat="1" ht="12.8">
       <c r="A113" s="4" t="s">
         <v>93</v>
       </c>
@@ -4560,7 +5750,7 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
     </row>
-    <row r="114" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="1" customFormat="1" ht="13.8">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4568,7 +5758,7 @@
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="1" t="n">
+      <c r="H114" s="1">
         <v>155</v>
       </c>
       <c r="I114" s="13" t="s">
@@ -4577,9 +5767,11 @@
       <c r="J114" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="K114" s="4"/>
-    </row>
-    <row r="115" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K114" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" ht="23.85">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4587,7 +5779,7 @@
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
-      <c r="H115" s="1" t="n">
+      <c r="H115" s="1">
         <v>156</v>
       </c>
       <c r="I115" s="12" t="s">
@@ -4596,9 +5788,11 @@
       <c r="J115" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="K115" s="4"/>
-    </row>
-    <row r="116" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K115" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" ht="35.05">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4606,7 +5800,7 @@
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="1" t="n">
+      <c r="H116" s="1">
         <v>157</v>
       </c>
       <c r="I116" s="12" t="s">
@@ -4615,9 +5809,11 @@
       <c r="J116" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="K116" s="4"/>
-    </row>
-    <row r="117" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K116" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" ht="23.85">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4625,7 +5821,7 @@
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
-      <c r="H117" s="1" t="n">
+      <c r="H117" s="1">
         <v>158</v>
       </c>
       <c r="I117" s="12" t="s">
@@ -4634,9 +5830,11 @@
       <c r="J117" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="K117" s="4"/>
-    </row>
-    <row r="118" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K117" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" ht="35.05">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4644,7 +5842,7 @@
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
-      <c r="H118" s="1" t="n">
+      <c r="H118" s="1">
         <v>159</v>
       </c>
       <c r="I118" s="12" t="s">
@@ -4653,9 +5851,11 @@
       <c r="J118" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="K118" s="4"/>
-    </row>
-    <row r="119" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K118" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" ht="35.05">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4663,7 +5863,7 @@
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
-      <c r="H119" s="1" t="n">
+      <c r="H119" s="1">
         <v>160</v>
       </c>
       <c r="I119" s="12" t="s">
@@ -4672,9 +5872,11 @@
       <c r="J119" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="K119" s="4"/>
-    </row>
-    <row r="120" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K119" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" ht="12.8">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
         <v>138</v>
@@ -4688,7 +5890,7 @@
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
     </row>
-    <row r="121" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" s="1" customFormat="1" ht="12.8">
       <c r="A121" s="4" t="s">
         <v>96</v>
       </c>
@@ -4702,7 +5904,7 @@
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
     </row>
-    <row r="122" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" s="1" customFormat="1" ht="13.8">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4710,7 +5912,7 @@
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
-      <c r="H122" s="1" t="n">
+      <c r="H122" s="1">
         <v>161</v>
       </c>
       <c r="I122" s="13" t="s">
@@ -4719,9 +5921,11 @@
       <c r="J122" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="K122" s="4"/>
-    </row>
-    <row r="123" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K122" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="1" ht="23.85">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4729,7 +5933,7 @@
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
-      <c r="H123" s="1" t="n">
+      <c r="H123" s="1">
         <v>162</v>
       </c>
       <c r="I123" s="12" t="s">
@@ -4738,9 +5942,11 @@
       <c r="J123" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="K123" s="4"/>
-    </row>
-    <row r="124" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K123" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="1" ht="35.05">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4748,7 +5954,7 @@
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
-      <c r="H124" s="1" t="n">
+      <c r="H124" s="1">
         <v>163</v>
       </c>
       <c r="I124" s="12" t="s">
@@ -4757,9 +5963,11 @@
       <c r="J124" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="K124" s="4"/>
-    </row>
-    <row r="125" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K124" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="1" ht="23.85">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4767,7 +5975,7 @@
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
-      <c r="H125" s="1" t="n">
+      <c r="H125" s="1">
         <v>164</v>
       </c>
       <c r="I125" s="12" t="s">
@@ -4776,9 +5984,11 @@
       <c r="J125" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="K125" s="4"/>
-    </row>
-    <row r="126" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K125" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="126" s="1" customFormat="1" ht="12.8">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
         <v>138</v>
@@ -4792,7 +6002,7 @@
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" s="1" customFormat="1" ht="12.8">
       <c r="A127" s="4" t="s">
         <v>69</v>
       </c>
@@ -4806,7 +6016,7 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
     </row>
-    <row r="128" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" s="1" customFormat="1" ht="13.8">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4814,7 +6024,7 @@
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
-      <c r="H128" s="1" t="n">
+      <c r="H128" s="1">
         <v>165</v>
       </c>
       <c r="I128" s="13" t="s">
@@ -4823,9 +6033,11 @@
       <c r="J128" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="K128" s="4"/>
-    </row>
-    <row r="129" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K128" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="129" s="1" customFormat="1" ht="13.8">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4833,7 +6045,7 @@
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="1" t="n">
+      <c r="H129" s="1">
         <v>166</v>
       </c>
       <c r="I129" s="13" t="s">
@@ -4842,9 +6054,11 @@
       <c r="J129" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K129" s="4"/>
-    </row>
-    <row r="130" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K129" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="1" ht="23.85">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4852,7 +6066,7 @@
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
-      <c r="H130" s="1" t="n">
+      <c r="H130" s="1">
         <v>167</v>
       </c>
       <c r="I130" s="13" t="s">
@@ -4861,9 +6075,11 @@
       <c r="J130" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="K130" s="4"/>
-    </row>
-    <row r="131" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K130" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="1" ht="23.85">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4871,7 +6087,7 @@
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="1" t="n">
+      <c r="H131" s="1">
         <v>168</v>
       </c>
       <c r="I131" s="12" t="s">
@@ -4880,9 +6096,11 @@
       <c r="J131" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K131" s="4"/>
-    </row>
-    <row r="132" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K131" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="132" s="1" customFormat="1" ht="12.8">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
         <v>138</v>
@@ -4896,7 +6114,7 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" s="1" customFormat="1" ht="12.8">
       <c r="A133" s="4" t="s">
         <v>60</v>
       </c>
@@ -4910,7 +6128,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
     </row>
-    <row r="134" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" s="1" customFormat="1" ht="23.85">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4918,7 +6136,7 @@
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="1" t="n">
+      <c r="H134" s="1">
         <v>116</v>
       </c>
       <c r="I134" s="12" t="s">
@@ -4927,9 +6145,11 @@
       <c r="J134" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K134" s="4"/>
-    </row>
-    <row r="135" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K134" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" ht="35.05">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4937,7 +6157,7 @@
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="1" t="n">
+      <c r="H135" s="1">
         <v>117</v>
       </c>
       <c r="I135" s="12" t="s">
@@ -4946,9 +6166,11 @@
       <c r="J135" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="K135" s="4"/>
-    </row>
-    <row r="136" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K135" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="1" ht="46.25">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4956,7 +6178,7 @@
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
-      <c r="H136" s="1" t="n">
+      <c r="H136" s="1">
         <v>118</v>
       </c>
       <c r="I136" s="12" t="s">
@@ -4965,9 +6187,11 @@
       <c r="J136" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="K136" s="4"/>
-    </row>
-    <row r="137" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K136" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="1" ht="35.05">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4975,7 +6199,7 @@
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="1" t="n">
+      <c r="H137" s="1">
         <v>119</v>
       </c>
       <c r="I137" s="12" t="s">
@@ -4984,9 +6208,11 @@
       <c r="J137" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="K137" s="4"/>
-    </row>
-    <row r="138" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K137" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="1" ht="23.85">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4994,7 +6220,7 @@
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="1" t="n">
+      <c r="H138" s="1">
         <v>120</v>
       </c>
       <c r="I138" s="12" t="s">
@@ -5003,9 +6229,11 @@
       <c r="J138" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="K138" s="4"/>
-    </row>
-    <row r="139" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K138" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="139" s="1" customFormat="1" ht="12.8">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
         <v>138</v>
@@ -5019,7 +6247,7 @@
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
     </row>
-    <row r="140" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" s="1" customFormat="1" ht="12.8">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -5031,7 +6259,7 @@
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
     </row>
-    <row r="141" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" s="1" customFormat="1" ht="22.35">
       <c r="A141" s="4" t="s">
         <v>63</v>
       </c>
@@ -5045,7 +6273,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" s="1" customFormat="1" ht="13.8">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -5053,7 +6281,7 @@
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
-      <c r="H142" s="1" t="n">
+      <c r="H142" s="1">
         <v>121</v>
       </c>
       <c r="I142" s="12" t="s">
@@ -5062,9 +6290,11 @@
       <c r="J142" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="K142" s="4"/>
-    </row>
-    <row r="143" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K142" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="143" s="1" customFormat="1" ht="35.05">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -5072,7 +6302,7 @@
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
-      <c r="H143" s="1" t="n">
+      <c r="H143" s="1">
         <v>122</v>
       </c>
       <c r="I143" s="12" t="s">
@@ -5081,9 +6311,11 @@
       <c r="J143" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="K143" s="4"/>
-    </row>
-    <row r="144" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K143" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="144" s="1" customFormat="1" ht="35.05">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -5091,7 +6323,7 @@
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
-      <c r="H144" s="1" t="n">
+      <c r="H144" s="1">
         <v>123</v>
       </c>
       <c r="I144" s="12" t="s">
@@ -5100,9 +6332,11 @@
       <c r="J144" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="K144" s="4"/>
-    </row>
-    <row r="145" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K144" s="4" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="145" s="1" customFormat="1" ht="23.85">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -5110,7 +6344,7 @@
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
-      <c r="H145" s="1" t="n">
+      <c r="H145" s="1">
         <v>124</v>
       </c>
       <c r="I145" s="12" t="s">
@@ -5119,9 +6353,11 @@
       <c r="J145" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="K145" s="4"/>
-    </row>
-    <row r="146" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K145" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="146" s="1" customFormat="1" ht="23.85">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -5129,7 +6365,7 @@
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
-      <c r="H146" s="1" t="n">
+      <c r="H146" s="1">
         <v>125</v>
       </c>
       <c r="I146" s="12" t="s">
@@ -5138,9 +6374,11 @@
       <c r="J146" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="K146" s="4"/>
-    </row>
-    <row r="147" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K146" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="147" s="1" customFormat="1" ht="22.35">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -5148,7 +6386,7 @@
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
-      <c r="H147" s="1" t="n">
+      <c r="H147" s="1">
         <v>126</v>
       </c>
       <c r="I147" s="4" t="s">
@@ -5157,9 +6395,11 @@
       <c r="J147" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="K147" s="4"/>
-    </row>
-    <row r="148" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K147" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="148" s="1" customFormat="1" ht="12.8">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -5171,7 +6411,7 @@
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
     </row>
-    <row r="149" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" s="1" customFormat="1" ht="12.8">
       <c r="A149" s="4"/>
       <c r="B149" s="4" t="s">
         <v>138</v>
@@ -5185,7 +6425,7 @@
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
     </row>
-    <row r="150" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="1" customFormat="1" ht="12.8">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -5197,7 +6437,7 @@
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
     </row>
-    <row r="151" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" s="1" customFormat="1" ht="22.35">
       <c r="A151" s="4" t="s">
         <v>66</v>
       </c>
@@ -5211,7 +6451,7 @@
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
     </row>
-    <row r="152" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" s="1" customFormat="1" ht="23.85">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -5219,7 +6459,7 @@
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
-      <c r="H152" s="1" t="n">
+      <c r="H152" s="1">
         <v>127</v>
       </c>
       <c r="I152" s="12" t="s">
@@ -5228,9 +6468,11 @@
       <c r="J152" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="K152" s="4"/>
-    </row>
-    <row r="153" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K152" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="153" s="1" customFormat="1" ht="23.85">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4" t="s">
@@ -5240,7 +6482,7 @@
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
-      <c r="H153" s="1" t="n">
+      <c r="H153" s="1">
         <v>230</v>
       </c>
       <c r="I153" s="12" t="s">
@@ -5249,9 +6491,11 @@
       <c r="J153" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="K153" s="4"/>
-    </row>
-    <row r="154" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K153" s="4" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="154" s="1" customFormat="1" ht="22.35">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4" t="s">
@@ -5269,7 +6513,7 @@
       <c r="J154" s="10"/>
       <c r="K154" s="4"/>
     </row>
-    <row r="155" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" s="1" customFormat="1" ht="23.85">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4" t="s">
@@ -5279,7 +6523,7 @@
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
-      <c r="H155" s="1" t="n">
+      <c r="H155" s="1">
         <v>231</v>
       </c>
       <c r="I155" s="12" t="s">
@@ -5288,9 +6532,11 @@
       <c r="J155" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="K155" s="4"/>
-    </row>
-    <row r="156" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K155" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="156" s="1" customFormat="1" ht="22.35">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4" t="s">
@@ -5300,7 +6546,7 @@
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
-      <c r="H156" s="1" t="n">
+      <c r="H156" s="1">
         <v>232</v>
       </c>
       <c r="I156" s="12" t="s">
@@ -5309,9 +6555,11 @@
       <c r="J156" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="K156" s="4"/>
-    </row>
-    <row r="157" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K156" s="4" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="157" s="1" customFormat="1" ht="23.85">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5319,7 +6567,7 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="H157" s="1" t="n">
+      <c r="H157" s="1">
         <v>128</v>
       </c>
       <c r="I157" s="14" t="s">
@@ -5328,9 +6576,11 @@
       <c r="J157" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="K157" s="4"/>
-    </row>
-    <row r="158" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K157" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="158" s="1" customFormat="1" ht="12.8">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -5342,7 +6592,7 @@
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
     </row>
-    <row r="159" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" s="1" customFormat="1" ht="12.8">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
         <v>138</v>
@@ -5356,7 +6606,7 @@
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
     </row>
-    <row r="160" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" s="1" customFormat="1" ht="12.8">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -5368,7 +6618,7 @@
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
     </row>
-    <row r="161" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" s="1" customFormat="1" ht="12.8">
       <c r="A161" s="4" t="s">
         <v>99</v>
       </c>
@@ -5382,7 +6632,7 @@
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
     </row>
-    <row r="162" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" s="1" customFormat="1" ht="13.8">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5390,7 +6640,7 @@
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
-      <c r="H162" s="1" t="n">
+      <c r="H162" s="1">
         <v>129</v>
       </c>
       <c r="I162" s="12" t="s">
@@ -5399,9 +6649,11 @@
       <c r="J162" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="K162" s="4"/>
-    </row>
-    <row r="163" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K162" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="1" ht="23.85">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -5409,7 +6661,7 @@
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
-      <c r="H163" s="1" t="n">
+      <c r="H163" s="1">
         <v>130</v>
       </c>
       <c r="I163" s="12" t="s">
@@ -5418,9 +6670,11 @@
       <c r="J163" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="K163" s="4"/>
-    </row>
-    <row r="164" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K163" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="164" s="1" customFormat="1" ht="23.85">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -5428,7 +6682,7 @@
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
-      <c r="H164" s="1" t="n">
+      <c r="H164" s="1">
         <v>131</v>
       </c>
       <c r="I164" s="12" t="s">
@@ -5437,9 +6691,11 @@
       <c r="J164" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="K164" s="4"/>
-    </row>
-    <row r="165" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K164" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" ht="23.85">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5447,7 +6703,7 @@
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
-      <c r="H165" s="1" t="n">
+      <c r="H165" s="1">
         <v>132</v>
       </c>
       <c r="I165" s="12" t="s">
@@ -5456,9 +6712,11 @@
       <c r="J165" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K165" s="4"/>
-    </row>
-    <row r="166" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K165" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="166" s="1" customFormat="1" ht="35.05">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -5466,7 +6724,7 @@
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
-      <c r="H166" s="1" t="n">
+      <c r="H166" s="1">
         <v>133</v>
       </c>
       <c r="I166" s="12" t="s">
@@ -5475,9 +6733,11 @@
       <c r="J166" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="K166" s="4"/>
-    </row>
-    <row r="167" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K166" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="167" s="1" customFormat="1" ht="35.05">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5485,7 +6745,7 @@
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
-      <c r="H167" s="1" t="n">
+      <c r="H167" s="1">
         <v>134</v>
       </c>
       <c r="I167" s="12" t="s">
@@ -5494,9 +6754,11 @@
       <c r="J167" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="K167" s="4"/>
-    </row>
-    <row r="168" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K167" s="4" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="168" s="1" customFormat="1" ht="23.85">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5504,7 +6766,7 @@
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
-      <c r="H168" s="1" t="n">
+      <c r="H168" s="1">
         <v>135</v>
       </c>
       <c r="I168" s="14" t="s">
@@ -5513,9 +6775,11 @@
       <c r="J168" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="K168" s="4"/>
-    </row>
-    <row r="169" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K168" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="169" s="1" customFormat="1" ht="23.85">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5523,7 +6787,7 @@
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="H169" s="1" t="n">
+      <c r="H169" s="1">
         <v>136</v>
       </c>
       <c r="I169" s="14" t="s">
@@ -5532,9 +6796,11 @@
       <c r="J169" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="K169" s="4"/>
-    </row>
-    <row r="170" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K169" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="170" s="1" customFormat="1" ht="12.8">
       <c r="A170" s="4"/>
       <c r="B170" s="4" t="s">
         <v>138</v>
@@ -5548,7 +6814,7 @@
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
     </row>
-    <row r="171" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" s="1" customFormat="1" ht="12.8">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5560,7 +6826,7 @@
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
     </row>
-    <row r="172" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" s="1" customFormat="1" ht="12.8">
       <c r="A172" s="4" t="s">
         <v>18</v>
       </c>
@@ -5574,7 +6840,7 @@
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
     </row>
-    <row r="173" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" s="1" customFormat="1" ht="23.85">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5582,7 +6848,7 @@
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
-      <c r="H173" s="1" t="n">
+      <c r="H173" s="1">
         <v>137</v>
       </c>
       <c r="I173" s="12" t="s">
@@ -5591,9 +6857,11 @@
       <c r="J173" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="K173" s="4"/>
-    </row>
-    <row r="174" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K173" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="174" s="1" customFormat="1" ht="13.8">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -5601,7 +6869,7 @@
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
-      <c r="H174" s="1" t="n">
+      <c r="H174" s="1">
         <v>138</v>
       </c>
       <c r="I174" s="12" t="s">
@@ -5610,9 +6878,11 @@
       <c r="J174" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="K174" s="4"/>
-    </row>
-    <row r="175" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K174" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="175" s="1" customFormat="1" ht="13.8">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5620,7 +6890,7 @@
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
-      <c r="H175" s="1" t="n">
+      <c r="H175" s="1">
         <v>139</v>
       </c>
       <c r="I175" s="12" t="s">
@@ -5629,9 +6899,11 @@
       <c r="J175" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="K175" s="4"/>
-    </row>
-    <row r="176" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K175" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="1" ht="35.05">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5639,7 +6911,7 @@
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
-      <c r="H176" s="1" t="n">
+      <c r="H176" s="1">
         <v>140</v>
       </c>
       <c r="I176" s="12" t="s">
@@ -5648,9 +6920,11 @@
       <c r="J176" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="K176" s="4"/>
-    </row>
-    <row r="177" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K176" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="1" ht="23.85">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5658,7 +6932,7 @@
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
-      <c r="H177" s="1" t="n">
+      <c r="H177" s="1">
         <v>141</v>
       </c>
       <c r="I177" s="12" t="s">
@@ -5667,9 +6941,11 @@
       <c r="J177" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="K177" s="4"/>
-    </row>
-    <row r="178" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K177" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="178" s="1" customFormat="1" ht="35.05">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -5677,7 +6953,7 @@
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="H178" s="1" t="n">
+      <c r="H178" s="1">
         <v>142</v>
       </c>
       <c r="I178" s="12" t="s">
@@ -5686,9 +6962,11 @@
       <c r="J178" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="K178" s="4"/>
-    </row>
-    <row r="179" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K178" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="179" s="1" customFormat="1" ht="12.8">
       <c r="A179" s="4"/>
       <c r="B179" s="4" t="s">
         <v>138</v>
@@ -5702,7 +6980,7 @@
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
     </row>
-    <row r="180" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="1" customFormat="1" ht="12.8">
       <c r="A180" s="4" t="s">
         <v>90</v>
       </c>
@@ -5716,7 +6994,7 @@
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="1" customFormat="1" ht="13.8">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5724,7 +7002,7 @@
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
-      <c r="H181" s="1" t="n">
+      <c r="H181" s="1">
         <v>143</v>
       </c>
       <c r="I181" s="12" t="s">
@@ -5733,9 +7011,11 @@
       <c r="J181" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="K181" s="4"/>
-    </row>
-    <row r="182" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K181" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="182" s="1" customFormat="1" ht="35.05">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5743,7 +7023,7 @@
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
-      <c r="H182" s="1" t="n">
+      <c r="H182" s="1">
         <v>144</v>
       </c>
       <c r="I182" s="12" t="s">
@@ -5752,9 +7032,11 @@
       <c r="J182" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="K182" s="4"/>
-    </row>
-    <row r="183" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K182" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="183" s="1" customFormat="1" ht="35.05">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5762,7 +7044,7 @@
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
-      <c r="H183" s="1" t="n">
+      <c r="H183" s="1">
         <v>145</v>
       </c>
       <c r="I183" s="12" t="s">
@@ -5771,9 +7053,11 @@
       <c r="J183" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="K183" s="4"/>
-    </row>
-    <row r="184" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K183" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="184" s="1" customFormat="1" ht="35.05">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5781,7 +7065,7 @@
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
-      <c r="H184" s="1" t="n">
+      <c r="H184" s="1">
         <v>146</v>
       </c>
       <c r="I184" s="12" t="s">
@@ -5790,9 +7074,11 @@
       <c r="J184" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="K184" s="4"/>
-    </row>
-    <row r="185" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K184" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="185" s="1" customFormat="1" ht="46.25">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5800,7 +7086,7 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="H185" s="1" t="n">
+      <c r="H185" s="1">
         <v>147</v>
       </c>
       <c r="I185" s="12" t="s">
@@ -5809,9 +7095,11 @@
       <c r="J185" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="K185" s="4"/>
-    </row>
-    <row r="186" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K185" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="186" s="1" customFormat="1" ht="12.8">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5823,7 +7111,7 @@
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
     </row>
-    <row r="187" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" s="1" customFormat="1" ht="12.8">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5835,7 +7123,7 @@
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
     </row>
-    <row r="188" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" s="1" customFormat="1" ht="12.8">
       <c r="A188" s="4"/>
       <c r="B188" s="4" t="s">
         <v>138</v>
@@ -5849,7 +7137,7 @@
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
     </row>
-    <row r="189" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" s="1" customFormat="1" ht="12.8">
       <c r="A189" s="4" t="s">
         <v>39</v>
       </c>
@@ -5863,7 +7151,7 @@
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
     </row>
-    <row r="190" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" s="1" customFormat="1" ht="12.8">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5871,7 +7159,7 @@
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
-      <c r="H190" s="1" t="n">
+      <c r="H190" s="1">
         <v>148</v>
       </c>
       <c r="I190" s="4" t="s">
@@ -5880,9 +7168,11 @@
       <c r="J190" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="K190" s="4"/>
-    </row>
-    <row r="191" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K190" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" ht="12.8">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5890,7 +7180,7 @@
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
-      <c r="H191" s="1" t="n">
+      <c r="H191" s="1">
         <v>149</v>
       </c>
       <c r="I191" s="4" t="s">
@@ -5899,9 +7189,11 @@
       <c r="J191" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="K191" s="4"/>
-    </row>
-    <row r="192" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K191" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" ht="32.8">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5909,7 +7201,7 @@
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
-      <c r="H192" s="1" t="n">
+      <c r="H192" s="1">
         <v>150</v>
       </c>
       <c r="I192" s="4" t="s">
@@ -5918,9 +7210,11 @@
       <c r="J192" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="K192" s="4"/>
-    </row>
-    <row r="193" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K192" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" ht="32.8">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5928,7 +7222,7 @@
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
-      <c r="H193" s="1" t="n">
+      <c r="H193" s="1">
         <v>151</v>
       </c>
       <c r="I193" s="4" t="s">
@@ -5937,9 +7231,11 @@
       <c r="J193" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="K193" s="4"/>
-    </row>
-    <row r="194" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K193" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" ht="43.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5947,7 +7243,7 @@
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
-      <c r="H194" s="1" t="n">
+      <c r="H194" s="1">
         <v>152</v>
       </c>
       <c r="I194" s="4" t="s">
@@ -5956,9 +7252,11 @@
       <c r="J194" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="K194" s="4"/>
-    </row>
-    <row r="195" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K194" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" ht="32.8">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5966,7 +7264,7 @@
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
-      <c r="H195" s="1" t="n">
+      <c r="H195" s="1">
         <v>153</v>
       </c>
       <c r="I195" s="4" t="s">
@@ -5975,9 +7273,11 @@
       <c r="J195" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="K195" s="4"/>
-    </row>
-    <row r="196" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K195" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="196" ht="32.8">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5985,7 +7285,7 @@
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="H196" s="1" t="n">
+      <c r="H196" s="1">
         <v>154</v>
       </c>
       <c r="I196" s="4" t="s">
@@ -5994,9 +7294,11 @@
       <c r="J196" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K196" s="4"/>
-    </row>
-    <row r="197" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K196" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="197" s="1" customFormat="1" ht="12.8">
       <c r="A197" s="4"/>
       <c r="B197" s="4" t="s">
         <v>138</v>
@@ -6010,17 +7312,17 @@
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
     </row>
-    <row r="198" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" s="1" customFormat="1" ht="12.8">
       <c r="B198" s="4"/>
     </row>
-    <row r="199" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" s="1" customFormat="1" ht="12.8">
       <c r="A199" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="200" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="201" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H201" s="1" t="n">
+    <row r="200" s="1" customFormat="1" ht="12.8"/>
+    <row r="201" s="1" customFormat="1" ht="12.8">
+      <c r="H201" s="1">
         <v>105</v>
       </c>
       <c r="I201" s="4" t="s">
@@ -6029,9 +7331,12 @@
       <c r="J201" s="10" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="202" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H202" s="1" t="n">
+      <c r="K201" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="202" s="1" customFormat="1" ht="22.35">
+      <c r="H202" s="1">
         <v>106</v>
       </c>
       <c r="I202" s="4" t="s">
@@ -6040,9 +7345,12 @@
       <c r="J202" s="4" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="203" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H203" s="1" t="n">
+      <c r="K202" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="203" s="1" customFormat="1" ht="32.8">
+      <c r="H203" s="1">
         <v>107</v>
       </c>
       <c r="I203" s="4" t="s">
@@ -6051,9 +7359,12 @@
       <c r="J203" s="4" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="204" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H204" s="1" t="n">
+      <c r="K203" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="204" s="1" customFormat="1" ht="32.8">
+      <c r="H204" s="1">
         <v>108</v>
       </c>
       <c r="I204" s="4" t="s">
@@ -6062,9 +7373,12 @@
       <c r="J204" s="4" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="205" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H205" s="1" t="n">
+      <c r="K204" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="205" s="1" customFormat="1" ht="22.35">
+      <c r="H205" s="1">
         <v>109</v>
       </c>
       <c r="I205" s="4" t="s">
@@ -6073,20 +7387,23 @@
       <c r="J205" s="4" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="206" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K205" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="1" ht="12.8">
       <c r="B206" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="207" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" s="1" customFormat="1" ht="12.8">
       <c r="A207" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="208" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="209" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H209" s="1" t="n">
+    <row r="208" s="1" customFormat="1" ht="12.8"/>
+    <row r="209" s="1" customFormat="1" ht="12.8">
+      <c r="H209" s="1">
         <v>110</v>
       </c>
       <c r="I209" s="4" t="s">
@@ -6095,9 +7412,12 @@
       <c r="J209" s="10" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="210" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H210" s="1" t="n">
+      <c r="K209" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="210" s="1" customFormat="1" ht="23.85">
+      <c r="H210" s="1">
         <v>111</v>
       </c>
       <c r="I210" s="4" t="s">
@@ -6106,9 +7426,12 @@
       <c r="J210" s="10" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="211" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H211" s="1" t="n">
+      <c r="K210" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" ht="23.85">
+      <c r="H211" s="1">
         <v>112</v>
       </c>
       <c r="I211" s="4" t="s">
@@ -6117,9 +7440,12 @@
       <c r="J211" s="10" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="212" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H212" s="1" t="n">
+      <c r="K211" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" ht="46.25">
+      <c r="H212" s="1">
         <v>113</v>
       </c>
       <c r="I212" s="4" t="s">
@@ -6128,9 +7454,12 @@
       <c r="J212" s="10" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="213" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H213" s="1" t="n">
+      <c r="K212" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" ht="23.85">
+      <c r="H213" s="1">
         <v>114</v>
       </c>
       <c r="I213" s="4" t="s">
@@ -6139,9 +7468,12 @@
       <c r="J213" s="10" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="214" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H214" s="1" t="n">
+      <c r="K213" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="214" ht="23.85">
+      <c r="H214" s="1">
         <v>115</v>
       </c>
       <c r="I214" s="4" t="s">
@@ -6150,24 +7482,26 @@
       <c r="J214" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="K214" s="1"/>
-    </row>
-    <row r="215" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K214" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" ht="12.8">
       <c r="B215" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="216" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" s="1" customFormat="1" ht="12.8">
       <c r="B216" s="4"/>
     </row>
-    <row r="217" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" s="1" customFormat="1" ht="22.35">
       <c r="A217" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="218" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="219" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H219" s="1" t="n">
+    <row r="218" s="1" customFormat="1" ht="12.8"/>
+    <row r="219" s="1" customFormat="1" ht="12.8">
+      <c r="H219" s="1">
         <v>26</v>
       </c>
       <c r="I219" s="4" t="s">
@@ -6176,9 +7510,12 @@
       <c r="J219" s="10" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="220" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H220" s="1" t="n">
+      <c r="K219" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="1" ht="32.8">
+      <c r="H220" s="1">
         <v>27</v>
       </c>
       <c r="I220" s="4" t="s">
@@ -6187,9 +7524,12 @@
       <c r="J220" s="4" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="221" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H221" s="1" t="n">
+      <c r="K220" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="1" ht="22.35">
+      <c r="H221" s="1">
         <v>28</v>
       </c>
       <c r="I221" s="4" t="s">
@@ -6198,9 +7538,12 @@
       <c r="J221" s="4" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="222" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H222" s="1" t="n">
+      <c r="K221" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="1" ht="64.15">
+      <c r="H222" s="1">
         <v>29</v>
       </c>
       <c r="I222" s="4" t="s">
@@ -6209,9 +7552,12 @@
       <c r="J222" s="4" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="223" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H223" s="1" t="n">
+      <c r="K222" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="1" ht="32.8">
+      <c r="H223" s="1">
         <v>30</v>
       </c>
       <c r="I223" s="4" t="s">
@@ -6220,9 +7566,12 @@
       <c r="J223" s="4" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="224" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H224" s="1" t="n">
+      <c r="K223" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="224" s="1" customFormat="1" ht="12.8">
+      <c r="H224" s="1">
         <v>31</v>
       </c>
       <c r="I224" s="4" t="s">
@@ -6231,9 +7580,12 @@
       <c r="J224" s="4" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="225" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H225" s="1" t="n">
+      <c r="K224" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="225" s="1" customFormat="1" ht="12.8">
+      <c r="H225" s="1">
         <v>32</v>
       </c>
       <c r="I225" s="4" t="s">
@@ -6242,9 +7594,12 @@
       <c r="J225" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="226" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H226" s="1" t="n">
+      <c r="K225" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="226" s="1" customFormat="1" ht="22.35">
+      <c r="H226" s="1">
         <v>33</v>
       </c>
       <c r="I226" s="4" t="s">
@@ -6253,9 +7608,12 @@
       <c r="J226" s="4" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H227" s="1" t="n">
+      <c r="K226" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="227" ht="12.8">
+      <c r="H227" s="1">
         <v>34</v>
       </c>
       <c r="I227" s="4" t="s">
@@ -6264,24 +7622,26 @@
       <c r="J227" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="K227" s="1"/>
-    </row>
-    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K227" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="228" ht="12.8">
       <c r="B228" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K228" s="1"/>
     </row>
-    <row r="229" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="230" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="15.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" ht="15.65" customHeight="1"/>
+    <row r="230" ht="15.65" customHeight="1"/>
+    <row r="231" ht="15.65" customHeight="1"/>
+    <row r="232" ht="12.8">
       <c r="A232" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H234" s="1" t="n">
+    <row r="234" ht="12.8">
+      <c r="H234" s="1">
         <v>35</v>
       </c>
       <c r="I234" s="4" t="s">
@@ -6290,15 +7650,18 @@
       <c r="J234" s="10" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K234" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="235" ht="12.8">
       <c r="B235" s="1" t="s">
         <v>395</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H235" s="1" t="n">
+      <c r="H235" s="1">
         <v>36</v>
       </c>
       <c r="I235" s="4" t="s">
@@ -6307,15 +7670,18 @@
       <c r="J235" s="10" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K235" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="236" ht="12.8">
       <c r="B236" s="1" t="s">
         <v>399</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H236" s="1" t="n">
+      <c r="H236" s="1">
         <v>37</v>
       </c>
       <c r="I236" s="4" t="s">
@@ -6324,20 +7690,23 @@
       <c r="J236" s="10" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K236" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="237" ht="12.8">
       <c r="I237" s="4"/>
       <c r="J237" s="10"/>
     </row>
-    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" ht="12.8">
       <c r="A238" s="1" t="s">
         <v>395</v>
       </c>
       <c r="I238" s="4"/>
       <c r="J238" s="10"/>
     </row>
-    <row r="239" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H239" s="1" t="n">
+    <row r="239" ht="22.35">
+      <c r="H239" s="1">
         <v>38</v>
       </c>
       <c r="I239" s="4" t="s">
@@ -6346,9 +7715,12 @@
       <c r="J239" s="4" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="240" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H240" s="1" t="n">
+      <c r="K239" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="240" s="1" customFormat="1" ht="22.35">
+      <c r="H240" s="1">
         <v>39</v>
       </c>
       <c r="I240" s="4" t="s">
@@ -6357,9 +7729,12 @@
       <c r="J240" s="4" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="241" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H241" s="1" t="n">
+      <c r="K240" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="241" ht="22.35">
+      <c r="H241" s="1">
         <v>40</v>
       </c>
       <c r="I241" s="4" t="s">
@@ -6368,9 +7743,12 @@
       <c r="J241" s="4" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="242" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H242" s="1" t="n">
+      <c r="K241" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="242" ht="22.35">
+      <c r="H242" s="1">
         <v>41</v>
       </c>
       <c r="I242" s="4" t="s">
@@ -6379,10 +7757,12 @@
       <c r="J242" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K242" s="1"/>
-    </row>
-    <row r="243" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H243" s="1" t="n">
+      <c r="K242" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="243" ht="22.35">
+      <c r="H243" s="1">
         <v>42</v>
       </c>
       <c r="I243" s="4" t="s">
@@ -6391,9 +7771,12 @@
       <c r="J243" s="4" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="244" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H244" s="1" t="n">
+      <c r="K243" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="244" ht="32.8">
+      <c r="H244" s="1">
         <v>43</v>
       </c>
       <c r="I244" s="4" t="s">
@@ -6402,21 +7785,24 @@
       <c r="J244" s="4" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K244" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="245" ht="12.8">
       <c r="B245" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J245" s="4"/>
     </row>
-    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" ht="12.8">
       <c r="A246" s="1" t="s">
         <v>399</v>
       </c>
       <c r="J246" s="4"/>
     </row>
-    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H247" s="1" t="n">
+    <row r="247" ht="12.8">
+      <c r="H247" s="1">
         <v>44</v>
       </c>
       <c r="I247" s="4" t="s">
@@ -6425,20 +7811,23 @@
       <c r="J247" s="10" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="248" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K247" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="248" s="1" customFormat="1" ht="12.8">
       <c r="B248" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="249" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="250" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" s="1" customFormat="1" ht="12.8"/>
+    <row r="250" s="1" customFormat="1" ht="12.8">
       <c r="A250" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="251" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H251" s="1" t="n">
+    <row r="251" s="1" customFormat="1" ht="23.85">
+      <c r="H251" s="1">
         <v>93</v>
       </c>
       <c r="I251" s="4" t="s">
@@ -6447,9 +7836,12 @@
       <c r="J251" s="10" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="252" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H252" s="1" t="n">
+      <c r="K251" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="252" s="1" customFormat="1" ht="32.8">
+      <c r="H252" s="1">
         <v>94</v>
       </c>
       <c r="I252" s="4" t="s">
@@ -6458,9 +7850,12 @@
       <c r="J252" s="4" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="253" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H253" s="1" t="n">
+      <c r="K252" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="253" s="1" customFormat="1" ht="32.8">
+      <c r="H253" s="1">
         <v>95</v>
       </c>
       <c r="I253" s="4" t="s">
@@ -6469,9 +7864,12 @@
       <c r="J253" s="4" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="254" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H254" s="1" t="n">
+      <c r="K253" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="254" s="1" customFormat="1" ht="32.8">
+      <c r="H254" s="1">
         <v>96</v>
       </c>
       <c r="I254" s="4" t="s">
@@ -6480,9 +7878,12 @@
       <c r="J254" s="4" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="255" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H255" s="1" t="n">
+      <c r="K254" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="255" s="1" customFormat="1" ht="12.8">
+      <c r="H255" s="1">
         <v>97</v>
       </c>
       <c r="I255" s="4" t="s">
@@ -6491,9 +7892,12 @@
       <c r="J255" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="256" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H256" s="1" t="n">
+      <c r="K255" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="256" s="1" customFormat="1" ht="12.8">
+      <c r="H256" s="1">
         <v>98</v>
       </c>
       <c r="I256" s="4" t="s">
@@ -6502,9 +7906,12 @@
       <c r="J256" s="4" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="257" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H257" s="1" t="n">
+      <c r="K256" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="257" s="1" customFormat="1" ht="32.8">
+      <c r="H257" s="1">
         <v>99</v>
       </c>
       <c r="I257" s="4" t="s">
@@ -6513,23 +7920,26 @@
       <c r="J257" s="4" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="258" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K257" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="258" s="1" customFormat="1" ht="12.8">
       <c r="I258" s="4"/>
       <c r="J258" s="4"/>
     </row>
-    <row r="259" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" s="1" customFormat="1" ht="12.8">
       <c r="B259" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="260" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" s="1" customFormat="1" ht="12.8">
       <c r="A260" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="261" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H261" s="1" t="n">
+    <row r="261" s="1" customFormat="1" ht="23.85">
+      <c r="H261" s="1">
         <v>100</v>
       </c>
       <c r="I261" s="4" t="s">
@@ -6538,9 +7948,12 @@
       <c r="J261" s="10" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="262" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H262" s="1" t="n">
+      <c r="K261" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="262" s="1" customFormat="1" ht="43.25">
+      <c r="H262" s="1">
         <v>101</v>
       </c>
       <c r="I262" s="4" t="s">
@@ -6549,9 +7962,12 @@
       <c r="J262" s="4" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="263" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H263" s="1" t="n">
+      <c r="K262" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="263" s="1" customFormat="1" ht="32.8">
+      <c r="H263" s="1">
         <v>102</v>
       </c>
       <c r="I263" s="4" t="s">
@@ -6560,9 +7976,12 @@
       <c r="J263" s="4" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="264" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H264" s="1" t="n">
+      <c r="K263" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="264" s="1" customFormat="1" ht="22.35">
+      <c r="H264" s="1">
         <v>103</v>
       </c>
       <c r="I264" s="4" t="s">
@@ -6571,9 +7990,12 @@
       <c r="J264" s="4" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="265" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H265" s="1" t="n">
+      <c r="K264" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="265" s="1" customFormat="1" ht="12.8">
+      <c r="H265" s="1">
         <v>104</v>
       </c>
       <c r="I265" s="4" t="s">
@@ -6582,26 +8004,29 @@
       <c r="J265" s="4" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="266" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K265" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="266" s="1" customFormat="1" ht="12.8">
       <c r="I266" s="4"/>
       <c r="J266" s="4"/>
     </row>
-    <row r="267" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" s="1" customFormat="1" ht="12.8">
       <c r="B267" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="268" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" s="1" customFormat="1" ht="12.8">
       <c r="B268" s="4"/>
     </row>
-    <row r="269" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" s="1" customFormat="1" ht="12.8">
       <c r="A269" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="270" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H270" s="1" t="n">
+    <row r="270" s="1" customFormat="1" ht="12.8">
+      <c r="H270" s="1">
         <v>79</v>
       </c>
       <c r="I270" s="4" t="s">
@@ -6610,9 +8035,12 @@
       <c r="J270" s="10" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="271" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H271" s="1" t="n">
+      <c r="K270" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="271" s="1" customFormat="1" ht="12.8">
+      <c r="H271" s="1">
         <v>80</v>
       </c>
       <c r="I271" s="4" t="s">
@@ -6621,9 +8049,12 @@
       <c r="J271" s="4" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="272" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H272" s="1" t="n">
+      <c r="K271" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="272" s="1" customFormat="1" ht="43.25">
+      <c r="H272" s="1">
         <v>81</v>
       </c>
       <c r="I272" s="4" t="s">
@@ -6632,9 +8063,12 @@
       <c r="J272" s="4" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="273" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H273" s="1" t="n">
+      <c r="K272" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="273" s="1" customFormat="1" ht="22.35">
+      <c r="H273" s="1">
         <v>82</v>
       </c>
       <c r="I273" s="4" t="s">
@@ -6643,9 +8077,12 @@
       <c r="J273" s="4" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="274" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H274" s="1" t="n">
+      <c r="K273" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="274" s="1" customFormat="1" ht="43.25">
+      <c r="H274" s="1">
         <v>83</v>
       </c>
       <c r="I274" s="4" t="s">
@@ -6654,9 +8091,12 @@
       <c r="J274" s="4" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="275" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H275" s="1" t="n">
+      <c r="K274" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="275" s="1" customFormat="1" ht="12.8">
+      <c r="H275" s="1">
         <v>84</v>
       </c>
       <c r="I275" s="4" t="s">
@@ -6665,30 +8105,33 @@
       <c r="J275" s="4" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K275" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="276" ht="12.8">
       <c r="I276" s="4"/>
       <c r="J276" s="4"/>
       <c r="K276" s="1"/>
     </row>
-    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" ht="12.8">
       <c r="B277" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K277" s="1"/>
     </row>
-    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" ht="12.8">
       <c r="B278" s="4"/>
       <c r="K278" s="1"/>
     </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" ht="12.8">
       <c r="A279" s="4" t="s">
         <v>48</v>
       </c>
       <c r="K279" s="1"/>
     </row>
-    <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H280" s="1" t="n">
+    <row r="280" ht="12.8">
+      <c r="H280" s="1">
         <v>85</v>
       </c>
       <c r="I280" s="4" t="s">
@@ -6697,10 +8140,12 @@
       <c r="J280" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="K280" s="1"/>
-    </row>
-    <row r="281" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H281" s="1" t="n">
+      <c r="K280" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="281" ht="22.35">
+      <c r="H281" s="1">
         <v>86</v>
       </c>
       <c r="I281" s="4" t="s">
@@ -6709,10 +8154,12 @@
       <c r="J281" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="K281" s="1"/>
-    </row>
-    <row r="282" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H282" s="1" t="n">
+      <c r="K281" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="282" ht="22.35">
+      <c r="H282" s="1">
         <v>87</v>
       </c>
       <c r="I282" s="4" t="s">
@@ -6721,10 +8168,12 @@
       <c r="J282" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="K282" s="1"/>
-    </row>
-    <row r="283" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H283" s="1" t="n">
+      <c r="K282" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="283" ht="43.25">
+      <c r="H283" s="1">
         <v>88</v>
       </c>
       <c r="I283" s="4" t="s">
@@ -6733,10 +8182,12 @@
       <c r="J283" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="K283" s="1"/>
-    </row>
-    <row r="284" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H284" s="1" t="n">
+      <c r="K283" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="284" ht="32.8">
+      <c r="H284" s="1">
         <v>89</v>
       </c>
       <c r="I284" s="4" t="s">
@@ -6745,10 +8196,12 @@
       <c r="J284" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="K284" s="1"/>
-    </row>
-    <row r="285" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H285" s="1" t="n">
+      <c r="K284" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="285" ht="22.35">
+      <c r="H285" s="1">
         <v>90</v>
       </c>
       <c r="I285" s="4" t="s">
@@ -6757,10 +8210,12 @@
       <c r="J285" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="K285" s="1"/>
-    </row>
-    <row r="286" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H286" s="1" t="n">
+      <c r="K285" s="1" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="286" ht="22.35">
+      <c r="H286" s="1">
         <v>91</v>
       </c>
       <c r="I286" s="4" t="s">
@@ -6769,10 +8224,12 @@
       <c r="J286" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="K286" s="1"/>
-    </row>
-    <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H287" s="1" t="n">
+      <c r="K286" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="287" ht="12.8">
+      <c r="H287" s="1">
         <v>92</v>
       </c>
       <c r="I287" s="4" t="s">
@@ -6781,22 +8238,24 @@
       <c r="J287" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="K287" s="1"/>
-    </row>
-    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K287" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="288" ht="12.8">
       <c r="B288" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K288" s="1"/>
     </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" ht="12.8">
       <c r="A290" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K290" s="1"/>
     </row>
-    <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H291" s="1" t="n">
+    <row r="291" ht="12.8">
+      <c r="H291" s="1">
         <v>74</v>
       </c>
       <c r="I291" s="4" t="s">
@@ -6805,10 +8264,12 @@
       <c r="J291" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="K291" s="1"/>
-    </row>
-    <row r="292" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H292" s="1" t="n">
+      <c r="K291" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="292" ht="32.8">
+      <c r="H292" s="1">
         <v>75</v>
       </c>
       <c r="I292" s="4" t="s">
@@ -6817,10 +8278,12 @@
       <c r="J292" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="K292" s="1"/>
-    </row>
-    <row r="293" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H293" s="1" t="n">
+      <c r="K292" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="293" ht="43.25">
+      <c r="H293" s="1">
         <v>76</v>
       </c>
       <c r="I293" s="4" t="s">
@@ -6829,10 +8292,12 @@
       <c r="J293" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="K293" s="1"/>
-    </row>
-    <row r="294" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H294" s="1" t="n">
+      <c r="K293" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="294" ht="22.35">
+      <c r="H294" s="1">
         <v>77</v>
       </c>
       <c r="I294" s="4" t="s">
@@ -6841,10 +8306,12 @@
       <c r="J294" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="K294" s="1"/>
-    </row>
-    <row r="295" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H295" s="1" t="n">
+      <c r="K294" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="295" ht="32.8">
+      <c r="H295" s="1">
         <v>78</v>
       </c>
       <c r="I295" s="4" t="s">
@@ -6853,31 +8320,33 @@
       <c r="J295" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="K295" s="1"/>
-    </row>
-    <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K295" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="296" ht="12.8">
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
       <c r="K296" s="1"/>
     </row>
-    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" ht="12.8">
       <c r="I297" s="4"/>
       <c r="J297" s="4"/>
       <c r="K297" s="1"/>
     </row>
-    <row r="298" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" s="1" customFormat="1" ht="12.8">
       <c r="B298" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="299" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="300" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" s="1" customFormat="1" ht="12.8"/>
+    <row r="300" s="1" customFormat="1" ht="12.8">
       <c r="A300" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="301" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H301" s="1" t="n">
+    <row r="301" s="1" customFormat="1" ht="23.85">
+      <c r="H301" s="1">
         <v>66</v>
       </c>
       <c r="I301" s="4" t="s">
@@ -6886,9 +8355,12 @@
       <c r="J301" s="10" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="302" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H302" s="1" t="n">
+      <c r="K301" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="302" s="1" customFormat="1" ht="22.35">
+      <c r="H302" s="1">
         <v>67</v>
       </c>
       <c r="I302" s="4" t="s">
@@ -6897,9 +8369,12 @@
       <c r="J302" s="4" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="303" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H303" s="1" t="n">
+      <c r="K302" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="303" s="1" customFormat="1" ht="12.8">
+      <c r="H303" s="1">
         <v>68</v>
       </c>
       <c r="I303" s="4" t="s">
@@ -6908,9 +8383,12 @@
       <c r="J303" s="4" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="304" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H304" s="1" t="n">
+      <c r="K303" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="304" s="1" customFormat="1" ht="22.35">
+      <c r="H304" s="1">
         <v>69</v>
       </c>
       <c r="I304" s="4" t="s">
@@ -6919,9 +8397,12 @@
       <c r="J304" s="4" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="305" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H305" s="1" t="n">
+      <c r="K304" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="305" s="1" customFormat="1" ht="32.8">
+      <c r="H305" s="1">
         <v>70</v>
       </c>
       <c r="I305" s="4" t="s">
@@ -6930,9 +8411,12 @@
       <c r="J305" s="4" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="306" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H306" s="1" t="n">
+      <c r="K305" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="306" s="1" customFormat="1" ht="32.8">
+      <c r="H306" s="1">
         <v>71</v>
       </c>
       <c r="I306" s="4" t="s">
@@ -6941,9 +8425,12 @@
       <c r="J306" s="4" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="307" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H307" s="1" t="n">
+      <c r="K306" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="307" s="1" customFormat="1" ht="22.35">
+      <c r="H307" s="1">
         <v>72</v>
       </c>
       <c r="I307" s="4" t="s">
@@ -6952,9 +8439,12 @@
       <c r="J307" s="4" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="308" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H308" s="1" t="n">
+      <c r="K307" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="308" s="1" customFormat="1" ht="22.35">
+      <c r="H308" s="1">
         <v>73</v>
       </c>
       <c r="I308" s="4" t="s">
@@ -6963,19 +8453,22 @@
       <c r="J308" s="4" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="309" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K308" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="309" s="1" customFormat="1" ht="12.8">
       <c r="B309" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="310" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" s="1" customFormat="1" ht="12.8">
       <c r="A310" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="311" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H311" s="1" t="n">
+    <row r="311" s="1" customFormat="1" ht="12.8">
+      <c r="H311" s="1">
         <v>60</v>
       </c>
       <c r="I311" s="4" t="s">
@@ -6984,9 +8477,12 @@
       <c r="J311" s="10" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="312" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H312" s="1" t="n">
+      <c r="K311" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="312" s="1" customFormat="1" ht="43.25">
+      <c r="H312" s="1">
         <v>61</v>
       </c>
       <c r="I312" s="4" t="s">
@@ -6995,9 +8491,12 @@
       <c r="J312" s="4" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="313" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H313" s="1" t="n">
+      <c r="K312" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="313" s="1" customFormat="1" ht="22.35">
+      <c r="H313" s="1">
         <v>62</v>
       </c>
       <c r="I313" s="4" t="s">
@@ -7006,9 +8505,12 @@
       <c r="J313" s="4" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="314" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H314" s="1" t="n">
+      <c r="K313" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="314" s="1" customFormat="1" ht="22.35">
+      <c r="H314" s="1">
         <v>63</v>
       </c>
       <c r="I314" s="4" t="s">
@@ -7017,9 +8519,12 @@
       <c r="J314" s="4" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="315" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H315" s="1" t="n">
+      <c r="K314" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="315" s="1" customFormat="1" ht="22.35">
+      <c r="H315" s="1">
         <v>64</v>
       </c>
       <c r="I315" s="4" t="s">
@@ -7028,9 +8533,12 @@
       <c r="J315" s="4" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="316" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H316" s="1" t="n">
+      <c r="K315" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="316" ht="32.8">
+      <c r="H316" s="1">
         <v>65</v>
       </c>
       <c r="I316" s="4" t="s">
@@ -7039,23 +8547,25 @@
       <c r="J316" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="K316" s="1"/>
-    </row>
-    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K316" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="317" ht="12.8">
       <c r="B317" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K317" s="1"/>
     </row>
-    <row r="318" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="319" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="320" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" s="1" customFormat="1" ht="12.8"/>
+    <row r="319" s="1" customFormat="1" ht="12.8"/>
+    <row r="320" s="1" customFormat="1" ht="12.8">
       <c r="A320" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="321" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H321" s="1" t="n">
+    <row r="321" s="1" customFormat="1" ht="23.85">
+      <c r="H321" s="1">
         <v>53</v>
       </c>
       <c r="I321" s="4" t="s">
@@ -7064,9 +8574,12 @@
       <c r="J321" s="10" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="322" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H322" s="1" t="n">
+      <c r="K321" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="322" s="1" customFormat="1" ht="23.85">
+      <c r="H322" s="1">
         <v>54</v>
       </c>
       <c r="I322" s="4" t="s">
@@ -7075,9 +8588,12 @@
       <c r="J322" s="10" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="323" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H323" s="1" t="n">
+      <c r="K322" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="323" s="1" customFormat="1" ht="23.85">
+      <c r="H323" s="1">
         <v>55</v>
       </c>
       <c r="I323" s="4" t="s">
@@ -7086,9 +8602,12 @@
       <c r="J323" s="10" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="324" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H324" s="1" t="n">
+      <c r="K323" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="324" s="1" customFormat="1" ht="23.85">
+      <c r="H324" s="1">
         <v>56</v>
       </c>
       <c r="I324" s="4" t="s">
@@ -7097,9 +8616,12 @@
       <c r="J324" s="10" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="325" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H325" s="1" t="n">
+      <c r="K324" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="325" s="1" customFormat="1" ht="12.8">
+      <c r="H325" s="1">
         <v>57</v>
       </c>
       <c r="I325" s="4" t="s">
@@ -7108,9 +8630,12 @@
       <c r="J325" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="326" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H326" s="1" t="n">
+      <c r="K325" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="326" s="1" customFormat="1" ht="35.05">
+      <c r="H326" s="1">
         <v>58</v>
       </c>
       <c r="I326" s="4" t="s">
@@ -7119,9 +8644,12 @@
       <c r="J326" s="10" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H327" s="1" t="n">
+      <c r="K326" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="327" ht="12.8">
+      <c r="H327" s="1">
         <v>59</v>
       </c>
       <c r="I327" s="4" t="s">
@@ -7130,23 +8658,25 @@
       <c r="J327" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K327" s="1"/>
-    </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K327" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="328" ht="12.8">
       <c r="B328" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K328" s="1"/>
     </row>
-    <row r="330" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="331" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="332" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" s="1" customFormat="1" ht="12.8"/>
+    <row r="331" s="1" customFormat="1" ht="12.8"/>
+    <row r="332" s="1" customFormat="1" ht="12.8">
       <c r="A332" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="333" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H333" s="1" t="n">
+    <row r="333" s="1" customFormat="1" ht="12.8">
+      <c r="H333" s="1">
         <v>45</v>
       </c>
       <c r="I333" s="4" t="s">
@@ -7155,9 +8685,12 @@
       <c r="J333" s="10" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="334" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H334" s="1" t="n">
+      <c r="K333" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="334" s="1" customFormat="1" ht="22.35">
+      <c r="H334" s="1">
         <v>46</v>
       </c>
       <c r="I334" s="4" t="s">
@@ -7166,9 +8699,12 @@
       <c r="J334" s="4" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="335" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H335" s="1" t="n">
+      <c r="K334" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="335" s="1" customFormat="1" ht="32.8">
+      <c r="H335" s="1">
         <v>50</v>
       </c>
       <c r="I335" s="4" t="s">
@@ -7177,9 +8713,12 @@
       <c r="J335" s="4" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="336" s="1" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H336" s="1" t="n">
+      <c r="K335" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="336" s="1" customFormat="1" ht="35.05">
+      <c r="H336" s="1">
         <v>47</v>
       </c>
       <c r="I336" s="4" t="s">
@@ -7188,9 +8727,12 @@
       <c r="J336" s="10" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="337" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H337" s="1" t="n">
+      <c r="K336" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="337" s="1" customFormat="1" ht="43.25">
+      <c r="H337" s="1">
         <v>48</v>
       </c>
       <c r="I337" s="4" t="s">
@@ -7199,9 +8741,12 @@
       <c r="J337" s="4" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="338" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H338" s="1" t="n">
+      <c r="K337" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="338" ht="22.35">
+      <c r="H338" s="1">
         <v>49</v>
       </c>
       <c r="I338" s="4" t="s">
@@ -7210,23 +8755,25 @@
       <c r="J338" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="K338" s="1"/>
-    </row>
-    <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K338" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="339" ht="12.8">
       <c r="B339" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K339" s="1"/>
     </row>
-    <row r="340" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="341" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="342" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" s="1" customFormat="1" ht="12.8"/>
+    <row r="341" s="1" customFormat="1" ht="12.8"/>
+    <row r="342" s="1" customFormat="1" ht="12.8">
       <c r="A342" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="343" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H343" s="1" t="n">
+    <row r="343" s="1" customFormat="1" ht="22.35">
+      <c r="H343" s="1">
         <v>1</v>
       </c>
       <c r="I343" s="4" t="s">
@@ -7235,9 +8782,12 @@
       <c r="J343" s="4" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="344" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H344" s="1" t="n">
+      <c r="K343" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="344" s="1" customFormat="1" ht="22.35">
+      <c r="H344" s="1">
         <v>2</v>
       </c>
       <c r="I344" s="4" t="s">
@@ -7246,9 +8796,12 @@
       <c r="J344" s="4" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="345" s="1" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H345" s="1" t="n">
+      <c r="K344" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="345" s="1" customFormat="1" ht="32.8">
+      <c r="H345" s="1">
         <v>5</v>
       </c>
       <c r="I345" s="4" t="s">
@@ -7257,9 +8810,12 @@
       <c r="J345" s="4" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="346" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H346" s="1" t="n">
+      <c r="K345" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="346" s="1" customFormat="1" ht="43.25">
+      <c r="H346" s="1">
         <v>6</v>
       </c>
       <c r="I346" s="4" t="s">
@@ -7268,9 +8824,12 @@
       <c r="J346" s="4" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="347" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H347" s="1" t="n">
+      <c r="K346" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="347" s="1" customFormat="1" ht="43.25">
+      <c r="H347" s="1">
         <v>212</v>
       </c>
       <c r="I347" s="4" t="s">
@@ -7279,9 +8838,12 @@
       <c r="J347" s="4" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="348" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H348" s="1" t="n">
+      <c r="K347" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="348" s="1" customFormat="1" ht="22.35">
+      <c r="H348" s="1">
         <v>52</v>
       </c>
       <c r="I348" s="4" t="s">
@@ -7290,9 +8852,12 @@
       <c r="J348" s="4" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="349" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H349" s="1" t="n">
+      <c r="K348" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="349" s="1" customFormat="1" ht="74.6">
+      <c r="H349" s="1">
         <v>17</v>
       </c>
       <c r="I349" s="4" t="s">
@@ -7301,9 +8866,12 @@
       <c r="J349" s="4" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H350" s="1" t="n">
+      <c r="K349" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="350" ht="12.8">
+      <c r="H350" s="1">
         <v>7</v>
       </c>
       <c r="I350" s="4" t="s">
@@ -7312,20 +8880,22 @@
       <c r="J350" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K350" s="1"/>
-    </row>
-    <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K350" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="351" ht="12.8">
       <c r="B351" s="4" t="s">
         <v>138</v>
       </c>
       <c r="K351" s="1"/>
     </row>
-    <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" ht="12.8">
       <c r="A353" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" ht="12.8">
       <c r="D354" s="1" t="s">
         <v>535</v>
       </c>
@@ -7333,8 +8903,8 @@
         <v>536</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H355" s="1" t="n">
+    <row r="355" ht="22.35">
+      <c r="H355" s="1">
         <v>8</v>
       </c>
       <c r="I355" s="4" t="s">
@@ -7343,9 +8913,12 @@
       <c r="J355" s="4" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="356" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H356" s="1" t="n">
+      <c r="K355" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="356" ht="43.25">
+      <c r="H356" s="1">
         <v>9</v>
       </c>
       <c r="I356" s="4" t="s">
@@ -7354,12 +8927,15 @@
       <c r="J356" s="4" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="357" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K356" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="357" ht="22.35">
       <c r="B357" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H357" s="1" t="n">
+      <c r="H357" s="1">
         <v>10</v>
       </c>
       <c r="I357" s="4" t="s">
@@ -7368,12 +8944,15 @@
       <c r="J357" s="4" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K357" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="360" ht="12.8">
       <c r="A360" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="H360" s="1" t="n">
+      <c r="H360" s="1">
         <v>11</v>
       </c>
       <c r="I360" s="1" t="s">
@@ -7382,15 +8961,18 @@
       <c r="J360" s="1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K360" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="361" ht="12.8">
       <c r="B361" s="1" t="s">
         <v>546</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H361" s="1" t="n">
+      <c r="H361" s="1">
         <v>12</v>
       </c>
       <c r="I361" s="1" t="s">
@@ -7399,15 +8981,18 @@
       <c r="J361" s="1" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K361" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="362" ht="12.8">
       <c r="B362" s="1" t="s">
         <v>546</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H362" s="1" t="n">
+      <c r="H362" s="1">
         <v>13</v>
       </c>
       <c r="I362" s="1" t="s">
@@ -7416,15 +9001,18 @@
       <c r="J362" s="1" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K362" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="363" ht="12.8">
       <c r="B363" s="1" t="s">
         <v>551</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H363" s="1" t="n">
+      <c r="H363" s="1">
         <v>14</v>
       </c>
       <c r="I363" s="1" t="s">
@@ -7433,8 +9021,11 @@
       <c r="J363" s="1" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K363" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="364" ht="12.8">
       <c r="B364" s="1" t="s">
         <v>138</v>
       </c>
@@ -7442,11 +9033,11 @@
         <v>554</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" ht="12.8">
       <c r="A368" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="H368" s="1" t="n">
+      <c r="H368" s="1">
         <v>15</v>
       </c>
       <c r="I368" s="1" t="s">
@@ -7455,19 +9046,22 @@
       <c r="J368" s="1" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K368" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="369" ht="12.8">
       <c r="B369" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" ht="12.8">
       <c r="A372" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H373" s="1" t="n">
+    <row r="373" ht="12.8">
+      <c r="H373" s="1">
         <v>16</v>
       </c>
       <c r="I373" s="1" t="s">
@@ -7476,20 +9070,23 @@
       <c r="J373" s="1" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K373" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="374" ht="12.8">
       <c r="B374" s="1" t="s">
         <v>138</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
